--- a/database/event/4998/event_4998_evp_summary.xlsx
+++ b/database/event/4998/event_4998_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.328</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4525</v>
+        <v>3.3765</v>
       </c>
       <c r="E2" t="n">
         <v>9.5893</v>
@@ -548,7 +548,7 @@
         <v>0.9688</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4047</v>
+        <v>2.3431</v>
       </c>
       <c r="E3" t="n">
         <v>6.9956</v>
@@ -594,7 +594,7 @@
         <v>0.9683</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4033</v>
+        <v>2.3417</v>
       </c>
       <c r="E4" t="n">
         <v>6.9921</v>
@@ -640,7 +640,7 @@
         <v>0.9461000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3387</v>
+        <v>2.278</v>
       </c>
       <c r="E5" t="n">
         <v>6.8321</v>
@@ -686,7 +686,7 @@
         <v>0.9459</v>
       </c>
       <c r="D6" t="n">
-        <v>2.338</v>
+        <v>2.2774</v>
       </c>
       <c r="E6" t="n">
         <v>6.8306</v>
@@ -732,7 +732,7 @@
         <v>0.7883</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8783</v>
+        <v>1.824</v>
       </c>
       <c r="E7" t="n">
         <v>5.6925</v>
@@ -778,7 +778,7 @@
         <v>0.6619</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5096</v>
+        <v>1.4604</v>
       </c>
       <c r="E8" t="n">
         <v>4.7798</v>
@@ -824,7 +824,7 @@
         <v>0.6019</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3345</v>
+        <v>1.2877</v>
       </c>
       <c r="E9" t="n">
         <v>4.3464</v>
@@ -870,7 +870,7 @@
         <v>0.5931999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3092</v>
+        <v>1.2628</v>
       </c>
       <c r="E10" t="n">
         <v>4.2839</v>
@@ -916,7 +916,7 @@
         <v>0.4874</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0006</v>
+        <v>0.9584</v>
       </c>
       <c r="E11" t="n">
         <v>3.5198</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1622</v>
+        <v>2.138</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2994</v>
+        <v>0.2961</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4521</v>
+        <v>0.4079</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1622</v>
+        <v>2.138</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1622</v>
+        <v>2.138</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1622</v>
+        <v>2.138</v>
       </c>
       <c r="I12" t="n">
         <v>2.1925</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0177</v>
+        <v>1.0064</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1409</v>
+        <v>0.1394</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0102</v>
+        <v>-0.043</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0177</v>
+        <v>1.0064</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0177</v>
+        <v>1.0064</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0177</v>
+        <v>1.0064</v>
       </c>
       <c r="I13" t="n">
         <v>1.032</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9813</v>
+        <v>0.9704</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1359</v>
+        <v>0.1344</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0249</v>
+        <v>-0.0573</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9813</v>
+        <v>0.9704</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9813</v>
+        <v>0.9704</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9813</v>
+        <v>0.9704</v>
       </c>
       <c r="I14" t="n">
         <v>0.9951</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9181</v>
+        <v>0.9079</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1271</v>
+        <v>0.1257</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0505</v>
+        <v>-0.0822</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9181</v>
+        <v>0.9079</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9181</v>
+        <v>0.9079</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9181</v>
+        <v>0.9079</v>
       </c>
       <c r="I15" t="n">
         <v>0.931</v>
@@ -1146,7 +1146,7 @@
         <v>0.1077</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1072</v>
+        <v>-0.1341</v>
       </c>
       <c r="E16" t="n">
         <v>0.7776999999999999</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6853</v>
       </c>
       <c r="C17" t="n">
-        <v>0.096</v>
+        <v>0.0949</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1414</v>
+        <v>-0.1709</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6853</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6853</v>
       </c>
       <c r="I17" t="n">
         <v>0.7027</v>
@@ -1238,7 +1238,7 @@
         <v>0.0746</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2037</v>
+        <v>-0.2292</v>
       </c>
       <c r="E18" t="n">
         <v>0.5389</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3219</v>
+        <v>0.3183</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0446</v>
+        <v>0.0441</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2913</v>
+        <v>-0.3171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3219</v>
+        <v>0.3183</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3219</v>
+        <v>0.3183</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3219</v>
+        <v>0.3183</v>
       </c>
       <c r="I19" t="n">
         <v>0.3264</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1048</v>
+        <v>-0.1037</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0145</v>
+        <v>-0.0144</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4637</v>
+        <v>-0.4852</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1048</v>
+        <v>-0.1037</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1048</v>
+        <v>-0.1037</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1048</v>
+        <v>-0.1037</v>
       </c>
       <c r="I20" t="n">
         <v>-0.1063</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2273</v>
+        <v>-0.2248</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0315</v>
+        <v>-0.0311</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5132</v>
+        <v>-0.5335</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2273</v>
+        <v>-0.2248</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2273</v>
+        <v>-0.2248</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2273</v>
+        <v>-0.2248</v>
       </c>
       <c r="I21" t="n">
         <v>-0.2305</v>
@@ -1422,7 +1422,7 @@
         <v>-0.0468</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5577</v>
+        <v>-0.5784</v>
       </c>
       <c r="E22" t="n">
         <v>-0.3376</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0621</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6025</v>
+        <v>-0.6226</v>
       </c>
       <c r="E23" t="n">
         <v>-0.4484</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5996</v>
+        <v>-0.5929</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.083</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6636</v>
+        <v>-0.6801</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5996</v>
+        <v>-0.5929</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5996</v>
+        <v>-0.5929</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5996</v>
+        <v>-0.5929</v>
       </c>
       <c r="I24" t="n">
         <v>-0.608</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1055</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.729</v>
+        <v>-0.7473</v>
       </c>
       <c r="E25" t="n">
         <v>-0.7615</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1094</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7406</v>
+        <v>-0.7587</v>
       </c>
       <c r="E26" t="n">
         <v>-0.7902</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1385</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E27" t="n">
         <v>-1</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1789</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9432</v>
+        <v>-0.9586</v>
       </c>
       <c r="E28" t="n">
         <v>-1.2918</v>
@@ -1744,7 +1744,7 @@
         <v>-0.267</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2004</v>
+        <v>-1.2121</v>
       </c>
       <c r="E29" t="n">
         <v>-1.9283</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2753</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2244</v>
+        <v>-1.2359</v>
       </c>
       <c r="E30" t="n">
         <v>-1.9878</v>
@@ -1836,7 +1836,7 @@
         <v>-0.4072</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6091</v>
+        <v>-1.6152</v>
       </c>
       <c r="E31" t="n">
         <v>-2.9401</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-5.2901</v>
+        <v>-5.2311</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.7326</v>
+        <v>-0.7244</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.5584</v>
+        <v>-2.528</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.2901</v>
+        <v>-5.2311</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.2901</v>
+        <v>-5.2311</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.2901</v>
+        <v>-5.2311</v>
       </c>
       <c r="I32" t="n">
         <v>-5.3643</v>

--- a/database/event/4998/event_4998_evp_summary.xlsx
+++ b/database/event/4998/event_4998_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.5893</v>
+        <v>8.797499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.328</v>
+        <v>1.2183</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3765</v>
+        <v>3.3336</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5893</v>
+        <v>8.797499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7231</v>
+        <v>4.3457</v>
       </c>
       <c r="H2" t="n">
-        <v>9.771699999999999</v>
+        <v>17.133</v>
       </c>
       <c r="I2" t="n">
-        <v>7.9202</v>
+        <v>8.9084</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7231</v>
+        <v>4.3457</v>
       </c>
       <c r="K2" t="n">
         <v>237</v>
@@ -529,7 +529,7 @@
         <v>181</v>
       </c>
       <c r="M2" t="n">
-        <v>12.6433</v>
+        <v>13.2541</v>
       </c>
       <c r="N2" t="n">
         <v>418</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9956</v>
+        <v>6.6695</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9688</v>
+        <v>0.9236</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3431</v>
+        <v>2.3729</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9956</v>
+        <v>6.6695</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2577</v>
+        <v>3.8142</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7379</v>
+        <v>2.8554</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5692</v>
+        <v>7.9524</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7035</v>
+        <v>4.1349</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7379</v>
+        <v>2.8554</v>
       </c>
       <c r="K3" t="n">
         <v>232</v>
@@ -575,7 +575,7 @@
         <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4414</v>
+        <v>6.9903</v>
       </c>
       <c r="N3" t="n">
         <v>409</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9921</v>
+        <v>6.6392</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9683</v>
+        <v>0.9194</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3417</v>
+        <v>2.3593</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9921</v>
+        <v>6.6392</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7055</v>
+        <v>4.4518</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2866</v>
+        <v>2.1874</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3708</v>
+        <v>11.371</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1637</v>
+        <v>5.9124</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2866</v>
+        <v>2.1874</v>
       </c>
       <c r="K4" t="n">
         <v>237</v>
@@ -621,7 +621,7 @@
         <v>126</v>
       </c>
       <c r="M4" t="n">
-        <v>7.4503</v>
+        <v>8.0998</v>
       </c>
       <c r="N4" t="n">
         <v>363</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8321</v>
+        <v>6.6289</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="D5" t="n">
-        <v>2.278</v>
+        <v>2.3546</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8321</v>
+        <v>6.6289</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7047</v>
+        <v>4.4518</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1274</v>
+        <v>2.1771</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3676</v>
+        <v>11.2185</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1611</v>
+        <v>5.8331</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1274</v>
+        <v>2.1771</v>
       </c>
       <c r="K5" t="n">
         <v>237</v>
@@ -667,7 +667,7 @@
         <v>162</v>
       </c>
       <c r="M5" t="n">
-        <v>7.288500000000001</v>
+        <v>8.010199999999999</v>
       </c>
       <c r="N5" t="n">
         <v>399</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.8306</v>
+        <v>6.5571</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9459</v>
+        <v>0.908</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2774</v>
+        <v>2.3222</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8306</v>
+        <v>6.5571</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5057</v>
+        <v>4.3873</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3249</v>
+        <v>2.1698</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5671</v>
+        <v>9.9716</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5123</v>
+        <v>5.1848</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3249</v>
+        <v>2.1698</v>
       </c>
       <c r="K6" t="n">
         <v>232</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>6.837199999999999</v>
+        <v>7.3546</v>
       </c>
       <c r="N6" t="n">
         <v>392</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6925</v>
+        <v>5.7365</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7883</v>
+        <v>0.7944</v>
       </c>
       <c r="D7" t="n">
-        <v>1.824</v>
+        <v>1.9517</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6925</v>
+        <v>5.7365</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5912</v>
+        <v>4.4518</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1013</v>
+        <v>1.2847</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9109</v>
+        <v>10.5523</v>
       </c>
       <c r="I7" t="n">
-        <v>4.791</v>
+        <v>5.4867</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1013</v>
+        <v>1.2847</v>
       </c>
       <c r="K7" t="n">
         <v>237</v>
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>5.892300000000001</v>
+        <v>6.7714</v>
       </c>
       <c r="N7" t="n">
         <v>399</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7798</v>
+        <v>5.2397</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6619</v>
+        <v>0.7256</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4604</v>
+        <v>1.7274</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7798</v>
+        <v>5.2397</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9865</v>
+        <v>3.3756</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7933</v>
+        <v>1.8641</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9865</v>
+        <v>6.4073</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4207</v>
+        <v>3.3315</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7933</v>
+        <v>1.8641</v>
       </c>
       <c r="K8" t="n">
         <v>237</v>
@@ -805,7 +805,7 @@
         <v>179</v>
       </c>
       <c r="M8" t="n">
-        <v>4.214</v>
+        <v>5.195600000000001</v>
       </c>
       <c r="N8" t="n">
         <v>416</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3464</v>
+        <v>3.9843</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6019</v>
+        <v>0.5518</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2877</v>
+        <v>1.1607</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3464</v>
+        <v>3.9843</v>
       </c>
       <c r="F9" t="n">
-        <v>3.582</v>
+        <v>4.0089</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7644</v>
+        <v>-0.0246</v>
       </c>
       <c r="H9" t="n">
-        <v>3.582</v>
+        <v>8.638500000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9033</v>
+        <v>4.4916</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7644</v>
+        <v>-0.0246</v>
       </c>
       <c r="K9" t="n">
         <v>277</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6677</v>
+        <v>4.467</v>
       </c>
       <c r="N9" t="n">
         <v>354</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2839</v>
+        <v>3.855</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5339</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2628</v>
+        <v>1.1023</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2839</v>
+        <v>3.855</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3094</v>
+        <v>3.2776</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0255</v>
+        <v>0.5774</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7773</v>
+        <v>6.0621</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8722</v>
+        <v>3.152</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0255</v>
+        <v>0.5774</v>
       </c>
       <c r="K10" t="n">
         <v>277</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8467</v>
+        <v>3.7294</v>
       </c>
       <c r="N10" t="n">
         <v>354</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5198</v>
+        <v>3.2775</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4874</v>
+        <v>0.4539</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9584</v>
+        <v>0.8416</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5198</v>
+        <v>3.2775</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9391</v>
+        <v>3.5216</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4193</v>
+        <v>-0.2441</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9391</v>
+        <v>6.9216</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1927</v>
+        <v>3.5989</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4193</v>
+        <v>-0.2441</v>
       </c>
       <c r="K11" t="n">
         <v>277</v>
@@ -943,7 +943,7 @@
         <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7734</v>
+        <v>3.3548</v>
       </c>
       <c r="N11" t="n">
         <v>354</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.138</v>
+        <v>2.8202</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2961</v>
+        <v>0.3905</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4079</v>
+        <v>0.6352</v>
       </c>
       <c r="E12" t="n">
-        <v>2.138</v>
+        <v>2.8202</v>
       </c>
       <c r="F12" t="n">
-        <v>2.138</v>
+        <v>2.8202</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.138</v>
+        <v>2.833</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1925</v>
+        <v>3.1971</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1925</v>
+        <v>3.1971</v>
       </c>
       <c r="N12" t="n">
         <v>263</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0064</v>
+        <v>1.605</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1394</v>
+        <v>0.2223</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.043</v>
+        <v>0.0866</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0064</v>
+        <v>1.605</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0064</v>
+        <v>1.605</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0064</v>
+        <v>1.605</v>
       </c>
       <c r="I13" t="n">
-        <v>1.032</v>
+        <v>1.8113</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.032</v>
+        <v>1.8113</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1044,32 +1044,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9704</v>
+        <v>1.5211</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1344</v>
+        <v>0.2106</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0573</v>
+        <v>0.0487</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9704</v>
+        <v>1.5211</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9704</v>
+        <v>1.5211</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9704</v>
+        <v>1.5211</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9951</v>
+        <v>1.7166</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9951</v>
+        <v>1.7166</v>
       </c>
       <c r="N14" t="n">
         <v>263</v>
@@ -1090,32 +1090,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9079</v>
+        <v>1.4574</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1257</v>
+        <v>0.2018</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0822</v>
+        <v>0.0199</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9079</v>
+        <v>1.4574</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9079</v>
+        <v>1.4574</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9079</v>
+        <v>1.4574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.931</v>
+        <v>1.6447</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.931</v>
+        <v>1.6447</v>
       </c>
       <c r="N15" t="n">
         <v>263</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.4237</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1077</v>
+        <v>0.1972</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1341</v>
+        <v>0.0047</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.4237</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3536</v>
+        <v>1.287</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4241</v>
+        <v>0.1367</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3536</v>
+        <v>1.287</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2866</v>
+        <v>0.6692</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4241</v>
+        <v>0.1367</v>
       </c>
       <c r="K16" t="n">
         <v>232</v>
@@ -1173,7 +1173,7 @@
         <v>160</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7107</v>
+        <v>0.8059000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>392</v>
@@ -1182,216 +1182,216 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6853</v>
+        <v>1.4148</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0949</v>
+        <v>0.1959</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1709</v>
+        <v>0.0007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6853</v>
+        <v>1.4148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6853</v>
+        <v>1.3167</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6853</v>
+        <v>1.3167</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7027</v>
+        <v>0.6846</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7027</v>
+        <v>0.7827</v>
       </c>
       <c r="N17" t="n">
-        <v>263</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5389</v>
+        <v>1.2856</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0746</v>
+        <v>0.178</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2292</v>
+        <v>-0.0576</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5389</v>
+        <v>1.2856</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4328</v>
+        <v>1.2856</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1061</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4328</v>
+        <v>1.2856</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3508</v>
+        <v>1.4508</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1061</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L18" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4569</v>
+        <v>1.4508</v>
       </c>
       <c r="N18" t="n">
-        <v>335</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3183</v>
+        <v>1.1905</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0441</v>
+        <v>0.1649</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3171</v>
+        <v>-0.1006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3183</v>
+        <v>1.1905</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3183</v>
+        <v>2.1905</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3183</v>
+        <v>2.2315</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3264</v>
+        <v>1.1603</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K19" t="n">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3264</v>
+        <v>0.1603000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>247</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1037</v>
+        <v>0.6121</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0144</v>
+        <v>0.0848</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4852</v>
+        <v>-0.3617</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1037</v>
+        <v>0.6121</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1037</v>
+        <v>0.1687</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.4434</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1037</v>
+        <v>0.1687</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1063</v>
+        <v>0.0877</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.4434</v>
       </c>
       <c r="K20" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1063</v>
+        <v>0.5311</v>
       </c>
       <c r="N20" t="n">
-        <v>247</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2248</v>
+        <v>0.5151</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0311</v>
+        <v>0.0713</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5335</v>
+        <v>-0.4055</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2248</v>
+        <v>0.5151</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2248</v>
+        <v>0.5151</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2248</v>
+        <v>0.5151</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2305</v>
+        <v>0.5813</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2305</v>
+        <v>0.5813</v>
       </c>
       <c r="N21" t="n">
         <v>247</v>
@@ -1412,219 +1412,219 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3376</v>
+        <v>0.4728</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0468</v>
+        <v>0.0655</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5784</v>
+        <v>-0.4246</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3376</v>
+        <v>0.4728</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6665</v>
+        <v>0.4728</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3289</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6665</v>
+        <v>0.4728</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5402</v>
+        <v>0.5336</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3289</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2113</v>
+        <v>0.5336</v>
       </c>
       <c r="N22" t="n">
-        <v>335</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4484</v>
+        <v>0.3654</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0621</v>
+        <v>0.0506</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6226</v>
+        <v>-0.4731</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4484</v>
+        <v>0.3654</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5516</v>
+        <v>0.3654</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5516</v>
+        <v>0.3654</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4471</v>
+        <v>0.4124</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="L23" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.4124</v>
       </c>
       <c r="N23" t="n">
-        <v>354</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5929</v>
+        <v>0.2912</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0403</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6801</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5929</v>
+        <v>0.2912</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5929</v>
+        <v>0.5002</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.209</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5929</v>
+        <v>0.5002</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.608</v>
+        <v>0.2601</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.209</v>
       </c>
       <c r="K24" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.608</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>247</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vegi</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7615</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1055</v>
+        <v>-0.0134</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7473</v>
+        <v>-0.6816</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7615</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3626</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6011</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3626</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1044</v>
+        <v>-0.109</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6011</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="L25" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5033000000000001</v>
+        <v>-0.109</v>
       </c>
       <c r="N25" t="n">
-        <v>335</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>Vegi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7902</v>
+        <v>-0.3311</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1094</v>
+        <v>-0.0459</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7587</v>
+        <v>-0.7875</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7902</v>
+        <v>-0.3311</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4009</v>
+        <v>-0.9407</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3893</v>
+        <v>0.6096</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4009</v>
+        <v>-0.9407</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3249</v>
+        <v>-0.4891</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3893</v>
+        <v>0.6096</v>
       </c>
       <c r="K26" t="n">
         <v>256</v>
@@ -1633,7 +1633,7 @@
         <v>79</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7141999999999999</v>
+        <v>0.1205000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>335</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rejin</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1</v>
+        <v>-0.383</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1385</v>
+        <v>-0.053</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8423</v>
+        <v>-0.8109</v>
       </c>
       <c r="E27" t="n">
-        <v>-1</v>
+        <v>-0.383</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.3034</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0.9204</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-1.3034</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-0.6777</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0.9204</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="L27" t="n">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="M27" t="n">
-        <v>-1</v>
+        <v>0.2427</v>
       </c>
       <c r="N27" t="n">
-        <v>47</v>
+        <v>375</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.2918</v>
+        <v>-0.4478</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1789</v>
+        <v>-0.062</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9586</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2918</v>
+        <v>-0.4478</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.7981</v>
+        <v>0.5356</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5063</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.7981</v>
+        <v>0.5356</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.4574</v>
+        <v>0.2785</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5063</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="L28" t="n">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.9511000000000001</v>
+        <v>-0.7049000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>375</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Rejin</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.9283</v>
+        <v>-1</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.267</v>
+        <v>-0.1385</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2121</v>
+        <v>-1.0895</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9283</v>
+        <v>-1</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9283</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9283</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7524</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>-1</v>
       </c>
       <c r="K29" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.7524</v>
+        <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>354</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.9878</v>
+        <v>-2.1661</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2753</v>
+        <v>-0.3</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.2359</v>
+        <v>-1.6159</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.9878</v>
+        <v>-2.1661</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.597</v>
+        <v>-2.8479</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6092</v>
+        <v>0.6818</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.597</v>
+        <v>-2.8479</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.1049</v>
+        <v>-1.4808</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6092</v>
+        <v>0.6818</v>
       </c>
       <c r="K30" t="n">
         <v>232</v>
@@ -1817,7 +1817,7 @@
         <v>113</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4957</v>
+        <v>-0.7989999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>345</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.9401</v>
+        <v>-2.7501</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4072</v>
+        <v>-0.3808</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6152</v>
+        <v>-1.8795</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.9401</v>
+        <v>-2.7501</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.9401</v>
+        <v>-1.8925</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>-0.8576</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.9401</v>
+        <v>-1.8925</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.5725</v>
+        <v>-0.984</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>-0.8576</v>
       </c>
       <c r="K31" t="n">
         <v>256</v>
@@ -1863,7 +1863,7 @@
         <v>79</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.5725</v>
+        <v>-1.8416</v>
       </c>
       <c r="N31" t="n">
         <v>335</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-5.2311</v>
+        <v>-3.9068</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.7244</v>
+        <v>-0.541</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.528</v>
+        <v>-2.4017</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.2311</v>
+        <v>-3.9068</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.2311</v>
+        <v>-3.9068</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.2311</v>
+        <v>-3.9068</v>
       </c>
       <c r="I32" t="n">
-        <v>-5.3643</v>
+        <v>-4.4089</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.3643</v>
+        <v>-4.4089</v>
       </c>
       <c r="N32" t="n">
         <v>263</v>
@@ -2015,10 +2015,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5435</v>
+        <v>0.6015</v>
       </c>
       <c r="J2" t="n">
-        <v>19.566</v>
+        <v>21.654</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3286</v>
+        <v>0.4023</v>
       </c>
       <c r="J3" t="n">
-        <v>11.8296</v>
+        <v>14.4828</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0374</v>
+        <v>0.0375</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3464</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0587</v>
+        <v>1.0416</v>
       </c>
       <c r="J5" t="n">
-        <v>38.1132</v>
+        <v>37.4976</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9731</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>35.0316</v>
+        <v>35.1828</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4806</v>
+        <v>0.5682</v>
       </c>
       <c r="J7" t="n">
-        <v>17.3016</v>
+        <v>20.4552</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4065</v>
+        <v>-0.2536</v>
       </c>
       <c r="J8" t="n">
-        <v>-14.634</v>
+        <v>-9.1296</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5272</v>
+        <v>-0.3406</v>
       </c>
       <c r="J9" t="n">
-        <v>-18.9792</v>
+        <v>-12.2616</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4124</v>
+        <v>0.4806</v>
       </c>
       <c r="J10" t="n">
-        <v>14.8464</v>
+        <v>17.3016</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3697</v>
+        <v>0.4267</v>
       </c>
       <c r="J11" t="n">
-        <v>13.3092</v>
+        <v>15.3612</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4483</v>
       </c>
       <c r="J12" t="n">
-        <v>8.5085</v>
+        <v>7.6211</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3418</v>
+        <v>0.2849</v>
       </c>
       <c r="J13" t="n">
-        <v>5.8106</v>
+        <v>4.8433</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.62</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5981</v>
+        <v>-0.3956</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.1677</v>
+        <v>-6.7252</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5053</v>
+        <v>-0.3298</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.5901</v>
+        <v>-5.6066</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.3676</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.503</v>
+        <v>-6.2492</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1944</v>
+        <v>-0.8677</v>
       </c>
       <c r="J17" t="n">
-        <v>-20.3048</v>
+        <v>-14.7509</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.276</v>
+        <v>-0.9379</v>
       </c>
       <c r="J18" t="n">
-        <v>-21.692</v>
+        <v>-15.9443</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2861</v>
+        <v>-0.9467</v>
       </c>
       <c r="J19" t="n">
-        <v>-21.8637</v>
+        <v>-16.0939</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>2.15</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5063</v>
+        <v>1.3167</v>
       </c>
       <c r="J20" t="n">
-        <v>25.6071</v>
+        <v>22.3839</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>1.87</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2309</v>
+        <v>1.1232</v>
       </c>
       <c r="J21" t="n">
-        <v>20.9253</v>
+        <v>19.0944</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4322</v>
+        <v>1.2968</v>
       </c>
       <c r="J22" t="n">
-        <v>42.966</v>
+        <v>38.904</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.66</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4134</v>
+        <v>1.2852</v>
       </c>
       <c r="J23" t="n">
-        <v>42.402</v>
+        <v>38.556</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>1.51</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1138</v>
+        <v>1.109</v>
       </c>
       <c r="J24" t="n">
-        <v>33.414</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>1.29</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6042</v>
+        <v>0.7217</v>
       </c>
       <c r="J25" t="n">
-        <v>18.126</v>
+        <v>21.651</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>1.16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3019</v>
+        <v>0.4066</v>
       </c>
       <c r="J26" t="n">
-        <v>9.057</v>
+        <v>12.198</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1972</v>
+        <v>-0.1508</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.916</v>
+        <v>-4.524</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>0.62</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3922</v>
       </c>
       <c r="J28" t="n">
-        <v>-17.766</v>
+        <v>-11.766</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7783</v>
+        <v>-0.5303</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.349</v>
+        <v>-15.909</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.22</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4693</v>
+        <v>0.5431</v>
       </c>
       <c r="J30" t="n">
-        <v>14.079</v>
+        <v>16.293</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1791</v>
+        <v>0.1621</v>
       </c>
       <c r="J31" t="n">
-        <v>5.373</v>
+        <v>4.863</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7904</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>22.1312</v>
+        <v>16.5256</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>0.89</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1564</v>
+        <v>-0.1283</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.3792</v>
+        <v>-3.5924</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3936</v>
+        <v>-0.258</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.0208</v>
+        <v>-7.224</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>0.63</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5772</v>
+        <v>-0.3817</v>
       </c>
       <c r="J35" t="n">
-        <v>-16.1616</v>
+        <v>-10.6876</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.5657</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.0748</v>
+        <v>-15.8396</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6067</v>
+        <v>0.4544</v>
       </c>
       <c r="J37" t="n">
-        <v>16.9876</v>
+        <v>12.7232</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5823</v>
+        <v>0.4415</v>
       </c>
       <c r="J38" t="n">
-        <v>16.3044</v>
+        <v>12.362</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4103</v>
+        <v>0.3556</v>
       </c>
       <c r="J39" t="n">
-        <v>11.4884</v>
+        <v>9.956799999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1716</v>
+        <v>0.1882</v>
       </c>
       <c r="J40" t="n">
-        <v>4.8048</v>
+        <v>5.2696</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1373</v>
+        <v>-0.0601</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.8444</v>
+        <v>-1.6828</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2911</v>
+        <v>0.9163</v>
       </c>
       <c r="J42" t="n">
-        <v>29.6953</v>
+        <v>21.0749</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9615</v>
+        <v>0.7135</v>
       </c>
       <c r="J43" t="n">
-        <v>22.1145</v>
+        <v>16.4105</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.872</v>
+        <v>0.6616</v>
       </c>
       <c r="J44" t="n">
-        <v>20.056</v>
+        <v>15.2168</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1515</v>
+        <v>0.23</v>
       </c>
       <c r="J45" t="n">
-        <v>3.4845</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3785</v>
+        <v>-0.2978</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.705500000000001</v>
+        <v>-6.8494</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4528</v>
+        <v>0.4462</v>
       </c>
       <c r="J47" t="n">
-        <v>10.4144</v>
+        <v>10.2626</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>0.83</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2152</v>
+        <v>-0.1783</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.9496</v>
+        <v>-4.1009</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.73</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.398</v>
+        <v>-0.2753</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.154</v>
+        <v>-6.3319</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.64</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5372</v>
+        <v>-0.3594</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.3556</v>
+        <v>-8.2662</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.36</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8933</v>
+        <v>-0.6194</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.5459</v>
+        <v>-14.2462</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2795</v>
+        <v>0.9008</v>
       </c>
       <c r="J52" t="n">
-        <v>35.826</v>
+        <v>25.2224</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1194</v>
+        <v>0.1705</v>
       </c>
       <c r="J53" t="n">
-        <v>3.3432</v>
+        <v>4.774</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0485</v>
+        <v>0.103</v>
       </c>
       <c r="J54" t="n">
-        <v>1.358</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0098</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2744</v>
+        <v>1.8508</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>1.02</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0098</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2744</v>
+        <v>1.8508</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4558</v>
+        <v>0.4472</v>
       </c>
       <c r="J57" t="n">
-        <v>12.7624</v>
+        <v>12.5216</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1026</v>
+        <v>-0.081</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.8728</v>
+        <v>-2.268</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2821</v>
+        <v>-0.1781</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.8988</v>
+        <v>-4.9868</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3457</v>
+        <v>-0.2189</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.679600000000001</v>
+        <v>-6.1292</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.434</v>
+        <v>-0.2781</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.152</v>
+        <v>-7.7868</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5272</v>
+        <v>0.4202</v>
       </c>
       <c r="J62" t="n">
-        <v>14.7616</v>
+        <v>11.7656</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4879</v>
+        <v>0.3968</v>
       </c>
       <c r="J63" t="n">
-        <v>13.6612</v>
+        <v>11.1104</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0555</v>
+        <v>0.0487</v>
       </c>
       <c r="J64" t="n">
-        <v>1.554</v>
+        <v>1.3636</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3289</v>
+        <v>-0.2004</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.209199999999999</v>
+        <v>-5.6112</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5994</v>
+        <v>-0.3943</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.7832</v>
+        <v>-11.0404</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.4</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6022</v>
+        <v>0.4465</v>
       </c>
       <c r="J67" t="n">
-        <v>16.8616</v>
+        <v>12.502</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.34</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5274</v>
+        <v>0.4058</v>
       </c>
       <c r="J68" t="n">
-        <v>14.7672</v>
+        <v>11.3624</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.435</v>
+        <v>0.3571</v>
       </c>
       <c r="J69" t="n">
-        <v>12.18</v>
+        <v>9.998799999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2121</v>
+        <v>-0.1146</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9388</v>
+        <v>-3.2088</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4774</v>
+        <v>-0.3028</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.3672</v>
+        <v>-8.478400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.92</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8202</v>
+        <v>1.3237</v>
       </c>
       <c r="J72" t="n">
-        <v>38.2242</v>
+        <v>27.7977</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1252</v>
+        <v>0.8306</v>
       </c>
       <c r="J73" t="n">
-        <v>23.6292</v>
+        <v>17.4426</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>1.3</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6509</v>
+        <v>0.5828</v>
       </c>
       <c r="J74" t="n">
-        <v>13.6689</v>
+        <v>12.2388</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>1.2</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4172</v>
+        <v>0.4439</v>
       </c>
       <c r="J75" t="n">
-        <v>8.761200000000001</v>
+        <v>9.321899999999999</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0795</v>
+        <v>0.1691</v>
       </c>
       <c r="J76" t="n">
-        <v>1.6695</v>
+        <v>3.5511</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.186</v>
+        <v>0.169</v>
       </c>
       <c r="J77" t="n">
-        <v>3.906</v>
+        <v>3.549</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>0.73</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3386</v>
+        <v>-0.2661</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.1106</v>
+        <v>-5.5881</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5662</v>
+        <v>-0.3852</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.8902</v>
+        <v>-8.0892</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6096</v>
+        <v>-0.4132</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.8016</v>
+        <v>-8.677199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.5069</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.6345</v>
+        <v>-10.6449</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2891</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>36.0948</v>
+        <v>25.7292</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.49</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1493</v>
+        <v>0.8324</v>
       </c>
       <c r="J83" t="n">
-        <v>32.1804</v>
+        <v>23.3072</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.42</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0023</v>
+        <v>0.7446</v>
       </c>
       <c r="J84" t="n">
-        <v>28.0644</v>
+        <v>20.8488</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2194</v>
+        <v>0.3052</v>
       </c>
       <c r="J85" t="n">
-        <v>6.1432</v>
+        <v>8.5456</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3277</v>
+        <v>-0.2429</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.175599999999999</v>
+        <v>-6.8012</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>0.051</v>
+        <v>0.0026</v>
       </c>
       <c r="J87" t="n">
-        <v>1.428</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1219</v>
+        <v>-0.1156</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.4132</v>
+        <v>-3.2368</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.7</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4553</v>
+        <v>-0.3054</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.7484</v>
+        <v>-8.5512</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5429</v>
+        <v>-0.3619</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.2012</v>
+        <v>-10.1332</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5843</v>
+        <v>-0.39</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.3604</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.05</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2533</v>
+        <v>0.2534</v>
       </c>
       <c r="J92" t="n">
-        <v>5.3193</v>
+        <v>5.3214</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>0.75</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3313</v>
+        <v>-0.2537</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.9573</v>
+        <v>-5.3277</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>0.73</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3668</v>
+        <v>-0.2725</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.7028</v>
+        <v>-5.7225</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5688</v>
+        <v>-0.3828</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.9448</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.45</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7798</v>
+        <v>-0.5322</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.3758</v>
+        <v>-11.1762</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.91</v>
       </c>
       <c r="I97" t="n">
-        <v>1.8851</v>
+        <v>1.5901</v>
       </c>
       <c r="J97" t="n">
-        <v>39.5871</v>
+        <v>33.3921</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1.39</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8862</v>
+        <v>0.9497</v>
       </c>
       <c r="J98" t="n">
-        <v>18.6102</v>
+        <v>19.9437</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.635</v>
+        <v>0.7369</v>
       </c>
       <c r="J99" t="n">
-        <v>13.335</v>
+        <v>15.4749</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4228</v>
+        <v>0.5239</v>
       </c>
       <c r="J100" t="n">
-        <v>8.8788</v>
+        <v>11.0019</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>1.12</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2221</v>
+        <v>0.3164</v>
       </c>
       <c r="J101" t="n">
-        <v>4.6641</v>
+        <v>6.6444</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.5232</v>
+        <v>1.3389</v>
       </c>
       <c r="J102" t="n">
-        <v>38.08</v>
+        <v>33.4725</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.5232</v>
+        <v>1.3389</v>
       </c>
       <c r="J103" t="n">
-        <v>38.08</v>
+        <v>33.4725</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0094</v>
+        <v>0.081</v>
       </c>
       <c r="J104" t="n">
-        <v>0.235</v>
+        <v>2.025</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.333</v>
+        <v>-0.254</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.324999999999999</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.803</v>
+        <v>-0.7549</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.075</v>
+        <v>-18.8725</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5298</v>
+        <v>0.6264</v>
       </c>
       <c r="J107" t="n">
-        <v>13.245</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1277</v>
+        <v>0.1015</v>
       </c>
       <c r="J108" t="n">
-        <v>3.1925</v>
+        <v>2.5375</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0959</v>
+        <v>-0.0866</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.3975</v>
+        <v>-2.165</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4039</v>
+        <v>-0.2616</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.0975</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.34</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9298</v>
+        <v>-0.6493</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.245</v>
+        <v>-16.2325</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6821</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1123</v>
+        <v>15.6883</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>0.95</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.6445</v>
+        <v>-1.5272</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3389</v>
+        <v>-0.2164</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.7947</v>
+        <v>-4.9772</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4141</v>
+        <v>-0.2658</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.5243</v>
+        <v>-6.1134</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5648</v>
+        <v>-0.3709</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.9904</v>
+        <v>-8.5307</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9474</v>
+        <v>0.948</v>
       </c>
       <c r="J117" t="n">
-        <v>21.7902</v>
+        <v>21.804</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7405</v>
+        <v>0.7458</v>
       </c>
       <c r="J118" t="n">
-        <v>17.0315</v>
+        <v>17.1534</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>1.26</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6994</v>
       </c>
       <c r="J119" t="n">
-        <v>15.893</v>
+        <v>16.0862</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3185</v>
+        <v>0.3834</v>
       </c>
       <c r="J120" t="n">
-        <v>7.3255</v>
+        <v>8.818199999999999</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1839</v>
+        <v>-0.1051</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.2297</v>
+        <v>-2.4173</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8848</v>
+        <v>0.8681</v>
       </c>
       <c r="J122" t="n">
-        <v>26.544</v>
+        <v>26.043</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5163</v>
+        <v>0.5028</v>
       </c>
       <c r="J123" t="n">
-        <v>15.489</v>
+        <v>15.084</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2572</v>
+        <v>0.2929</v>
       </c>
       <c r="J124" t="n">
-        <v>7.716</v>
+        <v>8.787000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.159</v>
+        <v>0.2044</v>
       </c>
       <c r="J125" t="n">
-        <v>4.77</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3295</v>
+        <v>-0.2607</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.885</v>
+        <v>-7.821</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4149</v>
+        <v>0.4779</v>
       </c>
       <c r="J127" t="n">
-        <v>12.447</v>
+        <v>14.337</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1389</v>
+        <v>0.141</v>
       </c>
       <c r="J128" t="n">
-        <v>4.167</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0455</v>
+        <v>0.0389</v>
       </c>
       <c r="J129" t="n">
-        <v>1.365</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1899</v>
+        <v>-0.1108</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.697</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4382</v>
+        <v>-0.2776</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.146</v>
+        <v>-8.327999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3619</v>
+        <v>0.3984</v>
       </c>
       <c r="J132" t="n">
-        <v>7.9618</v>
+        <v>8.764799999999999</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>0.95</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0044</v>
+        <v>-0.0371</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.0968</v>
+        <v>-0.8162</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>0.58</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6194</v>
+        <v>-0.4153</v>
       </c>
       <c r="J134" t="n">
-        <v>-13.6268</v>
+        <v>-9.1366</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.646</v>
+        <v>-0.434</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.212</v>
+        <v>-9.548</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6979</v>
+        <v>-0.4713</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.3538</v>
+        <v>-10.3686</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.84</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7917</v>
+        <v>1.5223</v>
       </c>
       <c r="J137" t="n">
-        <v>39.4174</v>
+        <v>33.4906</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.51</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1783</v>
+        <v>1.1267</v>
       </c>
       <c r="J138" t="n">
-        <v>25.9226</v>
+        <v>24.7874</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3924</v>
+        <v>0.4848</v>
       </c>
       <c r="J139" t="n">
-        <v>8.6328</v>
+        <v>10.6656</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0983</v>
+        <v>0.1837</v>
       </c>
       <c r="J140" t="n">
-        <v>2.1626</v>
+        <v>4.0414</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0683</v>
+        <v>0.1528</v>
       </c>
       <c r="J141" t="n">
-        <v>1.5026</v>
+        <v>3.3616</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>1.809</v>
+        <v>1.534</v>
       </c>
       <c r="J142" t="n">
-        <v>41.607</v>
+        <v>35.282</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2779</v>
+        <v>1.188</v>
       </c>
       <c r="J143" t="n">
-        <v>29.3917</v>
+        <v>27.324</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4911</v>
+        <v>0.5834</v>
       </c>
       <c r="J144" t="n">
-        <v>11.2953</v>
+        <v>13.4182</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1838</v>
+        <v>0.2717</v>
       </c>
       <c r="J145" t="n">
-        <v>4.2274</v>
+        <v>6.2491</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4263</v>
+        <v>-0.345</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.8049</v>
+        <v>-7.935</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.14</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3575</v>
+        <v>0.3915</v>
       </c>
       <c r="J147" t="n">
-        <v>8.2225</v>
+        <v>9.0045</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1167</v>
+        <v>0.0843</v>
       </c>
       <c r="J148" t="n">
-        <v>2.6841</v>
+        <v>1.9389</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0476</v>
+        <v>0.0045</v>
       </c>
       <c r="J149" t="n">
-        <v>1.0948</v>
+        <v>0.1035</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5624</v>
+        <v>-0.3715</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.9352</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.37</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8924</v>
+        <v>-0.6192</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.5252</v>
+        <v>-14.2416</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.76</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9076</v>
+        <v>0.8386</v>
       </c>
       <c r="J152" t="n">
-        <v>17.2444</v>
+        <v>15.9334</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7454</v>
+        <v>0.6915</v>
       </c>
       <c r="J153" t="n">
-        <v>14.1626</v>
+        <v>13.1385</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.42</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5004</v>
+        <v>0.5017</v>
       </c>
       <c r="J154" t="n">
-        <v>9.5076</v>
+        <v>9.532299999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>1.39</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4633</v>
+        <v>0.4697</v>
       </c>
       <c r="J155" t="n">
-        <v>8.8027</v>
+        <v>8.924300000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>1.33</v>
       </c>
       <c r="I156" t="n">
-        <v>0.3889</v>
+        <v>0.4039</v>
       </c>
       <c r="J156" t="n">
-        <v>7.3891</v>
+        <v>7.6741</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>0.73</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2386</v>
+        <v>-0.2117</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.5334</v>
+        <v>-4.0223</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>0.53</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.5528</v>
+        <v>-0.4213</v>
       </c>
       <c r="J158" t="n">
-        <v>-10.5032</v>
+        <v>-8.0047</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.6579</v>
+        <v>-0.4651</v>
       </c>
       <c r="J159" t="n">
-        <v>-12.5001</v>
+        <v>-8.8369</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.42</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.753</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.307</v>
+        <v>-9.9123</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.38</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8109</v>
+        <v>-0.5606</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.4071</v>
+        <v>-10.6514</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4341</v>
+        <v>0.3635</v>
       </c>
       <c r="J162" t="n">
-        <v>13.023</v>
+        <v>10.905</v>
       </c>
     </row>
     <row r="163">
@@ -8455,10 +8455,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4203</v>
+        <v>0.351</v>
       </c>
       <c r="J163" t="n">
-        <v>12.609</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="164">
@@ -8495,10 +8495,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0668</v>
+        <v>-0.0257</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.004</v>
+        <v>-0.771</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1744</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.232</v>
+        <v>-2.826</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2925</v>
+        <v>-0.1734</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.775</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6947</v>
+        <v>0.8589</v>
       </c>
       <c r="J167" t="n">
-        <v>20.841</v>
+        <v>25.767</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.29</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4717</v>
+        <v>0.5651</v>
       </c>
       <c r="J168" t="n">
-        <v>14.151</v>
+        <v>16.953</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2841</v>
+        <v>0.3385</v>
       </c>
       <c r="J169" t="n">
-        <v>8.523</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3482</v>
+        <v>-0.2103</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.446</v>
+        <v>-6.309</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4327</v>
+        <v>-0.2707</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.981</v>
+        <v>-8.121</v>
       </c>
     </row>
     <row r="172">
@@ -8815,10 +8815,10 @@
         <v>1.91</v>
       </c>
       <c r="I172" t="n">
-        <v>1.8287</v>
+        <v>1.5562</v>
       </c>
       <c r="J172" t="n">
-        <v>32.9166</v>
+        <v>28.0116</v>
       </c>
     </row>
     <row r="173">
@@ -8855,10 +8855,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.566</v>
+        <v>1.3881</v>
       </c>
       <c r="J173" t="n">
-        <v>28.188</v>
+        <v>24.9858</v>
       </c>
     </row>
     <row r="174">
@@ -8895,10 +8895,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8359</v>
+        <v>0.9656</v>
       </c>
       <c r="J174" t="n">
-        <v>15.0462</v>
+        <v>17.3808</v>
       </c>
     </row>
     <row r="175">
@@ -8935,10 +8935,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7725</v>
+        <v>0.9063</v>
       </c>
       <c r="J175" t="n">
-        <v>13.905</v>
+        <v>16.3134</v>
       </c>
     </row>
     <row r="176">
@@ -8975,10 +8975,10 @@
         <v>1.21</v>
       </c>
       <c r="I176" t="n">
-        <v>0.4005</v>
+        <v>0.5171</v>
       </c>
       <c r="J176" t="n">
-        <v>7.209</v>
+        <v>9.3078</v>
       </c>
     </row>
     <row r="177">
@@ -9015,10 +9015,10 @@
         <v>0.9</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0181</v>
+        <v>-0.0475</v>
       </c>
       <c r="J177" t="n">
-        <v>-0.3258</v>
+        <v>-0.855</v>
       </c>
     </row>
     <row r="178">
@@ -9055,10 +9055,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2902</v>
+        <v>-0.2452</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.2236</v>
+        <v>-4.4136</v>
       </c>
     </row>
     <row r="179">
@@ -9095,10 +9095,10 @@
         <v>0.62</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4645</v>
+        <v>-0.3549</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.361000000000001</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="180">
@@ -9135,10 +9135,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8383</v>
+        <v>-0.5777</v>
       </c>
       <c r="J180" t="n">
-        <v>-15.0894</v>
+        <v>-10.3986</v>
       </c>
     </row>
     <row r="181">
@@ -9175,10 +9175,10 @@
         <v>0.33</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.902</v>
+        <v>-0.6258</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.236</v>
+        <v>-11.2644</v>
       </c>
     </row>
     <row r="182">
@@ -9215,10 +9215,10 @@
         <v>1.01</v>
       </c>
       <c r="I182" t="n">
-        <v>0.144</v>
+        <v>0.1134</v>
       </c>
       <c r="J182" t="n">
-        <v>3.456</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="183">
@@ -9255,10 +9255,10 @@
         <v>0.9</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1054</v>
+        <v>-0.1045</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.5296</v>
+        <v>-2.508</v>
       </c>
     </row>
     <row r="184">
@@ -9295,10 +9295,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2583</v>
+        <v>-0.202</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.1992</v>
+        <v>-4.848</v>
       </c>
     </row>
     <row r="185">
@@ -9335,10 +9335,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6251</v>
+        <v>-0.4184</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.0024</v>
+        <v>-10.0416</v>
       </c>
     </row>
     <row r="186">
@@ -9375,10 +9375,10 @@
         <v>0.53</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6899</v>
+        <v>-0.4649</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.5576</v>
+        <v>-11.1576</v>
       </c>
     </row>
     <row r="187">
@@ -9415,10 +9415,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3003</v>
+        <v>1.1977</v>
       </c>
       <c r="J187" t="n">
-        <v>31.2072</v>
+        <v>28.7448</v>
       </c>
     </row>
     <row r="188">
@@ -9455,10 +9455,10 @@
         <v>1.38</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9274</v>
+        <v>0.9477</v>
       </c>
       <c r="J188" t="n">
-        <v>22.2576</v>
+        <v>22.7448</v>
       </c>
     </row>
     <row r="189">
@@ -9495,10 +9495,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5401</v>
+        <v>0.6171</v>
       </c>
       <c r="J189" t="n">
-        <v>12.9624</v>
+        <v>14.8104</v>
       </c>
     </row>
     <row r="190">
@@ -9535,10 +9535,10 @@
         <v>1.14</v>
       </c>
       <c r="I190" t="n">
-        <v>0.309</v>
+        <v>0.3923</v>
       </c>
       <c r="J190" t="n">
-        <v>7.416</v>
+        <v>9.4152</v>
       </c>
     </row>
     <row r="191">
@@ -9575,10 +9575,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2282</v>
+        <v>0.3109</v>
       </c>
       <c r="J191" t="n">
-        <v>5.4768</v>
+        <v>7.4616</v>
       </c>
     </row>
     <row r="192">
@@ -9615,10 +9615,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6867</v>
+        <v>0.846</v>
       </c>
       <c r="J192" t="n">
-        <v>24.7212</v>
+        <v>30.456</v>
       </c>
     </row>
     <row r="193">
@@ -9655,10 +9655,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0156</v>
+        <v>-0.0285</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.5616</v>
+        <v>-1.026</v>
       </c>
     </row>
     <row r="194">
@@ -9695,10 +9695,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.9124</v>
+        <v>-7.524</v>
       </c>
     </row>
     <row r="195">
@@ -9735,10 +9735,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3766</v>
+        <v>-0.2391</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.5576</v>
+        <v>-8.6076</v>
       </c>
     </row>
     <row r="196">
@@ -9775,10 +9775,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6452</v>
+        <v>-0.4294</v>
       </c>
       <c r="J196" t="n">
-        <v>-23.2272</v>
+        <v>-15.4584</v>
       </c>
     </row>
     <row r="197">
@@ -9815,10 +9815,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6143</v>
+        <v>1.3997</v>
       </c>
       <c r="J197" t="n">
-        <v>58.1148</v>
+        <v>50.3892</v>
       </c>
     </row>
     <row r="198">
@@ -9855,10 +9855,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6842</v>
+        <v>0.6828</v>
       </c>
       <c r="J198" t="n">
-        <v>24.6312</v>
+        <v>24.5808</v>
       </c>
     </row>
     <row r="199">
@@ -9895,10 +9895,10 @@
         <v>1.23</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6333</v>
+        <v>0.6353</v>
       </c>
       <c r="J199" t="n">
-        <v>22.7988</v>
+        <v>22.8708</v>
       </c>
     </row>
     <row r="200">
@@ -9935,10 +9935,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2476</v>
+        <v>0.3076</v>
       </c>
       <c r="J200" t="n">
-        <v>8.913600000000001</v>
+        <v>11.0736</v>
       </c>
     </row>
     <row r="201">
@@ -9975,10 +9975,10 @@
         <v>0.61</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.14</v>
+        <v>-1.1337</v>
       </c>
       <c r="J201" t="n">
-        <v>-41.04</v>
+        <v>-40.8132</v>
       </c>
     </row>
     <row r="202">
@@ -10015,10 +10015,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1639</v>
+        <v>1.1117</v>
       </c>
       <c r="J202" t="n">
-        <v>29.0975</v>
+        <v>27.7925</v>
       </c>
     </row>
     <row r="203">
@@ -10055,10 +10055,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0394</v>
+        <v>1.034</v>
       </c>
       <c r="J203" t="n">
-        <v>25.985</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="204">
@@ -10095,10 +10095,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.9079</v>
       </c>
       <c r="J204" t="n">
-        <v>22.14</v>
+        <v>22.6975</v>
       </c>
     </row>
     <row r="205">
@@ -10135,10 +10135,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5956</v>
+        <v>0.6649</v>
       </c>
       <c r="J205" t="n">
-        <v>14.89</v>
+        <v>16.6225</v>
       </c>
     </row>
     <row r="206">
@@ -10175,10 +10175,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6021</v>
+        <v>-0.5343</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.0525</v>
+        <v>-13.3575</v>
       </c>
     </row>
     <row r="207">
@@ -10215,10 +10215,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3736</v>
+        <v>0.4164</v>
       </c>
       <c r="J207" t="n">
-        <v>9.34</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="208">
@@ -10255,10 +10255,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1932</v>
+        <v>0.1873</v>
       </c>
       <c r="J208" t="n">
-        <v>4.83</v>
+        <v>4.6825</v>
       </c>
     </row>
     <row r="209">
@@ -10295,10 +10295,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2946</v>
+        <v>-0.1873</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.365</v>
+        <v>-4.6825</v>
       </c>
     </row>
     <row r="210">
@@ -10335,10 +10335,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3577</v>
+        <v>-0.2276</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.942500000000001</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="211">
@@ -10375,10 +10375,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.3628</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.8475</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="212">
@@ -10415,10 +10415,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6932</v>
+        <v>0.6282</v>
       </c>
       <c r="J212" t="n">
-        <v>15.9436</v>
+        <v>14.4486</v>
       </c>
     </row>
     <row r="213">
@@ -10455,10 +10455,10 @@
         <v>1.44</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5855</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>13.4665</v>
+        <v>12.2774</v>
       </c>
     </row>
     <row r="214">
@@ -10495,10 +10495,10 @@
         <v>1.41</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5471</v>
+        <v>0.5021</v>
       </c>
       <c r="J214" t="n">
-        <v>12.5833</v>
+        <v>11.5483</v>
       </c>
     </row>
     <row r="215">
@@ -10535,10 +10535,10 @@
         <v>1.3</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3855</v>
+        <v>0.3842</v>
       </c>
       <c r="J215" t="n">
-        <v>8.8665</v>
+        <v>8.836600000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10575,10 +10575,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1165</v>
+        <v>0.1479</v>
       </c>
       <c r="J216" t="n">
-        <v>2.6795</v>
+        <v>3.4017</v>
       </c>
     </row>
     <row r="217">
@@ -10615,10 +10615,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2161</v>
+        <v>-0.1863</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.9703</v>
+        <v>-4.2849</v>
       </c>
     </row>
     <row r="218">
@@ -10655,10 +10655,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3614</v>
+        <v>-0.2774</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.312200000000001</v>
+        <v>-6.3802</v>
       </c>
     </row>
     <row r="219">
@@ -10695,10 +10695,10 @@
         <v>0.66</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4776</v>
+        <v>-0.3315</v>
       </c>
       <c r="J219" t="n">
-        <v>-10.9848</v>
+        <v>-7.6245</v>
       </c>
     </row>
     <row r="220">
@@ -10735,10 +10735,10 @@
         <v>0.63</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.359</v>
       </c>
       <c r="J220" t="n">
-        <v>-12.0911</v>
+        <v>-8.257</v>
       </c>
     </row>
     <row r="221">
@@ -10775,10 +10775,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5558</v>
+        <v>-0.3776</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.7834</v>
+        <v>-8.684799999999999</v>
       </c>
     </row>
     <row r="222">
@@ -10815,10 +10815,10 @@
         <v>1.83</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0168</v>
+        <v>0.9344</v>
       </c>
       <c r="J222" t="n">
-        <v>23.3864</v>
+        <v>21.4912</v>
       </c>
     </row>
     <row r="223">
@@ -10855,10 +10855,10 @@
         <v>1.62</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7978</v>
+        <v>0.7235</v>
       </c>
       <c r="J223" t="n">
-        <v>18.3494</v>
+        <v>16.6405</v>
       </c>
     </row>
     <row r="224">
@@ -10895,10 +10895,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4685</v>
+        <v>0.4396</v>
       </c>
       <c r="J224" t="n">
-        <v>10.7755</v>
+        <v>10.1108</v>
       </c>
     </row>
     <row r="225">
@@ -10935,10 +10935,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2229</v>
+        <v>0.2425</v>
       </c>
       <c r="J225" t="n">
-        <v>5.1267</v>
+        <v>5.5775</v>
       </c>
     </row>
     <row r="226">
@@ -10975,10 +10975,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5143</v>
+        <v>-0.3296</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.8289</v>
+        <v>-7.5808</v>
       </c>
     </row>
     <row r="227">
@@ -11015,10 +11015,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0434</v>
+        <v>-0.0609</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.9982</v>
+        <v>-1.4007</v>
       </c>
     </row>
     <row r="228">
@@ -11055,10 +11055,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1165</v>
+        <v>-0.1094</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.6795</v>
+        <v>-2.5162</v>
       </c>
     </row>
     <row r="229">
@@ -11095,10 +11095,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2375</v>
+        <v>-0.1852</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.4625</v>
+        <v>-4.2596</v>
       </c>
     </row>
     <row r="230">
@@ -11135,10 +11135,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3888</v>
+        <v>-0.2616</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.942399999999999</v>
+        <v>-6.0168</v>
       </c>
     </row>
     <row r="231">
@@ -11175,10 +11175,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6953</v>
+        <v>-0.4684</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.9919</v>
+        <v>-10.7732</v>
       </c>
     </row>
     <row r="232">
@@ -11215,10 +11215,10 @@
         <v>2.02</v>
       </c>
       <c r="I232" t="n">
-        <v>1.9523</v>
+        <v>1.6597</v>
       </c>
       <c r="J232" t="n">
-        <v>37.0937</v>
+        <v>31.5343</v>
       </c>
     </row>
     <row r="233">
@@ -11255,10 +11255,10 @@
         <v>1.82</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6365</v>
+        <v>1.4416</v>
       </c>
       <c r="J233" t="n">
-        <v>31.0935</v>
+        <v>27.3904</v>
       </c>
     </row>
     <row r="234">
@@ -11295,10 +11295,10 @@
         <v>1.68</v>
       </c>
       <c r="I234" t="n">
-        <v>1.374</v>
+        <v>1.2868</v>
       </c>
       <c r="J234" t="n">
-        <v>26.106</v>
+        <v>24.4492</v>
       </c>
     </row>
     <row r="235">
@@ -11335,10 +11335,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9055</v>
+        <v>1.0327</v>
       </c>
       <c r="J235" t="n">
-        <v>17.2045</v>
+        <v>19.6213</v>
       </c>
     </row>
     <row r="236">
@@ -11375,10 +11375,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.2385</v>
+        <v>0.348</v>
       </c>
       <c r="J236" t="n">
-        <v>4.5315</v>
+        <v>6.612</v>
       </c>
     </row>
     <row r="237">
@@ -11415,10 +11415,10 @@
         <v>0.7</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.3209</v>
+        <v>-0.2685</v>
       </c>
       <c r="J237" t="n">
-        <v>-6.0971</v>
+        <v>-5.1015</v>
       </c>
     </row>
     <row r="238">
@@ -11455,10 +11455,10 @@
         <v>0.63</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.4297</v>
+        <v>-0.3398</v>
       </c>
       <c r="J238" t="n">
-        <v>-8.164300000000001</v>
+        <v>-6.4562</v>
       </c>
     </row>
     <row r="239">
@@ -11495,10 +11495,10 @@
         <v>0.61</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4621</v>
+        <v>-0.3591</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.7799</v>
+        <v>-6.8229</v>
       </c>
     </row>
     <row r="240">
@@ -11535,10 +11535,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.496</v>
+        <v>-0.3778</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.423999999999999</v>
+        <v>-7.1782</v>
       </c>
     </row>
     <row r="241">
@@ -11575,10 +11575,10 @@
         <v>0.3</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.6506</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.746</v>
+        <v>-12.3614</v>
       </c>
     </row>
     <row r="242">
@@ -11615,10 +11615,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0655</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.179</v>
+        <v>-1.4706</v>
       </c>
     </row>
     <row r="243">
@@ -11655,10 +11655,10 @@
         <v>0.61</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.4564</v>
+        <v>-0.3572</v>
       </c>
       <c r="J243" t="n">
-        <v>-8.215199999999999</v>
+        <v>-6.4296</v>
       </c>
     </row>
     <row r="244">
@@ -11695,10 +11695,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.5255</v>
+        <v>-0.3944</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.459</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="245">
@@ -11735,10 +11735,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6423</v>
+        <v>-0.4474</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.5614</v>
+        <v>-8.0532</v>
       </c>
     </row>
     <row r="246">
@@ -11775,10 +11775,10 @@
         <v>0.24</v>
       </c>
       <c r="I246" t="n">
-        <v>-1.0068</v>
+        <v>-0.7083</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.1224</v>
+        <v>-12.7494</v>
       </c>
     </row>
     <row r="247">
@@ -11815,10 +11815,10 @@
         <v>2.31</v>
       </c>
       <c r="I247" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J247" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="248">
@@ -11855,10 +11855,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2899</v>
+        <v>1.2427</v>
       </c>
       <c r="J248" t="n">
-        <v>23.2182</v>
+        <v>22.3686</v>
       </c>
     </row>
     <row r="249">
@@ -11895,10 +11895,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.0062</v>
+        <v>1.0949</v>
       </c>
       <c r="J249" t="n">
-        <v>18.1116</v>
+        <v>19.7082</v>
       </c>
     </row>
     <row r="250">
@@ -11935,10 +11935,10 @@
         <v>1.38</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7431</v>
+        <v>0.8894</v>
       </c>
       <c r="J250" t="n">
-        <v>13.3758</v>
+        <v>16.0092</v>
       </c>
     </row>
     <row r="251">
@@ -11975,10 +11975,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.5548</v>
+        <v>0.6889</v>
       </c>
       <c r="J251" t="n">
-        <v>9.9864</v>
+        <v>12.4002</v>
       </c>
     </row>
     <row r="252">
@@ -12015,10 +12015,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7333</v>
+        <v>0.91</v>
       </c>
       <c r="J252" t="n">
-        <v>21.999</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="253">
@@ -12055,10 +12055,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3488</v>
+        <v>0.4038</v>
       </c>
       <c r="J253" t="n">
-        <v>10.464</v>
+        <v>12.114</v>
       </c>
     </row>
     <row r="254">
@@ -12095,10 +12095,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3339</v>
+        <v>0.3856</v>
       </c>
       <c r="J254" t="n">
-        <v>10.017</v>
+        <v>11.568</v>
       </c>
     </row>
     <row r="255">
@@ -12135,10 +12135,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2767</v>
+        <v>-0.1626</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.301</v>
+        <v>-4.878</v>
       </c>
     </row>
     <row r="256">
@@ -12175,10 +12175,10 @@
         <v>0.55</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7125</v>
+        <v>-0.48</v>
       </c>
       <c r="J256" t="n">
-        <v>-21.375</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="257">
@@ -12215,10 +12215,10 @@
         <v>1.4</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6095</v>
+        <v>0.5303</v>
       </c>
       <c r="J257" t="n">
-        <v>18.285</v>
+        <v>15.909</v>
       </c>
     </row>
     <row r="258">
@@ -12255,10 +12255,10 @@
         <v>1.25</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4154</v>
+        <v>0.3529</v>
       </c>
       <c r="J258" t="n">
-        <v>12.462</v>
+        <v>10.587</v>
       </c>
     </row>
     <row r="259">
@@ -12295,10 +12295,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.13</v>
+        <v>0.1331</v>
       </c>
       <c r="J259" t="n">
-        <v>3.9</v>
+        <v>3.993</v>
       </c>
     </row>
     <row r="260">
@@ -12335,10 +12335,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0092</v>
+        <v>0.0348</v>
       </c>
       <c r="J260" t="n">
-        <v>0.276</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="261">
@@ -12375,10 +12375,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3781</v>
+        <v>-0.2314</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.343</v>
+        <v>-6.942</v>
       </c>
     </row>
     <row r="262">
@@ -12415,10 +12415,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.5748</v>
+        <v>0.6885</v>
       </c>
       <c r="J262" t="n">
-        <v>14.37</v>
+        <v>17.2125</v>
       </c>
     </row>
     <row r="263">
@@ -12455,10 +12455,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1493</v>
+        <v>0.1361</v>
       </c>
       <c r="J263" t="n">
-        <v>3.7325</v>
+        <v>3.4025</v>
       </c>
     </row>
     <row r="264">
@@ -12495,10 +12495,10 @@
         <v>0.88</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2314</v>
+        <v>-0.147</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.785</v>
+        <v>-3.675</v>
       </c>
     </row>
     <row r="265">
@@ -12535,10 +12535,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4764</v>
+        <v>-0.3073</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.91</v>
+        <v>-7.6825</v>
       </c>
     </row>
     <row r="266">
@@ -12575,10 +12575,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.595</v>
+        <v>-0.3924</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.875</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="267">
@@ -12615,10 +12615,10 @@
         <v>1.34</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5093</v>
+        <v>0.4457</v>
       </c>
       <c r="J267" t="n">
-        <v>12.7325</v>
+        <v>11.1425</v>
       </c>
     </row>
     <row r="268">
@@ -12655,10 +12655,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3071</v>
+        <v>0.2819</v>
       </c>
       <c r="J268" t="n">
-        <v>7.6775</v>
+        <v>7.0475</v>
       </c>
     </row>
     <row r="269">
@@ -12695,10 +12695,10 @@
         <v>1.19</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2855</v>
+        <v>0.2702</v>
       </c>
       <c r="J269" t="n">
-        <v>7.1375</v>
+        <v>6.755</v>
       </c>
     </row>
     <row r="270">
@@ -12735,10 +12735,10 @@
         <v>1.18</v>
       </c>
       <c r="I270" t="n">
-        <v>0.268</v>
+        <v>0.258</v>
       </c>
       <c r="J270" t="n">
-        <v>6.7</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="271">
@@ -12775,10 +12775,10 @@
         <v>1.07</v>
       </c>
       <c r="I271" t="n">
-        <v>0.0854</v>
+        <v>0.1086</v>
       </c>
       <c r="J271" t="n">
-        <v>2.135</v>
+        <v>2.715</v>
       </c>
     </row>
     <row r="272">
@@ -12815,10 +12815,10 @@
         <v>1.28</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5022</v>
+        <v>0.5914</v>
       </c>
       <c r="J272" t="n">
-        <v>18.0792</v>
+        <v>21.2904</v>
       </c>
     </row>
     <row r="273">
@@ -12855,10 +12855,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2539</v>
+        <v>0.2731</v>
       </c>
       <c r="J273" t="n">
-        <v>9.1404</v>
+        <v>9.8316</v>
       </c>
     </row>
     <row r="274">
@@ -12895,10 +12895,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3179</v>
+        <v>-0.1955</v>
       </c>
       <c r="J274" t="n">
-        <v>-11.4444</v>
+        <v>-7.038</v>
       </c>
     </row>
     <row r="275">
@@ -12935,10 +12935,10 @@
         <v>0.83</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3332</v>
+        <v>-0.2058</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.9952</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="276">
@@ -12975,10 +12975,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3483</v>
+        <v>-0.216</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.5388</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="277">
@@ -13015,10 +13015,10 @@
         <v>1.32</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5187</v>
+        <v>0.4432</v>
       </c>
       <c r="J277" t="n">
-        <v>18.6732</v>
+        <v>15.9552</v>
       </c>
     </row>
     <row r="278">
@@ -13055,10 +13055,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5187</v>
+        <v>0.4432</v>
       </c>
       <c r="J278" t="n">
-        <v>18.6732</v>
+        <v>15.9552</v>
       </c>
     </row>
     <row r="279">
@@ -13095,10 +13095,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3689</v>
+        <v>0.3085</v>
       </c>
       <c r="J279" t="n">
-        <v>13.2804</v>
+        <v>11.106</v>
       </c>
     </row>
     <row r="280">
@@ -13135,10 +13135,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2983</v>
+        <v>-0.1762</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.7388</v>
+        <v>-6.3432</v>
       </c>
     </row>
     <row r="281">
@@ -13175,10 +13175,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.534</v>
+        <v>-0.3451</v>
       </c>
       <c r="J281" t="n">
-        <v>-19.224</v>
+        <v>-12.4236</v>
       </c>
     </row>
     <row r="282">
@@ -13215,10 +13215,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3333</v>
+        <v>0.3629</v>
       </c>
       <c r="J282" t="n">
-        <v>11.3322</v>
+        <v>12.3386</v>
       </c>
     </row>
     <row r="283">
@@ -13255,10 +13255,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0487</v>
+        <v>-0.053</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.6558</v>
+        <v>-1.802</v>
       </c>
     </row>
     <row r="284">
@@ -13295,10 +13295,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2889</v>
+        <v>-0.1856</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.8226</v>
+        <v>-6.3104</v>
       </c>
     </row>
     <row r="285">
@@ -13335,10 +13335,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3982</v>
+        <v>-0.2555</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.5388</v>
+        <v>-8.686999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13375,10 +13375,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4273</v>
+        <v>-0.275</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.5282</v>
+        <v>-9.35</v>
       </c>
     </row>
     <row r="287">
@@ -13415,10 +13415,10 @@
         <v>1.38</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5546</v>
+        <v>0.4881</v>
       </c>
       <c r="J287" t="n">
-        <v>18.8564</v>
+        <v>16.5954</v>
       </c>
     </row>
     <row r="288">
@@ -13455,10 +13455,10 @@
         <v>1.3</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4504</v>
+        <v>0.3972</v>
       </c>
       <c r="J288" t="n">
-        <v>15.3136</v>
+        <v>13.5048</v>
       </c>
     </row>
     <row r="289">
@@ -13495,10 +13495,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2599</v>
+        <v>0.2564</v>
       </c>
       <c r="J289" t="n">
-        <v>8.836600000000001</v>
+        <v>8.717599999999999</v>
       </c>
     </row>
     <row r="290">
@@ -13535,10 +13535,10 @@
         <v>1.16</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2282</v>
+        <v>0.2312</v>
       </c>
       <c r="J290" t="n">
-        <v>7.7588</v>
+        <v>7.8608</v>
       </c>
     </row>
     <row r="291">
@@ -13575,10 +13575,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0447</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>1.5198</v>
+        <v>2.5466</v>
       </c>
     </row>
     <row r="292">
@@ -13615,10 +13615,10 @@
         <v>0.88</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1277</v>
+        <v>-0.1218</v>
       </c>
       <c r="J292" t="n">
-        <v>-2.4263</v>
+        <v>-2.3142</v>
       </c>
     </row>
     <row r="293">
@@ -13655,10 +13655,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2441</v>
+        <v>-0.1977</v>
       </c>
       <c r="J293" t="n">
-        <v>-4.6379</v>
+        <v>-3.7563</v>
       </c>
     </row>
     <row r="294">
@@ -13695,10 +13695,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2606</v>
+        <v>-0.2079</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.9514</v>
+        <v>-3.9501</v>
       </c>
     </row>
     <row r="295">
@@ -13735,10 +13735,10 @@
         <v>0.66</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5051</v>
+        <v>-0.3395</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.5969</v>
+        <v>-6.4505</v>
       </c>
     </row>
     <row r="296">
@@ -13775,10 +13775,10 @@
         <v>0.55</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6575</v>
+        <v>-0.4424</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.4925</v>
+        <v>-8.4056</v>
       </c>
     </row>
     <row r="297">
@@ -13815,10 +13815,10 @@
         <v>1.65</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8217</v>
+        <v>0.7484</v>
       </c>
       <c r="J297" t="n">
-        <v>15.6123</v>
+        <v>14.2196</v>
       </c>
     </row>
     <row r="298">
@@ -13855,10 +13855,10 @@
         <v>1.6</v>
       </c>
       <c r="I298" t="n">
-        <v>0.767</v>
+        <v>0.6975</v>
       </c>
       <c r="J298" t="n">
-        <v>14.573</v>
+        <v>13.2525</v>
       </c>
     </row>
     <row r="299">
@@ -13895,10 +13895,10 @@
         <v>1.41</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5397</v>
+        <v>0.5003</v>
       </c>
       <c r="J299" t="n">
-        <v>10.2543</v>
+        <v>9.505699999999999</v>
       </c>
     </row>
     <row r="300">
@@ -13935,10 +13935,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2438</v>
+        <v>0.2639</v>
       </c>
       <c r="J300" t="n">
-        <v>4.6322</v>
+        <v>5.0141</v>
       </c>
     </row>
     <row r="301">
@@ -13975,10 +13975,10 @@
         <v>1.03</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.024</v>
+        <v>0.0215</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.456</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="302">
@@ -14015,10 +14015,10 @@
         <v>1.26</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4824</v>
+        <v>0.5638</v>
       </c>
       <c r="J302" t="n">
-        <v>13.0248</v>
+        <v>15.2226</v>
       </c>
     </row>
     <row r="303">
@@ -14055,10 +14055,10 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0281</v>
+        <v>0.007</v>
       </c>
       <c r="J303" t="n">
-        <v>0.7587</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="304">
@@ -14095,10 +14095,10 @@
         <v>0.92</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1752</v>
+        <v>-0.1071</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.7304</v>
+        <v>-2.8917</v>
       </c>
     </row>
     <row r="305">
@@ -14135,10 +14135,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3578</v>
+        <v>-0.2237</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.660600000000001</v>
+        <v>-6.0399</v>
       </c>
     </row>
     <row r="306">
@@ -14175,10 +14175,10 @@
         <v>0.79</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3872</v>
+        <v>-0.2438</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.4544</v>
+        <v>-6.5826</v>
       </c>
     </row>
     <row r="307">
@@ -14215,10 +14215,10 @@
         <v>1.6</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8323</v>
+        <v>0.7478</v>
       </c>
       <c r="J307" t="n">
-        <v>22.4721</v>
+        <v>20.1906</v>
       </c>
     </row>
     <row r="308">
@@ -14255,10 +14255,10 @@
         <v>1.27</v>
       </c>
       <c r="I308" t="n">
-        <v>0.435</v>
+        <v>0.3731</v>
       </c>
       <c r="J308" t="n">
-        <v>11.745</v>
+        <v>10.0737</v>
       </c>
     </row>
     <row r="309">
@@ -14295,10 +14295,10 @@
         <v>1.02</v>
       </c>
       <c r="I309" t="n">
-        <v>0.0022</v>
+        <v>0.0317</v>
       </c>
       <c r="J309" t="n">
-        <v>0.0594</v>
+        <v>0.8559</v>
       </c>
     </row>
     <row r="310">
@@ -14335,10 +14335,10 @@
         <v>0.91</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.246</v>
+        <v>-0.1379</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.642</v>
+        <v>-3.7233</v>
       </c>
     </row>
     <row r="311">
@@ -14375,10 +14375,10 @@
         <v>0.89</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2782</v>
+        <v>-0.1602</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.5114</v>
+        <v>-4.3254</v>
       </c>
     </row>
     <row r="312">
@@ -14415,10 +14415,10 @@
         <v>1.5</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2342</v>
+        <v>1.1475</v>
       </c>
       <c r="J312" t="n">
-        <v>33.3234</v>
+        <v>30.9825</v>
       </c>
     </row>
     <row r="313">
@@ -14455,10 +14455,10 @@
         <v>1.2</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5541</v>
+        <v>0.5638</v>
       </c>
       <c r="J313" t="n">
-        <v>14.9607</v>
+        <v>15.2226</v>
       </c>
     </row>
     <row r="314">
@@ -14495,10 +14495,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4938</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>13.3326</v>
+        <v>13.9212</v>
       </c>
     </row>
     <row r="315">
@@ -14535,10 +14535,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4243</v>
+        <v>0.4671</v>
       </c>
       <c r="J315" t="n">
-        <v>11.4561</v>
+        <v>12.6117</v>
       </c>
     </row>
     <row r="316">
@@ -14575,10 +14575,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6264</v>
+        <v>-0.5641</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.9128</v>
+        <v>-15.2307</v>
       </c>
     </row>
     <row r="317">
@@ -14615,10 +14615,10 @@
         <v>1.38</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6207</v>
+        <v>0.7533</v>
       </c>
       <c r="J317" t="n">
-        <v>16.7589</v>
+        <v>20.3391</v>
       </c>
     </row>
     <row r="318">
@@ -14655,10 +14655,10 @@
         <v>1.1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2271</v>
+        <v>0.2459</v>
       </c>
       <c r="J318" t="n">
-        <v>6.1317</v>
+        <v>6.6393</v>
       </c>
     </row>
     <row r="319">
@@ -14695,10 +14695,10 @@
         <v>0.98</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.8657</v>
+        <v>-0.9747</v>
       </c>
     </row>
     <row r="320">
@@ -14735,10 +14735,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2454</v>
+        <v>-0.1455</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.6258</v>
+        <v>-3.9285</v>
       </c>
     </row>
     <row r="321">
@@ -14775,10 +14775,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5719</v>
+        <v>-0.3741</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.4413</v>
+        <v>-10.1007</v>
       </c>
     </row>
     <row r="322">
@@ -14815,10 +14815,10 @@
         <v>1.2</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4165</v>
+        <v>0.4733</v>
       </c>
       <c r="J322" t="n">
-        <v>12.495</v>
+        <v>14.199</v>
       </c>
     </row>
     <row r="323">
@@ -14855,10 +14855,10 @@
         <v>1.15</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3427</v>
+        <v>0.3763</v>
       </c>
       <c r="J323" t="n">
-        <v>10.281</v>
+        <v>11.289</v>
       </c>
     </row>
     <row r="324">
@@ -14895,10 +14895,10 @@
         <v>0.87</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2445</v>
+        <v>-0.1565</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.335</v>
+        <v>-4.695</v>
       </c>
     </row>
     <row r="325">
@@ -14935,10 +14935,10 @@
         <v>0.79</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3735</v>
+        <v>-0.2378</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.205</v>
+        <v>-7.134</v>
       </c>
     </row>
     <row r="326">
@@ -14975,10 +14975,10 @@
         <v>0.53</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7166</v>
+        <v>-0.4831</v>
       </c>
       <c r="J326" t="n">
-        <v>-21.498</v>
+        <v>-14.493</v>
       </c>
     </row>
     <row r="327">
@@ -15015,10 +15015,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9559</v>
+        <v>0.9528</v>
       </c>
       <c r="J327" t="n">
-        <v>28.677</v>
+        <v>28.584</v>
       </c>
     </row>
     <row r="328">
@@ -15055,10 +15055,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8894</v>
+        <v>0.888</v>
       </c>
       <c r="J328" t="n">
-        <v>26.682</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="329">
@@ -15095,10 +15095,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.726</v>
+        <v>0.7267</v>
       </c>
       <c r="J329" t="n">
-        <v>21.78</v>
+        <v>21.801</v>
       </c>
     </row>
     <row r="330">
@@ -15135,10 +15135,10 @@
         <v>1.23</v>
       </c>
       <c r="I330" t="n">
-        <v>0.6249</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J330" t="n">
-        <v>18.747</v>
+        <v>18.978</v>
       </c>
     </row>
     <row r="331">
@@ -15175,10 +15175,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.8243</v>
       </c>
       <c r="J331" t="n">
-        <v>-25.962</v>
+        <v>-24.729</v>
       </c>
     </row>
     <row r="332">
@@ -15215,10 +15215,10 @@
         <v>0.95</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0209</v>
+        <v>-0.0209</v>
       </c>
       <c r="J332" t="n">
-        <v>0.4389</v>
+        <v>-0.4389</v>
       </c>
     </row>
     <row r="333">
@@ -15255,10 +15255,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2672</v>
+        <v>-0.2191</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.6112</v>
+        <v>-4.6011</v>
       </c>
     </row>
     <row r="334">
@@ -15295,10 +15295,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.4263</v>
+        <v>-0.3054</v>
       </c>
       <c r="J334" t="n">
-        <v>-8.952299999999999</v>
+        <v>-6.4134</v>
       </c>
     </row>
     <row r="335">
@@ -15335,10 +15335,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.5437</v>
+        <v>-0.3693</v>
       </c>
       <c r="J335" t="n">
-        <v>-11.4177</v>
+        <v>-7.7553</v>
       </c>
     </row>
     <row r="336">
@@ -15375,10 +15375,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8115</v>
+        <v>-0.5563</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.0415</v>
+        <v>-11.6823</v>
       </c>
     </row>
     <row r="337">
@@ -15415,10 +15415,10 @@
         <v>1.7</v>
       </c>
       <c r="I337" t="n">
-        <v>0.866</v>
+        <v>0.7929</v>
       </c>
       <c r="J337" t="n">
-        <v>18.186</v>
+        <v>16.6509</v>
       </c>
     </row>
     <row r="338">
@@ -15455,10 +15455,10 @@
         <v>1.58</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7352</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J338" t="n">
-        <v>15.4392</v>
+        <v>14.1099</v>
       </c>
     </row>
     <row r="339">
@@ -15495,10 +15495,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4621</v>
+        <v>0.4561</v>
       </c>
       <c r="J339" t="n">
-        <v>9.7041</v>
+        <v>9.578099999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15535,10 +15535,10 @@
         <v>1.25</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3042</v>
+        <v>0.3207</v>
       </c>
       <c r="J340" t="n">
-        <v>6.3882</v>
+        <v>6.7347</v>
       </c>
     </row>
     <row r="341">
@@ -15575,10 +15575,10 @@
         <v>1.17</v>
       </c>
       <c r="I341" t="n">
-        <v>0.195</v>
+        <v>0.2221</v>
       </c>
       <c r="J341" t="n">
-        <v>4.095</v>
+        <v>4.6641</v>
       </c>
     </row>
     <row r="342">
@@ -15615,10 +15615,10 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3388</v>
+        <v>0.3767</v>
       </c>
       <c r="J342" t="n">
-        <v>8.470000000000001</v>
+        <v>9.4175</v>
       </c>
     </row>
     <row r="343">
@@ -15655,10 +15655,10 @@
         <v>1.05</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1524</v>
+        <v>0.1484</v>
       </c>
       <c r="J343" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="344">
@@ -15695,10 +15695,10 @@
         <v>0.98</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0367</v>
+        <v>-0.0332</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.9175</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="345">
@@ -15735,10 +15735,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1152</v>
+        <v>-0.0723</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.88</v>
+        <v>-1.8075</v>
       </c>
     </row>
     <row r="346">
@@ -15775,10 +15775,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5646</v>
+        <v>-0.3693</v>
       </c>
       <c r="J346" t="n">
-        <v>-14.115</v>
+        <v>-9.2325</v>
       </c>
     </row>
     <row r="347">
@@ -15815,10 +15815,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.664</v>
+        <v>0.5831</v>
       </c>
       <c r="J347" t="n">
-        <v>16.6</v>
+        <v>14.5775</v>
       </c>
     </row>
     <row r="348">
@@ -15855,10 +15855,10 @@
         <v>1.24</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3953</v>
+        <v>0.3378</v>
       </c>
       <c r="J348" t="n">
-        <v>9.8825</v>
+        <v>8.445</v>
       </c>
     </row>
     <row r="349">
@@ -15895,10 +15895,10 @@
         <v>1.21</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3518</v>
+        <v>0.301</v>
       </c>
       <c r="J349" t="n">
-        <v>8.795</v>
+        <v>7.525</v>
       </c>
     </row>
     <row r="350">
@@ -15935,10 +15935,10 @@
         <v>1.06</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0858</v>
+        <v>0.1009</v>
       </c>
       <c r="J350" t="n">
-        <v>2.145</v>
+        <v>2.5225</v>
       </c>
     </row>
     <row r="351">
@@ -15975,10 +15975,10 @@
         <v>0.7</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5407</v>
+        <v>-0.3498</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.5175</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="352">
@@ -16015,10 +16015,10 @@
         <v>1.15</v>
       </c>
       <c r="I352" t="n">
-        <v>0.2753</v>
+        <v>0.2304</v>
       </c>
       <c r="J352" t="n">
-        <v>7.4331</v>
+        <v>6.2208</v>
       </c>
     </row>
     <row r="353">
@@ -16055,10 +16055,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2067</v>
+        <v>0.1768</v>
       </c>
       <c r="J353" t="n">
-        <v>5.5809</v>
+        <v>4.7736</v>
       </c>
     </row>
     <row r="354">
@@ -16095,10 +16095,10 @@
         <v>1.1</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1876</v>
+        <v>0.1631</v>
       </c>
       <c r="J354" t="n">
-        <v>5.0652</v>
+        <v>4.4037</v>
       </c>
     </row>
     <row r="355">
@@ -16135,10 +16135,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="J355" t="n">
-        <v>2.2059</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="356">
@@ -16175,10 +16175,10 @@
         <v>1.04</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0611</v>
+        <v>0.0736</v>
       </c>
       <c r="J356" t="n">
-        <v>1.6497</v>
+        <v>1.9872</v>
       </c>
     </row>
     <row r="357">
@@ -16215,10 +16215,10 @@
         <v>1.4</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6231</v>
+        <v>0.7597</v>
       </c>
       <c r="J357" t="n">
-        <v>16.8237</v>
+        <v>20.5119</v>
       </c>
     </row>
     <row r="358">
@@ -16255,10 +16255,10 @@
         <v>1.14</v>
       </c>
       <c r="I358" t="n">
-        <v>0.2671</v>
+        <v>0.3088</v>
       </c>
       <c r="J358" t="n">
-        <v>7.2117</v>
+        <v>8.3376</v>
       </c>
     </row>
     <row r="359">
@@ -16295,10 +16295,10 @@
         <v>1.06</v>
       </c>
       <c r="I359" t="n">
-        <v>0.1124</v>
+        <v>0.1511</v>
       </c>
       <c r="J359" t="n">
-        <v>3.0348</v>
+        <v>4.0797</v>
       </c>
     </row>
     <row r="360">
@@ -16335,10 +16335,10 @@
         <v>1.04</v>
       </c>
       <c r="I360" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.1065</v>
       </c>
       <c r="J360" t="n">
-        <v>1.8765</v>
+        <v>2.8755</v>
       </c>
     </row>
     <row r="361">
@@ -16375,10 +16375,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5191</v>
+        <v>-0.3343</v>
       </c>
       <c r="J361" t="n">
-        <v>-14.0157</v>
+        <v>-9.0261</v>
       </c>
     </row>
     <row r="362">
@@ -16415,10 +16415,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>0.679</v>
+        <v>0.6045</v>
       </c>
       <c r="J362" t="n">
-        <v>14.938</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="363">
@@ -16455,10 +16455,10 @@
         <v>1.34</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4946</v>
+        <v>0.439</v>
       </c>
       <c r="J363" t="n">
-        <v>10.8812</v>
+        <v>9.657999999999999</v>
       </c>
     </row>
     <row r="364">
@@ -16495,10 +16495,10 @@
         <v>1.24</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3453</v>
+        <v>0.3255</v>
       </c>
       <c r="J364" t="n">
-        <v>7.5966</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="365">
@@ -16535,10 +16535,10 @@
         <v>1.23</v>
       </c>
       <c r="I365" t="n">
-        <v>0.3276</v>
+        <v>0.3141</v>
       </c>
       <c r="J365" t="n">
-        <v>7.2072</v>
+        <v>6.9102</v>
       </c>
     </row>
     <row r="366">
@@ -16575,10 +16575,10 @@
         <v>0.91</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2646</v>
+        <v>-0.148</v>
       </c>
       <c r="J366" t="n">
-        <v>-5.8212</v>
+        <v>-3.256</v>
       </c>
     </row>
     <row r="367">
@@ -16615,10 +16615,10 @@
         <v>1.1</v>
       </c>
       <c r="I367" t="n">
-        <v>0.2943</v>
+        <v>0.3079</v>
       </c>
       <c r="J367" t="n">
-        <v>6.4746</v>
+        <v>6.7738</v>
       </c>
     </row>
     <row r="368">
@@ -16655,10 +16655,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0205</v>
+        <v>-0.0424</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.451</v>
+        <v>-0.9328</v>
       </c>
     </row>
     <row r="369">
@@ -16695,10 +16695,10 @@
         <v>0.71</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.4649</v>
+        <v>-0.3049</v>
       </c>
       <c r="J369" t="n">
-        <v>-10.2278</v>
+        <v>-6.7078</v>
       </c>
     </row>
     <row r="370">
@@ -16735,10 +16735,10 @@
         <v>0.7</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4792</v>
+        <v>-0.3145</v>
       </c>
       <c r="J370" t="n">
-        <v>-10.5424</v>
+        <v>-6.919</v>
       </c>
     </row>
     <row r="371">
@@ -16775,10 +16775,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5212</v>
+        <v>-0.343</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.4664</v>
+        <v>-7.546</v>
       </c>
     </row>
     <row r="372">
@@ -16815,10 +16815,10 @@
         <v>1.38</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5987</v>
+        <v>0.7268</v>
       </c>
       <c r="J372" t="n">
-        <v>17.961</v>
+        <v>21.804</v>
       </c>
     </row>
     <row r="373">
@@ -16855,10 +16855,10 @@
         <v>1.22</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3881</v>
+        <v>0.4545</v>
       </c>
       <c r="J373" t="n">
-        <v>11.643</v>
+        <v>13.635</v>
       </c>
     </row>
     <row r="374">
@@ -16895,10 +16895,10 @@
         <v>0.98</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.096</v>
+        <v>-0.0426</v>
       </c>
       <c r="J374" t="n">
-        <v>-2.88</v>
+        <v>-1.278</v>
       </c>
     </row>
     <row r="375">
@@ -16935,10 +16935,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1777</v>
+        <v>-0.0955</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.331</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="376">
@@ -16975,10 +16975,10 @@
         <v>0.83</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3554</v>
+        <v>-0.2165</v>
       </c>
       <c r="J376" t="n">
-        <v>-10.662</v>
+        <v>-6.495</v>
       </c>
     </row>
     <row r="377">
@@ -17015,10 +17015,10 @@
         <v>1.33</v>
       </c>
       <c r="I377" t="n">
-        <v>0.9348</v>
+        <v>0.9127</v>
       </c>
       <c r="J377" t="n">
-        <v>28.044</v>
+        <v>27.381</v>
       </c>
     </row>
     <row r="378">
@@ -17055,10 +17055,10 @@
         <v>1.3</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8673</v>
+        <v>0.8414</v>
       </c>
       <c r="J378" t="n">
-        <v>26.019</v>
+        <v>25.242</v>
       </c>
     </row>
     <row r="379">
@@ -17095,10 +17095,10 @@
         <v>1.08</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2824</v>
+        <v>0.2727</v>
       </c>
       <c r="J379" t="n">
-        <v>8.472</v>
+        <v>8.180999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -17135,10 +17135,10 @@
         <v>0.95</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2745</v>
+        <v>-0.215</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.234999999999999</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="381">
@@ -17175,10 +17175,10 @@
         <v>0.67</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="J381" t="n">
-        <v>-29.712</v>
+        <v>-28.956</v>
       </c>
     </row>
     <row r="382">
@@ -17215,10 +17215,10 @@
         <v>1.53</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2907</v>
+        <v>1.1845</v>
       </c>
       <c r="J382" t="n">
-        <v>30.9768</v>
+        <v>28.428</v>
       </c>
     </row>
     <row r="383">
@@ -17255,10 +17255,10 @@
         <v>1.29</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7788</v>
+        <v>0.7755</v>
       </c>
       <c r="J383" t="n">
-        <v>18.6912</v>
+        <v>18.612</v>
       </c>
     </row>
     <row r="384">
@@ -17295,10 +17295,10 @@
         <v>1.24</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6563</v>
+        <v>0.6581</v>
       </c>
       <c r="J384" t="n">
-        <v>15.7512</v>
+        <v>15.7944</v>
       </c>
     </row>
     <row r="385">
@@ -17335,10 +17335,10 @@
         <v>1.03</v>
       </c>
       <c r="I385" t="n">
-        <v>0.0223</v>
+        <v>0.089</v>
       </c>
       <c r="J385" t="n">
-        <v>0.5352</v>
+        <v>2.136</v>
       </c>
     </row>
     <row r="386">
@@ -17375,10 +17375,10 @@
         <v>0.82</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6774</v>
+        <v>-0.6187</v>
       </c>
       <c r="J386" t="n">
-        <v>-16.2576</v>
+        <v>-14.8488</v>
       </c>
     </row>
     <row r="387">
@@ -17415,10 +17415,10 @@
         <v>1.1</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2599</v>
+        <v>0.2715</v>
       </c>
       <c r="J387" t="n">
-        <v>6.2376</v>
+        <v>6.516</v>
       </c>
     </row>
     <row r="388">
@@ -17455,10 +17455,10 @@
         <v>1.06</v>
       </c>
       <c r="I388" t="n">
-        <v>0.1892</v>
+        <v>0.184</v>
       </c>
       <c r="J388" t="n">
-        <v>4.5408</v>
+        <v>4.416</v>
       </c>
     </row>
     <row r="389">
@@ -17495,10 +17495,10 @@
         <v>0.95</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.0815</v>
+        <v>-0.0688</v>
       </c>
       <c r="J389" t="n">
-        <v>-1.956</v>
+        <v>-1.6512</v>
       </c>
     </row>
     <row r="390">
@@ -17535,10 +17535,10 @@
         <v>0.86</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2654</v>
+        <v>-0.1678</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.3696</v>
+        <v>-4.0272</v>
       </c>
     </row>
     <row r="391">
@@ -17575,10 +17575,10 @@
         <v>0.61</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.6199</v>
+        <v>-0.4107</v>
       </c>
       <c r="J391" t="n">
-        <v>-14.8776</v>
+        <v>-9.8568</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4998/event_4998_evp_summary.xlsx
+++ b/database/event/4998/event_4998_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.797499999999999</v>
+        <v>9.117800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2183</v>
+        <v>1.2627</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3336</v>
+        <v>3.5264</v>
       </c>
       <c r="E2" t="n">
-        <v>8.797499999999999</v>
+        <v>9.117800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3457</v>
+        <v>4.5371</v>
       </c>
       <c r="H2" t="n">
-        <v>17.133</v>
+        <v>16.3562</v>
       </c>
       <c r="I2" t="n">
-        <v>8.9084</v>
+        <v>8.8322</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3457</v>
+        <v>4.5371</v>
       </c>
       <c r="K2" t="n">
         <v>237</v>
@@ -529,7 +529,7 @@
         <v>181</v>
       </c>
       <c r="M2" t="n">
-        <v>13.2541</v>
+        <v>13.3693</v>
       </c>
       <c r="N2" t="n">
         <v>418</v>
@@ -538,139 +538,139 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6695</v>
+        <v>6.8593</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9236</v>
+        <v>0.9499</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3729</v>
+        <v>2.4983</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6695</v>
+        <v>6.8593</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8142</v>
+        <v>4.5807</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8554</v>
+        <v>2.2786</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9524</v>
+        <v>10.8659</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1349</v>
+        <v>5.8675</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8554</v>
+        <v>2.2786</v>
       </c>
       <c r="K3" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L3" t="n">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9903</v>
+        <v>8.146100000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>409</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6392</v>
+        <v>6.8472</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9194</v>
+        <v>0.9482</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3593</v>
+        <v>2.4928</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6392</v>
+        <v>6.8472</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1874</v>
+        <v>2.2665</v>
       </c>
       <c r="H4" t="n">
-        <v>11.371</v>
+        <v>10.6474</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9124</v>
+        <v>5.7495</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1874</v>
+        <v>2.2665</v>
       </c>
       <c r="K4" t="n">
         <v>237</v>
       </c>
       <c r="L4" t="n">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0998</v>
+        <v>8.016</v>
       </c>
       <c r="N4" t="n">
-        <v>363</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6289</v>
+        <v>6.7756</v>
       </c>
       <c r="C5" t="n">
-        <v>0.918</v>
+        <v>0.9383</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3546</v>
+        <v>2.4602</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6289</v>
+        <v>6.7756</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4518</v>
+        <v>3.7045</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1771</v>
+        <v>3.071</v>
       </c>
       <c r="H5" t="n">
-        <v>11.2185</v>
+        <v>7.3284</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8331</v>
+        <v>3.9573</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1771</v>
+        <v>3.071</v>
       </c>
       <c r="K5" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L5" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M5" t="n">
-        <v>8.010199999999999</v>
+        <v>7.0283</v>
       </c>
       <c r="N5" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.5571</v>
+        <v>6.5756</v>
       </c>
       <c r="C6" t="n">
-        <v>0.908</v>
+        <v>0.9106</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3222</v>
+        <v>2.3691</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5571</v>
+        <v>6.5756</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3873</v>
+        <v>4.3089</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1698</v>
+        <v>2.2667</v>
       </c>
       <c r="H6" t="n">
-        <v>9.9716</v>
+        <v>9.3224</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1848</v>
+        <v>5.034</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1698</v>
+        <v>2.2667</v>
       </c>
       <c r="K6" t="n">
         <v>232</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>7.3546</v>
+        <v>7.3007</v>
       </c>
       <c r="N6" t="n">
         <v>392</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7365</v>
+        <v>5.9696</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7944</v>
+        <v>0.8267</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9517</v>
+        <v>2.0933</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7365</v>
+        <v>5.9696</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4518</v>
+        <v>4.5173</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2847</v>
+        <v>1.4523</v>
       </c>
       <c r="H7" t="n">
-        <v>10.5523</v>
+        <v>10.0102</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4867</v>
+        <v>5.4054</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2847</v>
+        <v>1.4523</v>
       </c>
       <c r="K7" t="n">
         <v>237</v>
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>6.7714</v>
+        <v>6.8577</v>
       </c>
       <c r="N7" t="n">
         <v>399</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2397</v>
+        <v>5.3142</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7256</v>
+        <v>0.7359</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7274</v>
+        <v>1.7949</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2397</v>
+        <v>5.3142</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3756</v>
+        <v>3.3399</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8641</v>
+        <v>1.9743</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4073</v>
+        <v>6.1255</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3315</v>
+        <v>3.3077</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8641</v>
+        <v>1.9743</v>
       </c>
       <c r="K8" t="n">
         <v>237</v>
@@ -805,7 +805,7 @@
         <v>179</v>
       </c>
       <c r="M8" t="n">
-        <v>5.195600000000001</v>
+        <v>5.282</v>
       </c>
       <c r="N8" t="n">
         <v>416</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9843</v>
+        <v>3.9363</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5518</v>
+        <v>0.5451</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1607</v>
+        <v>1.1677</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9843</v>
+        <v>3.9363</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0089</v>
+        <v>3.9731</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0246</v>
+        <v>-0.0368</v>
       </c>
       <c r="H9" t="n">
-        <v>8.638500000000001</v>
+        <v>8.214600000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4916</v>
+        <v>4.4358</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0246</v>
+        <v>-0.0368</v>
       </c>
       <c r="K9" t="n">
         <v>277</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>4.467</v>
+        <v>4.399</v>
       </c>
       <c r="N9" t="n">
         <v>354</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.855</v>
+        <v>3.7453</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5339</v>
+        <v>0.5187</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1023</v>
+        <v>1.0807</v>
       </c>
       <c r="E10" t="n">
-        <v>3.855</v>
+        <v>3.7453</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2776</v>
+        <v>3.1617</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5774</v>
+        <v>0.5836</v>
       </c>
       <c r="H10" t="n">
-        <v>6.0621</v>
+        <v>5.5373</v>
       </c>
       <c r="I10" t="n">
-        <v>3.152</v>
+        <v>2.9901</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5774</v>
+        <v>0.5836</v>
       </c>
       <c r="K10" t="n">
         <v>277</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7294</v>
+        <v>3.5737</v>
       </c>
       <c r="N10" t="n">
         <v>354</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2775</v>
+        <v>3.2586</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4539</v>
+        <v>0.4513</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8416</v>
+        <v>0.8592</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2775</v>
+        <v>3.2586</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5216</v>
+        <v>3.4783</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2441</v>
+        <v>-0.2197</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9216</v>
+        <v>6.582</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5989</v>
+        <v>3.5542</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2441</v>
+        <v>-0.2197</v>
       </c>
       <c r="K11" t="n">
         <v>277</v>
@@ -943,7 +943,7 @@
         <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3548</v>
+        <v>3.3345</v>
       </c>
       <c r="N11" t="n">
         <v>354</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8202</v>
+        <v>2.5359</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3905</v>
+        <v>0.3512</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6352</v>
+        <v>0.5302</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8202</v>
+        <v>2.5359</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8202</v>
+        <v>2.5359</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.833</v>
+        <v>2.8254</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1971</v>
+        <v>3.0495</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1971</v>
+        <v>3.0495</v>
       </c>
       <c r="N12" t="n">
         <v>263</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.605</v>
+        <v>1.5342</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2223</v>
+        <v>0.2125</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0866</v>
+        <v>0.0742</v>
       </c>
       <c r="E13" t="n">
-        <v>1.605</v>
+        <v>1.5342</v>
       </c>
       <c r="F13" t="n">
-        <v>1.605</v>
+        <v>1.5342</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.605</v>
+        <v>1.5342</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8113</v>
+        <v>1.6559</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8113</v>
+        <v>1.6559</v>
       </c>
       <c r="N13" t="n">
         <v>247</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5211</v>
+        <v>1.4399</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2106</v>
+        <v>0.1994</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0487</v>
+        <v>0.0313</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5211</v>
+        <v>1.4399</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5211</v>
+        <v>1.4399</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5211</v>
+        <v>1.4399</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7166</v>
+        <v>1.5541</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7166</v>
+        <v>1.5541</v>
       </c>
       <c r="N14" t="n">
         <v>263</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4574</v>
+        <v>1.4089</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2018</v>
+        <v>0.1951</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0199</v>
+        <v>0.0172</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4574</v>
+        <v>1.4089</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4574</v>
+        <v>1.1396</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2693</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4574</v>
+        <v>1.1396</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6447</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2693</v>
       </c>
       <c r="K15" t="n">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6447</v>
+        <v>0.8846999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>263</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4237</v>
+        <v>1.4036</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1972</v>
+        <v>0.1944</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0047</v>
+        <v>0.0147</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4237</v>
+        <v>1.4036</v>
       </c>
       <c r="F16" t="n">
-        <v>1.287</v>
+        <v>1.4036</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1367</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.287</v>
+        <v>1.4036</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6692</v>
+        <v>1.5149</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1367</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="L16" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8059000000000001</v>
+        <v>1.5149</v>
       </c>
       <c r="N16" t="n">
-        <v>392</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4148</v>
+        <v>1.334</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1959</v>
+        <v>0.1847</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0007</v>
+        <v>-0.0169</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4148</v>
+        <v>1.334</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3167</v>
+        <v>1.2037</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1303</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3167</v>
+        <v>1.2037</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6846</v>
+        <v>0.65</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1303</v>
       </c>
       <c r="K17" t="n">
         <v>256</v>
@@ -1219,7 +1219,7 @@
         <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7827</v>
+        <v>0.7803</v>
       </c>
       <c r="N17" t="n">
         <v>335</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2856</v>
+        <v>1.2319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.178</v>
+        <v>0.1706</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0576</v>
+        <v>-0.0634</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2856</v>
+        <v>1.2319</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2856</v>
+        <v>1.2319</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2856</v>
+        <v>1.2319</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4508</v>
+        <v>1.3296</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4508</v>
+        <v>1.3296</v>
       </c>
       <c r="N18" t="n">
         <v>263</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1905</v>
+        <v>1.1382</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1649</v>
+        <v>0.1576</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1006</v>
+        <v>-0.1061</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1905</v>
+        <v>1.1382</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1905</v>
+        <v>2.1382</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2315</v>
+        <v>2.1604</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1603</v>
+        <v>1.1666</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1603000000000001</v>
+        <v>0.1666000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>354</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6121</v>
+        <v>0.5802</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0848</v>
+        <v>0.0803</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3617</v>
+        <v>-0.3601</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6121</v>
+        <v>0.5802</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1687</v>
+        <v>0.0794</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4434</v>
+        <v>0.5008</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1687</v>
+        <v>0.0794</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0877</v>
+        <v>0.0429</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4434</v>
+        <v>0.5008</v>
       </c>
       <c r="K20" t="n">
         <v>256</v>
@@ -1357,7 +1357,7 @@
         <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5311</v>
+        <v>0.5437000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>335</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5151</v>
+        <v>0.488</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0713</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4055</v>
+        <v>-0.4021</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5151</v>
+        <v>0.488</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5151</v>
+        <v>0.488</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5151</v>
+        <v>0.488</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5813</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5813</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>247</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4728</v>
+        <v>0.4524</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0655</v>
+        <v>0.0626</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4246</v>
+        <v>-0.4183</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4728</v>
+        <v>0.4524</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4728</v>
+        <v>0.4524</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4728</v>
+        <v>0.4524</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5336</v>
+        <v>0.4883</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5336</v>
+        <v>0.4883</v>
       </c>
       <c r="N22" t="n">
         <v>247</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3654</v>
+        <v>0.3407</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0506</v>
+        <v>0.0472</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4731</v>
+        <v>-0.4691</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3654</v>
+        <v>0.3407</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3654</v>
+        <v>0.3407</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3654</v>
+        <v>0.3407</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4124</v>
+        <v>0.3677</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4124</v>
+        <v>0.3677</v>
       </c>
       <c r="N23" t="n">
         <v>247</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2912</v>
+        <v>0.1638</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0403</v>
+        <v>0.0227</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5496</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2912</v>
+        <v>0.1638</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5002</v>
+        <v>0.3896</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.209</v>
+        <v>-0.2258</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5002</v>
+        <v>0.3896</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2601</v>
+        <v>0.2104</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.209</v>
+        <v>-0.2258</v>
       </c>
       <c r="K24" t="n">
         <v>256</v>
@@ -1541,7 +1541,7 @@
         <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>0.05110000000000001</v>
+        <v>-0.0154</v>
       </c>
       <c r="N24" t="n">
         <v>335</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1831</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0134</v>
+        <v>-0.0254</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6816</v>
+        <v>-0.7076</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1831</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1831</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1831</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.109</v>
+        <v>-0.1976</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.109</v>
+        <v>-0.1976</v>
       </c>
       <c r="N25" t="n">
         <v>247</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vegi</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3311</v>
+        <v>-0.1946</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0459</v>
+        <v>-0.0269</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7875</v>
+        <v>-0.7128</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3311</v>
+        <v>-0.1946</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9407</v>
+        <v>-1.1932</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6096</v>
+        <v>0.9986</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9407</v>
+        <v>-1.1932</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4891</v>
+        <v>-0.6443</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6096</v>
+        <v>0.9986</v>
       </c>
       <c r="K26" t="n">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="L26" t="n">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1205000000000001</v>
+        <v>0.3543000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>335</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Vegi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.383</v>
+        <v>-0.3126</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.053</v>
+        <v>-0.0433</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8109</v>
+        <v>-0.7665</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.383</v>
+        <v>-0.3126</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3034</v>
+        <v>-0.9993</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9204</v>
+        <v>0.6867</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3034</v>
+        <v>-0.9993</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6777</v>
+        <v>-0.5396</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9204</v>
+        <v>0.6867</v>
       </c>
       <c r="K27" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="L27" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2427</v>
+        <v>0.1471</v>
       </c>
       <c r="N27" t="n">
-        <v>375</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4478</v>
+        <v>-0.6433</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.062</v>
+        <v>-0.0891</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.917</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4478</v>
+        <v>-0.6433</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5356</v>
+        <v>0.3567</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5356</v>
+        <v>0.3567</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2785</v>
+        <v>0.1926</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
         <v>277</v>
@@ -1725,7 +1725,7 @@
         <v>77</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7049000000000001</v>
+        <v>-0.8074</v>
       </c>
       <c r="N28" t="n">
         <v>354</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1385</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0895</v>
+        <v>-1.0794</v>
       </c>
       <c r="E29" t="n">
         <v>-1</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.1661</v>
+        <v>-1.8961</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3</v>
+        <v>-0.2626</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.6159</v>
+        <v>-1.4873</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.1661</v>
+        <v>-1.8961</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.8479</v>
+        <v>-2.6597</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6818</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.8479</v>
+        <v>-2.6597</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4808</v>
+        <v>-1.4362</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6818</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>232</v>
@@ -1817,7 +1817,7 @@
         <v>113</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7989999999999999</v>
+        <v>-0.6726</v>
       </c>
       <c r="N30" t="n">
         <v>345</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.7501</v>
+        <v>-2.7627</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3808</v>
+        <v>-0.3826</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8795</v>
+        <v>-1.8818</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.7501</v>
+        <v>-2.7627</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.8925</v>
+        <v>-1.8871</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8576</v>
+        <v>-0.8756</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8925</v>
+        <v>-1.8871</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.984</v>
+        <v>-1.019</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8576</v>
+        <v>-0.8756</v>
       </c>
       <c r="K31" t="n">
         <v>256</v>
@@ -1863,7 +1863,7 @@
         <v>79</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.8416</v>
+        <v>-1.8946</v>
       </c>
       <c r="N31" t="n">
         <v>335</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.9068</v>
+        <v>-4.0237</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.541</v>
+        <v>-0.5572</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.4017</v>
+        <v>-2.4559</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.9068</v>
+        <v>-4.0237</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.9068</v>
+        <v>-4.0237</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-3.9068</v>
+        <v>-4.0237</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.4089</v>
+        <v>-4.3428</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-4.4089</v>
+        <v>-4.3428</v>
       </c>
       <c r="N32" t="n">
         <v>263</v>
@@ -2015,10 +2015,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6015</v>
+        <v>0.5838</v>
       </c>
       <c r="J2" t="n">
-        <v>21.654</v>
+        <v>21.0168</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4023</v>
+        <v>0.4038</v>
       </c>
       <c r="J3" t="n">
-        <v>14.4828</v>
+        <v>14.5368</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0375</v>
+        <v>0.0607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.35</v>
+        <v>2.1852</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0416</v>
+        <v>0.998</v>
       </c>
       <c r="J5" t="n">
-        <v>37.4976</v>
+        <v>35.928</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>35.1828</v>
+        <v>33.1884</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5682</v>
+        <v>0.5553</v>
       </c>
       <c r="J7" t="n">
-        <v>20.4552</v>
+        <v>19.9908</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2536</v>
+        <v>-0.2659</v>
       </c>
       <c r="J8" t="n">
-        <v>-9.1296</v>
+        <v>-9.5724</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3406</v>
+        <v>-0.3511</v>
       </c>
       <c r="J9" t="n">
-        <v>-12.2616</v>
+        <v>-12.6396</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4806</v>
+        <v>0.4748</v>
       </c>
       <c r="J10" t="n">
-        <v>17.3016</v>
+        <v>17.0928</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4267</v>
+        <v>0.425</v>
       </c>
       <c r="J11" t="n">
-        <v>15.3612</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4483</v>
+        <v>0.4378</v>
       </c>
       <c r="J12" t="n">
-        <v>7.6211</v>
+        <v>7.4426</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2849</v>
+        <v>0.2837</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8433</v>
+        <v>4.8229</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.62</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3956</v>
+        <v>-0.4076</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.7252</v>
+        <v>-6.9292</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3298</v>
+        <v>-0.3443</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.6066</v>
+        <v>-5.8531</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3676</v>
+        <v>-0.3807</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.2492</v>
+        <v>-6.4719</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8677</v>
+        <v>-0.8478</v>
       </c>
       <c r="J17" t="n">
-        <v>-14.7509</v>
+        <v>-14.4126</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9379</v>
+        <v>-0.9117</v>
       </c>
       <c r="J18" t="n">
-        <v>-15.9443</v>
+        <v>-15.4989</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9467</v>
+        <v>-0.9197</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.0939</v>
+        <v>-15.6349</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>2.15</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3167</v>
+        <v>1.4264</v>
       </c>
       <c r="J20" t="n">
-        <v>22.3839</v>
+        <v>24.2488</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>1.87</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1232</v>
+        <v>1.1361</v>
       </c>
       <c r="J21" t="n">
-        <v>19.0944</v>
+        <v>19.3137</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2968</v>
+        <v>1.3777</v>
       </c>
       <c r="J22" t="n">
-        <v>38.904</v>
+        <v>41.331</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.66</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2852</v>
+        <v>1.361</v>
       </c>
       <c r="J23" t="n">
-        <v>38.556</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>1.51</v>
       </c>
       <c r="I24" t="n">
-        <v>1.109</v>
+        <v>1.1047</v>
       </c>
       <c r="J24" t="n">
-        <v>33.27</v>
+        <v>33.141</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>1.29</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7217</v>
+        <v>0.6992</v>
       </c>
       <c r="J25" t="n">
-        <v>21.651</v>
+        <v>20.976</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>1.16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4066</v>
+        <v>0.4179</v>
       </c>
       <c r="J26" t="n">
-        <v>12.198</v>
+        <v>12.537</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1508</v>
+        <v>-0.1679</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.524</v>
+        <v>-5.037</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>0.62</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3922</v>
+        <v>-0.4049</v>
       </c>
       <c r="J28" t="n">
-        <v>-11.766</v>
+        <v>-12.147</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5303</v>
+        <v>-0.5357</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.909</v>
+        <v>-16.071</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.22</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5431</v>
+        <v>0.5175</v>
       </c>
       <c r="J30" t="n">
-        <v>16.293</v>
+        <v>15.525</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1621</v>
+        <v>0.1581</v>
       </c>
       <c r="J31" t="n">
-        <v>4.863</v>
+        <v>4.743</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6528</v>
       </c>
       <c r="J32" t="n">
-        <v>16.5256</v>
+        <v>18.2784</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>0.89</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1283</v>
+        <v>-0.1453</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.5924</v>
+        <v>-4.0684</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.258</v>
+        <v>-0.2753</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.224</v>
+        <v>-7.7084</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>0.63</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3817</v>
+        <v>-0.3951</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.6876</v>
+        <v>-11.0628</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5657</v>
+        <v>-0.5689</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.8396</v>
+        <v>-15.9292</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4544</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>12.7232</v>
+        <v>14.5208</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4415</v>
+        <v>0.5032</v>
       </c>
       <c r="J38" t="n">
-        <v>12.362</v>
+        <v>14.0896</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3556</v>
+        <v>0.3868</v>
       </c>
       <c r="J39" t="n">
-        <v>9.956799999999999</v>
+        <v>10.8304</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1882</v>
+        <v>0.2077</v>
       </c>
       <c r="J40" t="n">
-        <v>5.2696</v>
+        <v>5.8156</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0601</v>
+        <v>-0.0614</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6828</v>
+        <v>-1.7192</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9163</v>
+        <v>1.0118</v>
       </c>
       <c r="J42" t="n">
-        <v>21.0749</v>
+        <v>23.2714</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7135</v>
+        <v>0.7927</v>
       </c>
       <c r="J43" t="n">
-        <v>16.4105</v>
+        <v>18.2321</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6616</v>
+        <v>0.7359</v>
       </c>
       <c r="J44" t="n">
-        <v>15.2168</v>
+        <v>16.9257</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.23</v>
+        <v>0.2463</v>
       </c>
       <c r="J45" t="n">
-        <v>5.29</v>
+        <v>5.6649</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2978</v>
+        <v>-0.2784</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.8494</v>
+        <v>-6.4032</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4462</v>
+        <v>0.4765</v>
       </c>
       <c r="J47" t="n">
-        <v>10.2626</v>
+        <v>10.9595</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>0.83</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1783</v>
+        <v>-0.1989</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.1009</v>
+        <v>-4.5747</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.73</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2753</v>
+        <v>-0.2947</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.3319</v>
+        <v>-6.7781</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.64</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3594</v>
+        <v>-0.3761</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.2662</v>
+        <v>-8.6503</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.36</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6194</v>
+        <v>-0.6203</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.2462</v>
+        <v>-14.2669</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9008</v>
+        <v>0.9886</v>
       </c>
       <c r="J52" t="n">
-        <v>25.2224</v>
+        <v>27.6808</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1705</v>
+        <v>0.1821</v>
       </c>
       <c r="J53" t="n">
-        <v>4.774</v>
+        <v>5.0988</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.103</v>
+        <v>0.117</v>
       </c>
       <c r="J54" t="n">
-        <v>2.884</v>
+        <v>3.276</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>1.8508</v>
+        <v>2.2596</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>1.02</v>
       </c>
       <c r="I56" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>1.8508</v>
+        <v>2.2596</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4472</v>
+        <v>0.4901</v>
       </c>
       <c r="J57" t="n">
-        <v>12.5216</v>
+        <v>13.7228</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.081</v>
+        <v>-0.0936</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.268</v>
+        <v>-2.6208</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1781</v>
+        <v>-0.1939</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.9868</v>
+        <v>-5.4292</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2189</v>
+        <v>-0.2346</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.1292</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2781</v>
+        <v>-0.293</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.7868</v>
+        <v>-8.204000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4202</v>
+        <v>0.4663</v>
       </c>
       <c r="J62" t="n">
-        <v>11.7656</v>
+        <v>13.0564</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3968</v>
+        <v>0.4364</v>
       </c>
       <c r="J63" t="n">
-        <v>11.1104</v>
+        <v>12.2192</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0487</v>
+        <v>0.0562</v>
       </c>
       <c r="J64" t="n">
-        <v>1.3636</v>
+        <v>1.5736</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2004</v>
+        <v>-0.2135</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.6112</v>
+        <v>-5.978</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3943</v>
+        <v>-0.4034</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.0404</v>
+        <v>-11.2952</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.4</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4465</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>12.502</v>
+        <v>14.1848</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.34</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4058</v>
+        <v>0.4577</v>
       </c>
       <c r="J68" t="n">
-        <v>11.3624</v>
+        <v>12.8156</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3571</v>
+        <v>0.3863</v>
       </c>
       <c r="J69" t="n">
-        <v>9.998799999999999</v>
+        <v>10.8164</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1146</v>
+        <v>-0.1228</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.2088</v>
+        <v>-3.4384</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3028</v>
+        <v>-0.3124</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.478400000000001</v>
+        <v>-8.747199999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.92</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3237</v>
+        <v>1.4484</v>
       </c>
       <c r="J72" t="n">
-        <v>27.7977</v>
+        <v>30.4164</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8306</v>
+        <v>0.9244</v>
       </c>
       <c r="J73" t="n">
-        <v>17.4426</v>
+        <v>19.4124</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>1.3</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5828</v>
+        <v>0.6523</v>
       </c>
       <c r="J74" t="n">
-        <v>12.2388</v>
+        <v>13.6983</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>1.2</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4439</v>
+        <v>0.4972</v>
       </c>
       <c r="J75" t="n">
-        <v>9.321899999999999</v>
+        <v>10.4412</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1691</v>
+        <v>0.1966</v>
       </c>
       <c r="J76" t="n">
-        <v>3.5511</v>
+        <v>4.1286</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.169</v>
+        <v>0.1396</v>
       </c>
       <c r="J77" t="n">
-        <v>3.549</v>
+        <v>2.9316</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>0.73</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2661</v>
+        <v>-0.2877</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.5881</v>
+        <v>-6.0417</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3852</v>
+        <v>-0.4027</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.0892</v>
+        <v>-8.4567</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4132</v>
+        <v>-0.4292</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.677199999999999</v>
+        <v>-9.013199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5069</v>
+        <v>-0.5172</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.6449</v>
+        <v>-10.8612</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9189000000000001</v>
+        <v>1.0165</v>
       </c>
       <c r="J82" t="n">
-        <v>25.7292</v>
+        <v>28.462</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.49</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8324</v>
+        <v>0.9234</v>
       </c>
       <c r="J83" t="n">
-        <v>23.3072</v>
+        <v>25.8552</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.42</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7446</v>
+        <v>0.8282</v>
       </c>
       <c r="J84" t="n">
-        <v>20.8488</v>
+        <v>23.1896</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3052</v>
+        <v>0.3186</v>
       </c>
       <c r="J85" t="n">
-        <v>8.5456</v>
+        <v>8.9208</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2429</v>
+        <v>-0.2235</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.8012</v>
+        <v>-6.258</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0026</v>
+        <v>-0.0137</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0728</v>
+        <v>-0.3836</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1156</v>
+        <v>-0.1354</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.2368</v>
+        <v>-3.7912</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.7</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3054</v>
+        <v>-0.3236</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.5512</v>
+        <v>-9.0608</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3619</v>
+        <v>-0.378</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.1332</v>
+        <v>-10.584</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.39</v>
+        <v>-0.4048</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.92</v>
+        <v>-11.3344</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.05</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2534</v>
+        <v>0.2316</v>
       </c>
       <c r="J92" t="n">
-        <v>5.3214</v>
+        <v>4.8636</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>0.75</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2537</v>
+        <v>-0.2742</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.3277</v>
+        <v>-5.7582</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>0.73</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2725</v>
+        <v>-0.2926</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.7225</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3828</v>
+        <v>-0.3992</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.0388</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.45</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5322</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.1762</v>
+        <v>-11.3358</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.91</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5901</v>
+        <v>1.5874</v>
       </c>
       <c r="J97" t="n">
-        <v>33.3921</v>
+        <v>33.3354</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1.39</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9497</v>
+        <v>0.8999</v>
       </c>
       <c r="J98" t="n">
-        <v>19.9437</v>
+        <v>18.8979</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7369</v>
+        <v>0.7098</v>
       </c>
       <c r="J99" t="n">
-        <v>15.4749</v>
+        <v>14.9058</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5239</v>
+        <v>0.5203</v>
       </c>
       <c r="J100" t="n">
-        <v>11.0019</v>
+        <v>10.9263</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>1.12</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3164</v>
+        <v>0.3323</v>
       </c>
       <c r="J101" t="n">
-        <v>6.6444</v>
+        <v>6.9783</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3389</v>
+        <v>1.3153</v>
       </c>
       <c r="J102" t="n">
-        <v>33.4725</v>
+        <v>32.8825</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.3389</v>
+        <v>1.3153</v>
       </c>
       <c r="J103" t="n">
-        <v>33.4725</v>
+        <v>32.8825</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.081</v>
+        <v>0.1017</v>
       </c>
       <c r="J104" t="n">
-        <v>2.025</v>
+        <v>2.5425</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.35</v>
+        <v>-5.9925</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7549</v>
+        <v>-0.6955</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.8725</v>
+        <v>-17.3875</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6264</v>
+        <v>0.5952</v>
       </c>
       <c r="J107" t="n">
-        <v>15.66</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1015</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>2.5375</v>
+        <v>2.4775</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0866</v>
+        <v>-0.1012</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.165</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2616</v>
+        <v>-0.2782</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.54</v>
+        <v>-6.955</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.34</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6493</v>
+        <v>-0.6464</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.2325</v>
+        <v>-16.16</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6821</v>
+        <v>0.6483</v>
       </c>
       <c r="J112" t="n">
-        <v>15.6883</v>
+        <v>14.9109</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>0.95</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0664</v>
+        <v>-0.0789</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.5272</v>
+        <v>-1.8147</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2164</v>
+        <v>-0.2327</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.9772</v>
+        <v>-5.3521</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2658</v>
+        <v>-0.2814</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.1134</v>
+        <v>-6.4722</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3709</v>
+        <v>-0.3834</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.5307</v>
+        <v>-8.818199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.948</v>
+        <v>0.8907</v>
       </c>
       <c r="J117" t="n">
-        <v>21.804</v>
+        <v>20.4861</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7458</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>17.1534</v>
+        <v>16.3576</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>1.26</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6994</v>
+        <v>0.6702</v>
       </c>
       <c r="J119" t="n">
-        <v>16.0862</v>
+        <v>15.4146</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3834</v>
+        <v>0.3849</v>
       </c>
       <c r="J120" t="n">
-        <v>8.818199999999999</v>
+        <v>8.8527</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1051</v>
+        <v>-0.0945</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.4173</v>
+        <v>-2.1735</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8681</v>
+        <v>0.8132</v>
       </c>
       <c r="J122" t="n">
-        <v>26.043</v>
+        <v>24.396</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5028</v>
+        <v>0.4898</v>
       </c>
       <c r="J123" t="n">
-        <v>15.084</v>
+        <v>14.694</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2929</v>
+        <v>0.2968</v>
       </c>
       <c r="J124" t="n">
-        <v>8.787000000000001</v>
+        <v>8.904</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2044</v>
+        <v>0.2137</v>
       </c>
       <c r="J125" t="n">
-        <v>6.132</v>
+        <v>6.411</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2607</v>
+        <v>-0.2524</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.821</v>
+        <v>-7.572</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4779</v>
+        <v>0.4695</v>
       </c>
       <c r="J127" t="n">
-        <v>14.337</v>
+        <v>14.085</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.141</v>
+        <v>0.1491</v>
       </c>
       <c r="J128" t="n">
-        <v>4.23</v>
+        <v>4.473</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0389</v>
+        <v>0.0441</v>
       </c>
       <c r="J129" t="n">
-        <v>1.167</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1108</v>
+        <v>-0.123</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.324</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2776</v>
+        <v>-0.2907</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.327999999999999</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3984</v>
+        <v>0.3733</v>
       </c>
       <c r="J132" t="n">
-        <v>8.764799999999999</v>
+        <v>8.2126</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>0.95</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0371</v>
+        <v>-0.056</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.8162</v>
+        <v>-1.232</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>0.58</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4153</v>
+        <v>-0.4293</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.1366</v>
+        <v>-9.444599999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.434</v>
+        <v>-0.447</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.548</v>
+        <v>-9.834</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4713</v>
+        <v>-0.4822</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.3686</v>
+        <v>-10.6084</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.84</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5223</v>
+        <v>1.5141</v>
       </c>
       <c r="J137" t="n">
-        <v>33.4906</v>
+        <v>33.3102</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.51</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1267</v>
+        <v>1.0937</v>
       </c>
       <c r="J138" t="n">
-        <v>24.7874</v>
+        <v>24.0614</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4848</v>
+        <v>0.483</v>
       </c>
       <c r="J139" t="n">
-        <v>10.6656</v>
+        <v>10.626</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1837</v>
+        <v>0.2069</v>
       </c>
       <c r="J140" t="n">
-        <v>4.0414</v>
+        <v>4.5518</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1528</v>
+        <v>0.1778</v>
       </c>
       <c r="J141" t="n">
-        <v>3.3616</v>
+        <v>3.9116</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>1.534</v>
+        <v>1.5264</v>
       </c>
       <c r="J142" t="n">
-        <v>35.282</v>
+        <v>35.1072</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>1.188</v>
+        <v>1.1597</v>
       </c>
       <c r="J143" t="n">
-        <v>27.324</v>
+        <v>26.6731</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5834</v>
+        <v>0.5714</v>
       </c>
       <c r="J144" t="n">
-        <v>13.4182</v>
+        <v>13.1422</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2717</v>
+        <v>0.2888</v>
       </c>
       <c r="J145" t="n">
-        <v>6.2491</v>
+        <v>6.6424</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.345</v>
+        <v>-0.3189</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.935</v>
+        <v>-7.3347</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.14</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3915</v>
+        <v>0.3764</v>
       </c>
       <c r="J147" t="n">
-        <v>9.0045</v>
+        <v>8.6572</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0843</v>
+        <v>0.0771</v>
       </c>
       <c r="J148" t="n">
-        <v>1.9389</v>
+        <v>1.7733</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0045</v>
+        <v>-0.0075</v>
       </c>
       <c r="J149" t="n">
-        <v>0.1035</v>
+        <v>-0.1725</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3715</v>
+        <v>-0.3855</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.8665</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.37</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6192</v>
+        <v>-0.6189</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.2416</v>
+        <v>-14.2347</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.76</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8386</v>
+        <v>0.8328</v>
       </c>
       <c r="J152" t="n">
-        <v>15.9334</v>
+        <v>15.8232</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6915</v>
+        <v>0.6965</v>
       </c>
       <c r="J153" t="n">
-        <v>13.1385</v>
+        <v>13.2335</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.42</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5017</v>
+        <v>0.5171</v>
       </c>
       <c r="J154" t="n">
-        <v>9.532299999999999</v>
+        <v>9.8249</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>1.39</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4697</v>
+        <v>0.4868</v>
       </c>
       <c r="J155" t="n">
-        <v>8.924300000000001</v>
+        <v>9.2492</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>1.33</v>
       </c>
       <c r="I156" t="n">
-        <v>0.4039</v>
+        <v>0.4239</v>
       </c>
       <c r="J156" t="n">
-        <v>7.6741</v>
+        <v>8.0541</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>0.73</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2117</v>
+        <v>-0.245</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.0223</v>
+        <v>-4.655</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>0.53</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.4213</v>
+        <v>-0.4419</v>
       </c>
       <c r="J158" t="n">
-        <v>-8.0047</v>
+        <v>-8.396100000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4651</v>
+        <v>-0.4831</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.8369</v>
+        <v>-9.178900000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.42</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5356</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.9123</v>
+        <v>-10.1764</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.38</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5606</v>
+        <v>-0.5714</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.6514</v>
+        <v>-10.8566</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3635</v>
+        <v>0.3741</v>
       </c>
       <c r="J162" t="n">
-        <v>10.905</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="163">
@@ -8455,10 +8455,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.351</v>
+        <v>0.3621</v>
       </c>
       <c r="J163" t="n">
-        <v>10.53</v>
+        <v>10.863</v>
       </c>
     </row>
     <row r="164">
@@ -8495,10 +8495,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0257</v>
+        <v>-0.0292</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.771</v>
+        <v>-0.876</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1037</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.826</v>
+        <v>-3.111</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1734</v>
+        <v>-0.1853</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.202</v>
+        <v>-5.559</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8589</v>
+        <v>0.8215</v>
       </c>
       <c r="J167" t="n">
-        <v>25.767</v>
+        <v>24.645</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.29</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5651</v>
+        <v>0.5562</v>
       </c>
       <c r="J168" t="n">
-        <v>16.953</v>
+        <v>16.686</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3385</v>
+        <v>0.3456</v>
       </c>
       <c r="J169" t="n">
-        <v>10.155</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2103</v>
+        <v>-0.2212</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.309</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2707</v>
+        <v>-0.2813</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.121</v>
+        <v>-8.439</v>
       </c>
     </row>
     <row r="172">
@@ -8815,10 +8815,10 @@
         <v>1.91</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5562</v>
+        <v>1.5573</v>
       </c>
       <c r="J172" t="n">
-        <v>28.0116</v>
+        <v>28.0314</v>
       </c>
     </row>
     <row r="173">
@@ -8855,10 +8855,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3881</v>
+        <v>1.3797</v>
       </c>
       <c r="J173" t="n">
-        <v>24.9858</v>
+        <v>24.8346</v>
       </c>
     </row>
     <row r="174">
@@ -8895,10 +8895,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9656</v>
+        <v>0.92</v>
       </c>
       <c r="J174" t="n">
-        <v>17.3808</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="175">
@@ -8935,10 +8935,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9063</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>16.3134</v>
+        <v>15.5592</v>
       </c>
     </row>
     <row r="176">
@@ -8975,10 +8975,10 @@
         <v>1.21</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5171</v>
+        <v>0.5204</v>
       </c>
       <c r="J176" t="n">
-        <v>9.3078</v>
+        <v>9.3672</v>
       </c>
     </row>
     <row r="177">
@@ -9015,10 +9015,10 @@
         <v>0.9</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0475</v>
+        <v>-0.0791</v>
       </c>
       <c r="J177" t="n">
-        <v>-0.855</v>
+        <v>-1.4238</v>
       </c>
     </row>
     <row r="178">
@@ -9055,10 +9055,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2452</v>
+        <v>-0.2714</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.4136</v>
+        <v>-4.8852</v>
       </c>
     </row>
     <row r="179">
@@ -9095,10 +9095,10 @@
         <v>0.62</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3549</v>
+        <v>-0.3761</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.3882</v>
+        <v>-6.7698</v>
       </c>
     </row>
     <row r="180">
@@ -9135,10 +9135,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5777</v>
+        <v>-0.5848</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.3986</v>
+        <v>-10.5264</v>
       </c>
     </row>
     <row r="181">
@@ -9175,10 +9175,10 @@
         <v>0.33</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6258</v>
+        <v>-0.629</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.2644</v>
+        <v>-11.322</v>
       </c>
     </row>
     <row r="182">
@@ -9215,10 +9215,10 @@
         <v>1.01</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1134</v>
+        <v>0.0985</v>
       </c>
       <c r="J182" t="n">
-        <v>2.7216</v>
+        <v>2.364</v>
       </c>
     </row>
     <row r="183">
@@ -9255,10 +9255,10 @@
         <v>0.9</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1045</v>
+        <v>-0.124</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.508</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="184">
@@ -9295,10 +9295,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.202</v>
+        <v>-0.2217</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.848</v>
+        <v>-5.3208</v>
       </c>
     </row>
     <row r="185">
@@ -9335,10 +9335,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4184</v>
+        <v>-0.4317</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.0416</v>
+        <v>-10.3608</v>
       </c>
     </row>
     <row r="186">
@@ -9375,10 +9375,10 @@
         <v>0.53</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4649</v>
+        <v>-0.4757</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.1576</v>
+        <v>-11.4168</v>
       </c>
     </row>
     <row r="187">
@@ -9415,10 +9415,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1977</v>
+        <v>1.1682</v>
       </c>
       <c r="J187" t="n">
-        <v>28.7448</v>
+        <v>28.0368</v>
       </c>
     </row>
     <row r="188">
@@ -9455,10 +9455,10 @@
         <v>1.38</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9477</v>
+        <v>0.8944</v>
       </c>
       <c r="J188" t="n">
-        <v>22.7448</v>
+        <v>21.4656</v>
       </c>
     </row>
     <row r="189">
@@ -9495,10 +9495,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6171</v>
+        <v>0.5995</v>
       </c>
       <c r="J189" t="n">
-        <v>14.8104</v>
+        <v>14.388</v>
       </c>
     </row>
     <row r="190">
@@ -9535,10 +9535,10 @@
         <v>1.14</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3923</v>
+        <v>0.3969</v>
       </c>
       <c r="J190" t="n">
-        <v>9.4152</v>
+        <v>9.525600000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9575,10 +9575,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3109</v>
+        <v>0.3224</v>
       </c>
       <c r="J191" t="n">
-        <v>7.4616</v>
+        <v>7.7376</v>
       </c>
     </row>
     <row r="192">
@@ -9615,10 +9615,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.846</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>30.456</v>
+        <v>28.6884</v>
       </c>
     </row>
     <row r="193">
@@ -9655,10 +9655,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0285</v>
+        <v>-0.0371</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.026</v>
+        <v>-1.3356</v>
       </c>
     </row>
     <row r="194">
@@ -9695,10 +9695,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.524</v>
+        <v>-8.0892</v>
       </c>
     </row>
     <row r="195">
@@ -9735,10 +9735,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2391</v>
+        <v>-0.2545</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.6076</v>
+        <v>-9.162000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9775,10 +9775,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4294</v>
+        <v>-0.4389</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.4584</v>
+        <v>-15.8004</v>
       </c>
     </row>
     <row r="197">
@@ -9815,10 +9815,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3997</v>
+        <v>1.3776</v>
       </c>
       <c r="J197" t="n">
-        <v>50.3892</v>
+        <v>49.5936</v>
       </c>
     </row>
     <row r="198">
@@ -9855,10 +9855,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6828</v>
+        <v>0.654</v>
       </c>
       <c r="J198" t="n">
-        <v>24.5808</v>
+        <v>23.544</v>
       </c>
     </row>
     <row r="199">
@@ -9895,10 +9895,10 @@
         <v>1.23</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6353</v>
+        <v>0.6118</v>
       </c>
       <c r="J199" t="n">
-        <v>22.8708</v>
+        <v>22.0248</v>
       </c>
     </row>
     <row r="200">
@@ -9935,10 +9935,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3076</v>
+        <v>0.3138</v>
       </c>
       <c r="J200" t="n">
-        <v>11.0736</v>
+        <v>11.2968</v>
       </c>
     </row>
     <row r="201">
@@ -9975,10 +9975,10 @@
         <v>0.61</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.1337</v>
+        <v>-1.0269</v>
       </c>
       <c r="J201" t="n">
-        <v>-40.8132</v>
+        <v>-36.9684</v>
       </c>
     </row>
     <row r="202">
@@ -10015,10 +10015,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1117</v>
+        <v>1.0754</v>
       </c>
       <c r="J202" t="n">
-        <v>27.7925</v>
+        <v>26.885</v>
       </c>
     </row>
     <row r="203">
@@ -10055,10 +10055,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>1.034</v>
+        <v>0.9851</v>
       </c>
       <c r="J203" t="n">
-        <v>25.85</v>
+        <v>24.6275</v>
       </c>
     </row>
     <row r="204">
@@ -10095,10 +10095,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9079</v>
+        <v>0.8572</v>
       </c>
       <c r="J204" t="n">
-        <v>22.6975</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="205">
@@ -10135,10 +10135,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6649</v>
+        <v>0.6419</v>
       </c>
       <c r="J205" t="n">
-        <v>16.6225</v>
+        <v>16.0475</v>
       </c>
     </row>
     <row r="206">
@@ -10175,10 +10175,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5343</v>
+        <v>-0.4956</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.3575</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="207">
@@ -10215,10 +10215,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4164</v>
+        <v>0.4064</v>
       </c>
       <c r="J207" t="n">
-        <v>10.41</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="208">
@@ -10255,10 +10255,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1873</v>
+        <v>0.1887</v>
       </c>
       <c r="J208" t="n">
-        <v>4.6825</v>
+        <v>4.7175</v>
       </c>
     </row>
     <row r="209">
@@ -10295,10 +10295,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1873</v>
+        <v>-0.2033</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.6825</v>
+        <v>-5.0825</v>
       </c>
     </row>
     <row r="210">
@@ -10335,10 +10335,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2276</v>
+        <v>-0.2435</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.69</v>
+        <v>-6.0875</v>
       </c>
     </row>
     <row r="211">
@@ -10375,10 +10375,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3628</v>
+        <v>-0.3754</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.07</v>
+        <v>-9.385</v>
       </c>
     </row>
     <row r="212">
@@ -10415,10 +10415,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6282</v>
+        <v>0.6341</v>
       </c>
       <c r="J212" t="n">
-        <v>14.4486</v>
+        <v>14.5843</v>
       </c>
     </row>
     <row r="213">
@@ -10455,10 +10455,10 @@
         <v>1.44</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5453</v>
       </c>
       <c r="J213" t="n">
-        <v>12.2774</v>
+        <v>12.5419</v>
       </c>
     </row>
     <row r="214">
@@ -10495,10 +10495,10 @@
         <v>1.41</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5021</v>
+        <v>0.5152</v>
       </c>
       <c r="J214" t="n">
-        <v>11.5483</v>
+        <v>11.8496</v>
       </c>
     </row>
     <row r="215">
@@ -10535,10 +10535,10 @@
         <v>1.3</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3842</v>
+        <v>0.402</v>
       </c>
       <c r="J215" t="n">
-        <v>8.836600000000001</v>
+        <v>9.246</v>
       </c>
     </row>
     <row r="216">
@@ -10575,10 +10575,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1479</v>
+        <v>0.1704</v>
       </c>
       <c r="J216" t="n">
-        <v>3.4017</v>
+        <v>3.9192</v>
       </c>
     </row>
     <row r="217">
@@ -10615,10 +10615,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1863</v>
+        <v>-0.2095</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.2849</v>
+        <v>-4.8185</v>
       </c>
     </row>
     <row r="218">
@@ -10655,10 +10655,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2774</v>
+        <v>-0.2984</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.3802</v>
+        <v>-6.8632</v>
       </c>
     </row>
     <row r="219">
@@ -10695,10 +10695,10 @@
         <v>0.66</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3315</v>
+        <v>-0.351</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.6245</v>
+        <v>-8.073</v>
       </c>
     </row>
     <row r="220">
@@ -10735,10 +10735,10 @@
         <v>0.63</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.359</v>
+        <v>-0.3775</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.257</v>
+        <v>-8.682499999999999</v>
       </c>
     </row>
     <row r="221">
@@ -10775,10 +10775,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3776</v>
+        <v>-0.3952</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.684799999999999</v>
+        <v>-9.089600000000001</v>
       </c>
     </row>
     <row r="222">
@@ -10815,10 +10815,10 @@
         <v>1.83</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9344</v>
+        <v>0.9177</v>
       </c>
       <c r="J222" t="n">
-        <v>21.4912</v>
+        <v>21.1071</v>
       </c>
     </row>
     <row r="223">
@@ -10855,10 +10855,10 @@
         <v>1.62</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7235</v>
+        <v>0.7225</v>
       </c>
       <c r="J223" t="n">
-        <v>16.6405</v>
+        <v>16.6175</v>
       </c>
     </row>
     <row r="224">
@@ -10895,10 +10895,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4396</v>
+        <v>0.4552</v>
       </c>
       <c r="J224" t="n">
-        <v>10.1108</v>
+        <v>10.4696</v>
       </c>
     </row>
     <row r="225">
@@ -10935,10 +10935,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2425</v>
+        <v>0.264</v>
       </c>
       <c r="J225" t="n">
-        <v>5.5775</v>
+        <v>6.072</v>
       </c>
     </row>
     <row r="226">
@@ -10975,10 +10975,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3296</v>
+        <v>-0.3353</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.5808</v>
+        <v>-7.7119</v>
       </c>
     </row>
     <row r="227">
@@ -11015,10 +11015,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0609</v>
+        <v>-0.078</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.4007</v>
+        <v>-1.794</v>
       </c>
     </row>
     <row r="228">
@@ -11055,10 +11055,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1094</v>
+        <v>-0.1278</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.5162</v>
+        <v>-2.9394</v>
       </c>
     </row>
     <row r="229">
@@ -11095,10 +11095,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1852</v>
+        <v>-0.2042</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.2596</v>
+        <v>-4.6966</v>
       </c>
     </row>
     <row r="230">
@@ -11135,10 +11135,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2616</v>
+        <v>-0.2802</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.0168</v>
+        <v>-6.4446</v>
       </c>
     </row>
     <row r="231">
@@ -11175,10 +11175,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4684</v>
+        <v>-0.4784</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.7732</v>
+        <v>-11.0032</v>
       </c>
     </row>
     <row r="232">
@@ -11215,10 +11215,10 @@
         <v>2.02</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6597</v>
+        <v>1.6689</v>
       </c>
       <c r="J232" t="n">
-        <v>31.5343</v>
+        <v>31.7091</v>
       </c>
     </row>
     <row r="233">
@@ -11255,10 +11255,10 @@
         <v>1.82</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4416</v>
+        <v>1.4391</v>
       </c>
       <c r="J233" t="n">
-        <v>27.3904</v>
+        <v>27.3429</v>
       </c>
     </row>
     <row r="234">
@@ -11295,10 +11295,10 @@
         <v>1.68</v>
       </c>
       <c r="I234" t="n">
-        <v>1.2868</v>
+        <v>1.274</v>
       </c>
       <c r="J234" t="n">
-        <v>24.4492</v>
+        <v>24.206</v>
       </c>
     </row>
     <row r="235">
@@ -11335,10 +11335,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>1.0327</v>
+        <v>0.994</v>
       </c>
       <c r="J235" t="n">
-        <v>19.6213</v>
+        <v>18.886</v>
       </c>
     </row>
     <row r="236">
@@ -11375,10 +11375,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.348</v>
+        <v>0.3714</v>
       </c>
       <c r="J236" t="n">
-        <v>6.612</v>
+        <v>7.0566</v>
       </c>
     </row>
     <row r="237">
@@ -11415,10 +11415,10 @@
         <v>0.7</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2685</v>
+        <v>-0.2951</v>
       </c>
       <c r="J237" t="n">
-        <v>-5.1015</v>
+        <v>-5.6069</v>
       </c>
     </row>
     <row r="238">
@@ -11455,10 +11455,10 @@
         <v>0.63</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3398</v>
+        <v>-0.3627</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.4562</v>
+        <v>-6.8913</v>
       </c>
     </row>
     <row r="239">
@@ -11495,10 +11495,10 @@
         <v>0.61</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3591</v>
+        <v>-0.381</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.8229</v>
+        <v>-7.239</v>
       </c>
     </row>
     <row r="240">
@@ -11535,10 +11535,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3778</v>
+        <v>-0.3987</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.1782</v>
+        <v>-7.5753</v>
       </c>
     </row>
     <row r="241">
@@ -11575,10 +11575,10 @@
         <v>0.3</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6506</v>
+        <v>-0.6522</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.3614</v>
+        <v>-12.3918</v>
       </c>
     </row>
     <row r="242">
@@ -11615,10 +11615,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.1161</v>
       </c>
       <c r="J242" t="n">
-        <v>-1.4706</v>
+        <v>-2.0898</v>
       </c>
     </row>
     <row r="243">
@@ -11655,10 +11655,10 @@
         <v>0.61</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.3572</v>
+        <v>-0.3796</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.4296</v>
+        <v>-6.8328</v>
       </c>
     </row>
     <row r="244">
@@ -11695,10 +11695,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3944</v>
+        <v>-0.4148</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.0992</v>
+        <v>-7.4664</v>
       </c>
     </row>
     <row r="245">
@@ -11735,10 +11735,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4474</v>
+        <v>-0.4649</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.0532</v>
+        <v>-8.3682</v>
       </c>
     </row>
     <row r="246">
@@ -11775,10 +11775,10 @@
         <v>0.24</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7083</v>
+        <v>-0.7049</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.7494</v>
+        <v>-12.6882</v>
       </c>
     </row>
     <row r="247">
@@ -11815,10 +11815,10 @@
         <v>2.31</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J247" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="248">
@@ -11855,10 +11855,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2427</v>
+        <v>1.2265</v>
       </c>
       <c r="J248" t="n">
-        <v>22.3686</v>
+        <v>22.077</v>
       </c>
     </row>
     <row r="249">
@@ -11895,10 +11895,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.0949</v>
+        <v>1.066</v>
       </c>
       <c r="J249" t="n">
-        <v>19.7082</v>
+        <v>19.188</v>
       </c>
     </row>
     <row r="250">
@@ -11935,10 +11935,10 @@
         <v>1.38</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8894</v>
+        <v>0.8524</v>
       </c>
       <c r="J250" t="n">
-        <v>16.0092</v>
+        <v>15.3432</v>
       </c>
     </row>
     <row r="251">
@@ -11975,10 +11975,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.6889</v>
+        <v>0.6764</v>
       </c>
       <c r="J251" t="n">
-        <v>12.4002</v>
+        <v>12.1752</v>
       </c>
     </row>
     <row r="252">
@@ -12015,10 +12015,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>0.91</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>27.3</v>
+        <v>25.932</v>
       </c>
     </row>
     <row r="253">
@@ -12055,10 +12055,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4038</v>
+        <v>0.4046</v>
       </c>
       <c r="J253" t="n">
-        <v>12.114</v>
+        <v>12.138</v>
       </c>
     </row>
     <row r="254">
@@ -12095,10 +12095,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3856</v>
+        <v>0.3876</v>
       </c>
       <c r="J254" t="n">
-        <v>11.568</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="255">
@@ -12135,10 +12135,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1626</v>
+        <v>-0.1743</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.878</v>
+        <v>-5.229</v>
       </c>
     </row>
     <row r="256">
@@ -12175,10 +12175,10 @@
         <v>0.55</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.48</v>
+        <v>-0.4847</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.4</v>
+        <v>-14.541</v>
       </c>
     </row>
     <row r="257">
@@ -12215,10 +12215,10 @@
         <v>1.4</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5303</v>
+        <v>0.5346</v>
       </c>
       <c r="J257" t="n">
-        <v>15.909</v>
+        <v>16.038</v>
       </c>
     </row>
     <row r="258">
@@ -12255,10 +12255,10 @@
         <v>1.25</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3529</v>
+        <v>0.366</v>
       </c>
       <c r="J258" t="n">
-        <v>10.587</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="259">
@@ -12295,10 +12295,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1331</v>
+        <v>0.1483</v>
       </c>
       <c r="J259" t="n">
-        <v>3.993</v>
+        <v>4.449</v>
       </c>
     </row>
     <row r="260">
@@ -12335,10 +12335,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0348</v>
+        <v>0.0454</v>
       </c>
       <c r="J260" t="n">
-        <v>1.044</v>
+        <v>1.362</v>
       </c>
     </row>
     <row r="261">
@@ -12375,10 +12375,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2314</v>
+        <v>-0.2422</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.942</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="262">
@@ -12415,10 +12415,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6885</v>
+        <v>0.6559</v>
       </c>
       <c r="J262" t="n">
-        <v>17.2125</v>
+        <v>16.3975</v>
       </c>
     </row>
     <row r="263">
@@ -12455,10 +12455,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1361</v>
+        <v>0.1391</v>
       </c>
       <c r="J263" t="n">
-        <v>3.4025</v>
+        <v>3.4775</v>
       </c>
     </row>
     <row r="264">
@@ -12495,10 +12495,10 @@
         <v>0.88</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.147</v>
+        <v>-0.1623</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.675</v>
+        <v>-4.0575</v>
       </c>
     </row>
     <row r="265">
@@ -12535,10 +12535,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3073</v>
+        <v>-0.3214</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.6825</v>
+        <v>-8.035</v>
       </c>
     </row>
     <row r="266">
@@ -12575,10 +12575,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3924</v>
+        <v>-0.4035</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.81</v>
+        <v>-10.0875</v>
       </c>
     </row>
     <row r="267">
@@ -12615,10 +12615,10 @@
         <v>1.34</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4457</v>
+        <v>0.4575</v>
       </c>
       <c r="J267" t="n">
-        <v>11.1425</v>
+        <v>11.4375</v>
       </c>
     </row>
     <row r="268">
@@ -12655,10 +12655,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2819</v>
+        <v>0.2993</v>
       </c>
       <c r="J268" t="n">
-        <v>7.0475</v>
+        <v>7.4825</v>
       </c>
     </row>
     <row r="269">
@@ -12695,10 +12695,10 @@
         <v>1.19</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2702</v>
+        <v>0.2876</v>
       </c>
       <c r="J269" t="n">
-        <v>6.755</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="270">
@@ -12735,10 +12735,10 @@
         <v>1.18</v>
       </c>
       <c r="I270" t="n">
-        <v>0.258</v>
+        <v>0.2756</v>
       </c>
       <c r="J270" t="n">
-        <v>6.45</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="271">
@@ -12775,10 +12775,10 @@
         <v>1.07</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1086</v>
+        <v>0.1258</v>
       </c>
       <c r="J271" t="n">
-        <v>2.715</v>
+        <v>3.145</v>
       </c>
     </row>
     <row r="272">
@@ -12815,10 +12815,10 @@
         <v>1.28</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5914</v>
+        <v>0.5724</v>
       </c>
       <c r="J272" t="n">
-        <v>21.2904</v>
+        <v>20.6064</v>
       </c>
     </row>
     <row r="273">
@@ -12855,10 +12855,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2731</v>
+        <v>0.2766</v>
       </c>
       <c r="J273" t="n">
-        <v>9.8316</v>
+        <v>9.957599999999999</v>
       </c>
     </row>
     <row r="274">
@@ -12895,10 +12895,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1955</v>
+        <v>-0.2097</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.038</v>
+        <v>-7.5492</v>
       </c>
     </row>
     <row r="275">
@@ -12935,10 +12935,10 @@
         <v>0.83</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2058</v>
+        <v>-0.22</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.4088</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="276">
@@ -12975,10 +12975,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.216</v>
+        <v>-0.2302</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.776</v>
+        <v>-8.2872</v>
       </c>
     </row>
     <row r="277">
@@ -13015,10 +13015,10 @@
         <v>1.32</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4432</v>
+        <v>0.4512</v>
       </c>
       <c r="J277" t="n">
-        <v>15.9552</v>
+        <v>16.2432</v>
       </c>
     </row>
     <row r="278">
@@ -13055,10 +13055,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4432</v>
+        <v>0.4512</v>
       </c>
       <c r="J278" t="n">
-        <v>15.9552</v>
+        <v>16.2432</v>
       </c>
     </row>
     <row r="279">
@@ -13095,10 +13095,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3085</v>
+        <v>0.322</v>
       </c>
       <c r="J279" t="n">
-        <v>11.106</v>
+        <v>11.592</v>
       </c>
     </row>
     <row r="280">
@@ -13135,10 +13135,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1762</v>
+        <v>-0.1875</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.3432</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="281">
@@ -13175,10 +13175,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3451</v>
+        <v>-0.3547</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.4236</v>
+        <v>-12.7692</v>
       </c>
     </row>
     <row r="282">
@@ -13215,10 +13215,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3629</v>
+        <v>0.3552</v>
       </c>
       <c r="J282" t="n">
-        <v>12.3386</v>
+        <v>12.0768</v>
       </c>
     </row>
     <row r="283">
@@ -13255,10 +13255,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.053</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.802</v>
+        <v>-2.1998</v>
       </c>
     </row>
     <row r="284">
@@ -13295,10 +13295,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1856</v>
+        <v>-0.2021</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.3104</v>
+        <v>-6.8714</v>
       </c>
     </row>
     <row r="285">
@@ -13335,10 +13335,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2555</v>
+        <v>-0.2714</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.686999999999999</v>
+        <v>-9.227600000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13375,10 +13375,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.275</v>
+        <v>-0.2906</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.35</v>
+        <v>-9.8804</v>
       </c>
     </row>
     <row r="287">
@@ -13415,10 +13415,10 @@
         <v>1.38</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4881</v>
+        <v>0.4983</v>
       </c>
       <c r="J287" t="n">
-        <v>16.5954</v>
+        <v>16.9422</v>
       </c>
     </row>
     <row r="288">
@@ -13455,10 +13455,10 @@
         <v>1.3</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3972</v>
+        <v>0.4117</v>
       </c>
       <c r="J288" t="n">
-        <v>13.5048</v>
+        <v>13.9978</v>
       </c>
     </row>
     <row r="289">
@@ -13495,10 +13495,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2564</v>
+        <v>0.2744</v>
       </c>
       <c r="J289" t="n">
-        <v>8.717599999999999</v>
+        <v>9.329599999999999</v>
       </c>
     </row>
     <row r="290">
@@ -13535,10 +13535,10 @@
         <v>1.16</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2312</v>
+        <v>0.2495</v>
       </c>
       <c r="J290" t="n">
-        <v>7.8608</v>
+        <v>8.483000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13575,10 +13575,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0917</v>
       </c>
       <c r="J291" t="n">
-        <v>2.5466</v>
+        <v>3.1178</v>
       </c>
     </row>
     <row r="292">
@@ -13615,10 +13615,10 @@
         <v>0.88</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1218</v>
+        <v>-0.1428</v>
       </c>
       <c r="J292" t="n">
-        <v>-2.3142</v>
+        <v>-2.7132</v>
       </c>
     </row>
     <row r="293">
@@ -13655,10 +13655,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1977</v>
+        <v>-0.2184</v>
       </c>
       <c r="J293" t="n">
-        <v>-3.7563</v>
+        <v>-4.1496</v>
       </c>
     </row>
     <row r="294">
@@ -13695,10 +13695,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2079</v>
+        <v>-0.2285</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.9501</v>
+        <v>-4.3415</v>
       </c>
     </row>
     <row r="295">
@@ -13735,10 +13735,10 @@
         <v>0.66</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3395</v>
+        <v>-0.3571</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.4505</v>
+        <v>-6.7849</v>
       </c>
     </row>
     <row r="296">
@@ -13775,10 +13775,10 @@
         <v>0.55</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4424</v>
+        <v>-0.4551</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.4056</v>
+        <v>-8.6469</v>
       </c>
     </row>
     <row r="297">
@@ -13815,10 +13815,10 @@
         <v>1.65</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7484</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="J297" t="n">
-        <v>14.2196</v>
+        <v>14.1835</v>
       </c>
     </row>
     <row r="298">
@@ -13855,10 +13855,10 @@
         <v>1.6</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6975</v>
+        <v>0.6992</v>
       </c>
       <c r="J298" t="n">
-        <v>13.2525</v>
+        <v>13.2848</v>
       </c>
     </row>
     <row r="299">
@@ -13895,10 +13895,10 @@
         <v>1.41</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5003</v>
+        <v>0.5139</v>
       </c>
       <c r="J299" t="n">
-        <v>9.505699999999999</v>
+        <v>9.764099999999999</v>
       </c>
     </row>
     <row r="300">
@@ -13935,10 +13935,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2639</v>
+        <v>0.2858</v>
       </c>
       <c r="J300" t="n">
-        <v>5.0141</v>
+        <v>5.4302</v>
       </c>
     </row>
     <row r="301">
@@ -13975,10 +13975,10 @@
         <v>1.03</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0215</v>
+        <v>0.0411</v>
       </c>
       <c r="J301" t="n">
-        <v>0.4085</v>
+        <v>0.7809</v>
       </c>
     </row>
     <row r="302">
@@ -14015,10 +14015,10 @@
         <v>1.26</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5638</v>
+        <v>0.5458</v>
       </c>
       <c r="J302" t="n">
-        <v>15.2226</v>
+        <v>14.7366</v>
       </c>
     </row>
     <row r="303">
@@ -14055,10 +14055,10 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.007</v>
+        <v>0.0049</v>
       </c>
       <c r="J303" t="n">
-        <v>0.189</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="304">
@@ -14095,10 +14095,10 @@
         <v>0.92</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1071</v>
+        <v>-0.1201</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.8917</v>
+        <v>-3.2427</v>
       </c>
     </row>
     <row r="305">
@@ -14135,10 +14135,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2237</v>
+        <v>-0.2384</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.0399</v>
+        <v>-6.4368</v>
       </c>
     </row>
     <row r="306">
@@ -14175,10 +14175,10 @@
         <v>0.79</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2438</v>
+        <v>-0.2582</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.5826</v>
+        <v>-6.9714</v>
       </c>
     </row>
     <row r="307">
@@ -14215,10 +14215,10 @@
         <v>1.6</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7478</v>
+        <v>0.7379</v>
       </c>
       <c r="J307" t="n">
-        <v>20.1906</v>
+        <v>19.9233</v>
       </c>
     </row>
     <row r="308">
@@ -14255,10 +14255,10 @@
         <v>1.27</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3731</v>
+        <v>0.3863</v>
       </c>
       <c r="J308" t="n">
-        <v>10.0737</v>
+        <v>10.4301</v>
       </c>
     </row>
     <row r="309">
@@ -14295,10 +14295,10 @@
         <v>1.02</v>
       </c>
       <c r="I309" t="n">
-        <v>0.0317</v>
+        <v>0.0431</v>
       </c>
       <c r="J309" t="n">
-        <v>0.8559</v>
+        <v>1.1637</v>
       </c>
     </row>
     <row r="310">
@@ -14335,10 +14335,10 @@
         <v>0.91</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1379</v>
+        <v>-0.1469</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.7233</v>
+        <v>-3.9663</v>
       </c>
     </row>
     <row r="311">
@@ -14375,10 +14375,10 @@
         <v>0.89</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1602</v>
+        <v>-0.1699</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.3254</v>
+        <v>-4.5873</v>
       </c>
     </row>
     <row r="312">
@@ -14415,10 +14415,10 @@
         <v>1.5</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1475</v>
+        <v>1.1096</v>
       </c>
       <c r="J312" t="n">
-        <v>30.9825</v>
+        <v>29.9592</v>
       </c>
     </row>
     <row r="313">
@@ -14455,10 +14455,10 @@
         <v>1.2</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5638</v>
+        <v>0.5476</v>
       </c>
       <c r="J313" t="n">
-        <v>15.2226</v>
+        <v>14.7852</v>
       </c>
     </row>
     <row r="314">
@@ -14495,10 +14495,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5041</v>
       </c>
       <c r="J314" t="n">
-        <v>13.9212</v>
+        <v>13.6107</v>
       </c>
     </row>
     <row r="315">
@@ -14535,10 +14535,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4671</v>
+        <v>0.4598</v>
       </c>
       <c r="J315" t="n">
-        <v>12.6117</v>
+        <v>12.4146</v>
       </c>
     </row>
     <row r="316">
@@ -14575,10 +14575,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5641</v>
+        <v>-0.5273</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.2307</v>
+        <v>-14.2371</v>
       </c>
     </row>
     <row r="317">
@@ -14615,10 +14615,10 @@
         <v>1.38</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7533</v>
+        <v>0.7204</v>
       </c>
       <c r="J317" t="n">
-        <v>20.3391</v>
+        <v>19.4508</v>
       </c>
     </row>
     <row r="318">
@@ -14655,10 +14655,10 @@
         <v>1.1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2459</v>
+        <v>0.2521</v>
       </c>
       <c r="J318" t="n">
-        <v>6.6393</v>
+        <v>6.8067</v>
       </c>
     </row>
     <row r="319">
@@ -14695,10 +14695,10 @@
         <v>0.98</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0361</v>
+        <v>-0.0428</v>
       </c>
       <c r="J319" t="n">
-        <v>-0.9747</v>
+        <v>-1.1556</v>
       </c>
     </row>
     <row r="320">
@@ -14735,10 +14735,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1455</v>
+        <v>-0.1584</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.9285</v>
+        <v>-4.2768</v>
       </c>
     </row>
     <row r="321">
@@ -14775,10 +14775,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3741</v>
+        <v>-0.3842</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.1007</v>
+        <v>-10.3734</v>
       </c>
     </row>
     <row r="322">
@@ -14815,10 +14815,10 @@
         <v>1.2</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4733</v>
+        <v>0.4591</v>
       </c>
       <c r="J322" t="n">
-        <v>14.199</v>
+        <v>13.773</v>
       </c>
     </row>
     <row r="323">
@@ -14855,10 +14855,10 @@
         <v>1.15</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3763</v>
+        <v>0.3692</v>
       </c>
       <c r="J323" t="n">
-        <v>11.289</v>
+        <v>11.076</v>
       </c>
     </row>
     <row r="324">
@@ -14895,10 +14895,10 @@
         <v>0.87</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1565</v>
+        <v>-0.1722</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.695</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="325">
@@ -14935,10 +14935,10 @@
         <v>0.79</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2378</v>
+        <v>-0.2536</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.134</v>
+        <v>-7.608</v>
       </c>
     </row>
     <row r="326">
@@ -14975,10 +14975,10 @@
         <v>0.53</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4831</v>
+        <v>-0.4901</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.493</v>
+        <v>-14.703</v>
       </c>
     </row>
     <row r="327">
@@ -15015,10 +15015,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9528</v>
+        <v>0.8944</v>
       </c>
       <c r="J327" t="n">
-        <v>28.584</v>
+        <v>26.832</v>
       </c>
     </row>
     <row r="328">
@@ -15055,10 +15055,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.888</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J328" t="n">
-        <v>26.64</v>
+        <v>25.056</v>
       </c>
     </row>
     <row r="329">
@@ -15095,10 +15095,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.7267</v>
+        <v>0.6935</v>
       </c>
       <c r="J329" t="n">
-        <v>21.801</v>
+        <v>20.805</v>
       </c>
     </row>
     <row r="330">
@@ -15135,10 +15135,10 @@
         <v>1.23</v>
       </c>
       <c r="I330" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="J330" t="n">
-        <v>18.978</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="331">
@@ -15175,10 +15175,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8243</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-24.729</v>
+        <v>-22.728</v>
       </c>
     </row>
     <row r="332">
@@ -15215,10 +15215,10 @@
         <v>0.95</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0209</v>
+        <v>-0.0433</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.4389</v>
+        <v>-0.9093</v>
       </c>
     </row>
     <row r="333">
@@ -15255,10 +15255,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2191</v>
+        <v>-0.2414</v>
       </c>
       <c r="J333" t="n">
-        <v>-4.6011</v>
+        <v>-5.0694</v>
       </c>
     </row>
     <row r="334">
@@ -15295,10 +15295,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3054</v>
+        <v>-0.3255</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.4134</v>
+        <v>-6.8355</v>
       </c>
     </row>
     <row r="335">
@@ -15335,10 +15335,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3693</v>
+        <v>-0.387</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.7553</v>
+        <v>-8.127000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15375,10 +15375,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5563</v>
+        <v>-0.5628</v>
       </c>
       <c r="J336" t="n">
-        <v>-11.6823</v>
+        <v>-11.8188</v>
       </c>
     </row>
     <row r="337">
@@ -15415,10 +15415,10 @@
         <v>1.7</v>
       </c>
       <c r="I337" t="n">
-        <v>0.7929</v>
+        <v>0.7885</v>
       </c>
       <c r="J337" t="n">
-        <v>16.6509</v>
+        <v>16.5585</v>
       </c>
     </row>
     <row r="338">
@@ -15455,10 +15455,10 @@
         <v>1.58</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6763</v>
       </c>
       <c r="J338" t="n">
-        <v>14.1099</v>
+        <v>14.2023</v>
       </c>
     </row>
     <row r="339">
@@ -15495,10 +15495,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4561</v>
+        <v>0.4721</v>
       </c>
       <c r="J339" t="n">
-        <v>9.578099999999999</v>
+        <v>9.914099999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15535,10 +15535,10 @@
         <v>1.25</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3207</v>
+        <v>0.3419</v>
       </c>
       <c r="J340" t="n">
-        <v>6.7347</v>
+        <v>7.1799</v>
       </c>
     </row>
     <row r="341">
@@ -15575,10 +15575,10 @@
         <v>1.17</v>
       </c>
       <c r="I341" t="n">
-        <v>0.2221</v>
+        <v>0.2456</v>
       </c>
       <c r="J341" t="n">
-        <v>4.6641</v>
+        <v>5.1576</v>
       </c>
     </row>
     <row r="342">
@@ -15615,10 +15615,10 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3767</v>
+        <v>0.3734</v>
       </c>
       <c r="J342" t="n">
-        <v>9.4175</v>
+        <v>9.335000000000001</v>
       </c>
     </row>
     <row r="343">
@@ -15655,10 +15655,10 @@
         <v>1.05</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1484</v>
+        <v>0.1544</v>
       </c>
       <c r="J343" t="n">
-        <v>3.71</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="344">
@@ -15695,10 +15695,10 @@
         <v>0.98</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0332</v>
+        <v>-0.0406</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.83</v>
+        <v>-1.015</v>
       </c>
     </row>
     <row r="345">
@@ -15735,10 +15735,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0723</v>
+        <v>-0.0833</v>
       </c>
       <c r="J345" t="n">
-        <v>-1.8075</v>
+        <v>-2.0825</v>
       </c>
     </row>
     <row r="346">
@@ -15775,10 +15775,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3693</v>
+        <v>-0.3805</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.2325</v>
+        <v>-9.512499999999999</v>
       </c>
     </row>
     <row r="347">
@@ -15815,10 +15815,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5831</v>
+        <v>0.5848</v>
       </c>
       <c r="J347" t="n">
-        <v>14.5775</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="348">
@@ -15855,10 +15855,10 @@
         <v>1.24</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3378</v>
+        <v>0.3521</v>
       </c>
       <c r="J348" t="n">
-        <v>8.445</v>
+        <v>8.8025</v>
       </c>
     </row>
     <row r="349">
@@ -15895,10 +15895,10 @@
         <v>1.21</v>
       </c>
       <c r="I349" t="n">
-        <v>0.301</v>
+        <v>0.3163</v>
       </c>
       <c r="J349" t="n">
-        <v>7.525</v>
+        <v>7.9075</v>
       </c>
     </row>
     <row r="350">
@@ -15935,10 +15935,10 @@
         <v>1.06</v>
       </c>
       <c r="I350" t="n">
-        <v>0.1009</v>
+        <v>0.1158</v>
       </c>
       <c r="J350" t="n">
-        <v>2.5225</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="351">
@@ -15975,10 +15975,10 @@
         <v>0.7</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3498</v>
+        <v>-0.3583</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.744999999999999</v>
+        <v>-8.9575</v>
       </c>
     </row>
     <row r="352">
@@ -16015,10 +16015,10 @@
         <v>1.15</v>
       </c>
       <c r="I352" t="n">
-        <v>0.2304</v>
+        <v>0.2457</v>
       </c>
       <c r="J352" t="n">
-        <v>6.2208</v>
+        <v>6.6339</v>
       </c>
     </row>
     <row r="353">
@@ -16055,10 +16055,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1768</v>
+        <v>0.1922</v>
       </c>
       <c r="J353" t="n">
-        <v>4.7736</v>
+        <v>5.1894</v>
       </c>
     </row>
     <row r="354">
@@ -16095,10 +16095,10 @@
         <v>1.1</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1631</v>
+        <v>0.1784</v>
       </c>
       <c r="J354" t="n">
-        <v>4.4037</v>
+        <v>4.8168</v>
       </c>
     </row>
     <row r="355">
@@ -16135,10 +16135,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.09</v>
+        <v>0.1031</v>
       </c>
       <c r="J355" t="n">
-        <v>2.43</v>
+        <v>2.7837</v>
       </c>
     </row>
     <row r="356">
@@ -16175,10 +16175,10 @@
         <v>1.04</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0736</v>
+        <v>0.0859</v>
       </c>
       <c r="J356" t="n">
-        <v>1.9872</v>
+        <v>2.3193</v>
       </c>
     </row>
     <row r="357">
@@ -16215,10 +16215,10 @@
         <v>1.4</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7597</v>
+        <v>0.7305</v>
       </c>
       <c r="J357" t="n">
-        <v>20.5119</v>
+        <v>19.7235</v>
       </c>
     </row>
     <row r="358">
@@ -16255,10 +16255,10 @@
         <v>1.14</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3088</v>
+        <v>0.3158</v>
       </c>
       <c r="J358" t="n">
-        <v>8.3376</v>
+        <v>8.5266</v>
       </c>
     </row>
     <row r="359">
@@ -16295,10 +16295,10 @@
         <v>1.06</v>
       </c>
       <c r="I359" t="n">
-        <v>0.1511</v>
+        <v>0.1626</v>
       </c>
       <c r="J359" t="n">
-        <v>4.0797</v>
+        <v>4.3902</v>
       </c>
     </row>
     <row r="360">
@@ -16335,10 +16335,10 @@
         <v>1.04</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1065</v>
+        <v>0.1178</v>
       </c>
       <c r="J360" t="n">
-        <v>2.8755</v>
+        <v>3.1806</v>
       </c>
     </row>
     <row r="361">
@@ -16375,10 +16375,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3343</v>
+        <v>-0.3444</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.0261</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="362">
@@ -16415,10 +16415,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6045</v>
+        <v>0.6087</v>
       </c>
       <c r="J362" t="n">
-        <v>13.299</v>
+        <v>13.3914</v>
       </c>
     </row>
     <row r="363">
@@ -16455,10 +16455,10 @@
         <v>1.34</v>
       </c>
       <c r="I363" t="n">
-        <v>0.439</v>
+        <v>0.4524</v>
       </c>
       <c r="J363" t="n">
-        <v>9.657999999999999</v>
+        <v>9.9528</v>
       </c>
     </row>
     <row r="364">
@@ -16495,10 +16495,10 @@
         <v>1.24</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3255</v>
+        <v>0.3429</v>
       </c>
       <c r="J364" t="n">
-        <v>7.161</v>
+        <v>7.5438</v>
       </c>
     </row>
     <row r="365">
@@ -16535,10 +16535,10 @@
         <v>1.23</v>
       </c>
       <c r="I365" t="n">
-        <v>0.3141</v>
+        <v>0.3316</v>
       </c>
       <c r="J365" t="n">
-        <v>6.9102</v>
+        <v>7.2952</v>
       </c>
     </row>
     <row r="366">
@@ -16575,10 +16575,10 @@
         <v>0.91</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.148</v>
+        <v>-0.1549</v>
       </c>
       <c r="J366" t="n">
-        <v>-3.256</v>
+        <v>-3.4078</v>
       </c>
     </row>
     <row r="367">
@@ -16615,10 +16615,10 @@
         <v>1.1</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3079</v>
+        <v>0.2975</v>
       </c>
       <c r="J367" t="n">
-        <v>6.7738</v>
+        <v>6.545</v>
       </c>
     </row>
     <row r="368">
@@ -16655,10 +16655,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0424</v>
+        <v>-0.0565</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.9328</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="369">
@@ -16695,10 +16695,10 @@
         <v>0.71</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3049</v>
+        <v>-0.3214</v>
       </c>
       <c r="J369" t="n">
-        <v>-6.7078</v>
+        <v>-7.0708</v>
       </c>
     </row>
     <row r="370">
@@ -16735,10 +16735,10 @@
         <v>0.7</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3145</v>
+        <v>-0.3306</v>
       </c>
       <c r="J370" t="n">
-        <v>-6.919</v>
+        <v>-7.2732</v>
       </c>
     </row>
     <row r="371">
@@ -16775,10 +16775,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.343</v>
+        <v>-0.3581</v>
       </c>
       <c r="J371" t="n">
-        <v>-7.546</v>
+        <v>-7.8782</v>
       </c>
     </row>
     <row r="372">
@@ -16815,10 +16815,10 @@
         <v>1.38</v>
       </c>
       <c r="I372" t="n">
-        <v>0.7268</v>
+        <v>0.7009</v>
       </c>
       <c r="J372" t="n">
-        <v>21.804</v>
+        <v>21.027</v>
       </c>
     </row>
     <row r="373">
@@ -16855,10 +16855,10 @@
         <v>1.22</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4545</v>
+        <v>0.4523</v>
       </c>
       <c r="J373" t="n">
-        <v>13.635</v>
+        <v>13.569</v>
       </c>
     </row>
     <row r="374">
@@ -16895,10 +16895,10 @@
         <v>0.98</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0426</v>
+        <v>-0.0478</v>
       </c>
       <c r="J374" t="n">
-        <v>-1.278</v>
+        <v>-1.434</v>
       </c>
     </row>
     <row r="375">
@@ -16935,10 +16935,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.0955</v>
+        <v>-0.1047</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.865</v>
+        <v>-3.141</v>
       </c>
     </row>
     <row r="376">
@@ -16975,10 +16975,10 @@
         <v>0.83</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2165</v>
+        <v>-0.2284</v>
       </c>
       <c r="J376" t="n">
-        <v>-6.495</v>
+        <v>-6.852</v>
       </c>
     </row>
     <row r="377">
@@ -17015,10 +17015,10 @@
         <v>1.33</v>
       </c>
       <c r="I377" t="n">
-        <v>0.9127</v>
+        <v>0.8488</v>
       </c>
       <c r="J377" t="n">
-        <v>27.381</v>
+        <v>25.464</v>
       </c>
     </row>
     <row r="378">
@@ -17055,10 +17055,10 @@
         <v>1.3</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8414</v>
+        <v>0.7863</v>
       </c>
       <c r="J378" t="n">
-        <v>25.242</v>
+        <v>23.589</v>
       </c>
     </row>
     <row r="379">
@@ -17095,10 +17095,10 @@
         <v>1.08</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2727</v>
+        <v>0.2757</v>
       </c>
       <c r="J379" t="n">
-        <v>8.180999999999999</v>
+        <v>8.271000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -17135,10 +17135,10 @@
         <v>0.95</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.215</v>
+        <v>-0.2125</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.45</v>
+        <v>-6.375</v>
       </c>
     </row>
     <row r="381">
@@ -17175,10 +17175,10 @@
         <v>0.67</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.8854</v>
       </c>
       <c r="J381" t="n">
-        <v>-28.956</v>
+        <v>-26.562</v>
       </c>
     </row>
     <row r="382">
@@ -17215,10 +17215,10 @@
         <v>1.53</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1845</v>
+        <v>1.1494</v>
       </c>
       <c r="J382" t="n">
-        <v>28.428</v>
+        <v>27.5856</v>
       </c>
     </row>
     <row r="383">
@@ -17255,10 +17255,10 @@
         <v>1.29</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7755</v>
+        <v>0.7361</v>
       </c>
       <c r="J383" t="n">
-        <v>18.612</v>
+        <v>17.6664</v>
       </c>
     </row>
     <row r="384">
@@ -17295,10 +17295,10 @@
         <v>1.24</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6581</v>
+        <v>0.6323</v>
       </c>
       <c r="J384" t="n">
-        <v>15.7944</v>
+        <v>15.1752</v>
       </c>
     </row>
     <row r="385">
@@ -17335,10 +17335,10 @@
         <v>1.03</v>
       </c>
       <c r="I385" t="n">
-        <v>0.089</v>
+        <v>0.1073</v>
       </c>
       <c r="J385" t="n">
-        <v>2.136</v>
+        <v>2.5752</v>
       </c>
     </row>
     <row r="386">
@@ -17375,10 +17375,10 @@
         <v>0.82</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6187</v>
+        <v>-0.5759</v>
       </c>
       <c r="J386" t="n">
-        <v>-14.8488</v>
+        <v>-13.8216</v>
       </c>
     </row>
     <row r="387">
@@ -17415,10 +17415,10 @@
         <v>1.1</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2715</v>
+        <v>0.2708</v>
       </c>
       <c r="J387" t="n">
-        <v>6.516</v>
+        <v>6.4992</v>
       </c>
     </row>
     <row r="388">
@@ -17455,10 +17455,10 @@
         <v>1.06</v>
       </c>
       <c r="I388" t="n">
-        <v>0.184</v>
+        <v>0.1863</v>
       </c>
       <c r="J388" t="n">
-        <v>4.416</v>
+        <v>4.4712</v>
       </c>
     </row>
     <row r="389">
@@ -17495,10 +17495,10 @@
         <v>0.95</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.0688</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J389" t="n">
-        <v>-1.6512</v>
+        <v>-1.9368</v>
       </c>
     </row>
     <row r="390">
@@ -17535,10 +17535,10 @@
         <v>0.86</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1678</v>
+        <v>-0.1834</v>
       </c>
       <c r="J390" t="n">
-        <v>-4.0272</v>
+        <v>-4.4016</v>
       </c>
     </row>
     <row r="391">
@@ -17575,10 +17575,10 @@
         <v>0.61</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4107</v>
+        <v>-0.421</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.8568</v>
+        <v>-10.104</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4998/event_4998_evp_summary.xlsx
+++ b/database/event/4998/event_4998_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.117800000000001</v>
+        <v>9.0975</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2627</v>
+        <v>1.2598</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5264</v>
+        <v>3.5386</v>
       </c>
       <c r="E2" t="n">
-        <v>9.117800000000001</v>
+        <v>9.0975</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5807</v>
+        <v>4.605</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5371</v>
+        <v>4.4924</v>
       </c>
       <c r="H2" t="n">
-        <v>16.3562</v>
+        <v>15.4897</v>
       </c>
       <c r="I2" t="n">
-        <v>8.8322</v>
+        <v>8.696999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5371</v>
+        <v>4.4924</v>
       </c>
       <c r="K2" t="n">
         <v>237</v>
@@ -529,7 +529,7 @@
         <v>181</v>
       </c>
       <c r="M2" t="n">
-        <v>13.3693</v>
+        <v>13.1894</v>
       </c>
       <c r="N2" t="n">
         <v>418</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8593</v>
+        <v>6.6705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9499</v>
+        <v>0.9237</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4983</v>
+        <v>2.4329</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8593</v>
+        <v>6.6705</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5807</v>
+        <v>4.4946</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2786</v>
+        <v>2.1759</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8659</v>
+        <v>10.4321</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8675</v>
+        <v>5.8573</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2786</v>
+        <v>2.1759</v>
       </c>
       <c r="K3" t="n">
         <v>237</v>
@@ -575,7 +575,7 @@
         <v>126</v>
       </c>
       <c r="M3" t="n">
-        <v>8.146100000000001</v>
+        <v>8.033200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>363</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8472</v>
+        <v>6.5474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9482</v>
+        <v>0.9067</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4928</v>
+        <v>2.3769</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8472</v>
+        <v>6.5474</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5807</v>
+        <v>4.3243</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2665</v>
+        <v>2.2231</v>
       </c>
       <c r="H4" t="n">
-        <v>10.6474</v>
+        <v>9.7927</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7495</v>
+        <v>5.4983</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2665</v>
+        <v>2.2231</v>
       </c>
       <c r="K4" t="n">
         <v>237</v>
@@ -621,7 +621,7 @@
         <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>8.016</v>
+        <v>7.721400000000001</v>
       </c>
       <c r="N4" t="n">
         <v>399</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7756</v>
+        <v>6.4875</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9383</v>
+        <v>0.8984</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4602</v>
+        <v>2.3496</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7756</v>
+        <v>6.4875</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7045</v>
+        <v>3.4899</v>
       </c>
       <c r="G5" t="n">
-        <v>3.071</v>
+        <v>2.9977</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3284</v>
+        <v>6.6599</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9573</v>
+        <v>3.7393</v>
       </c>
       <c r="J5" t="n">
-        <v>3.071</v>
+        <v>2.9977</v>
       </c>
       <c r="K5" t="n">
         <v>232</v>
@@ -667,7 +667,7 @@
         <v>177</v>
       </c>
       <c r="M5" t="n">
-        <v>7.0283</v>
+        <v>6.737</v>
       </c>
       <c r="N5" t="n">
         <v>409</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.5756</v>
+        <v>6.3379</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9106</v>
+        <v>0.8777</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3691</v>
+        <v>2.2814</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5756</v>
+        <v>6.3379</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3089</v>
+        <v>4.0706</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2667</v>
+        <v>2.2673</v>
       </c>
       <c r="H6" t="n">
-        <v>9.3224</v>
+        <v>8.840199999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>5.034</v>
+        <v>4.9635</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2667</v>
+        <v>2.2673</v>
       </c>
       <c r="K6" t="n">
         <v>232</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>7.3007</v>
+        <v>7.2308</v>
       </c>
       <c r="N6" t="n">
         <v>392</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9696</v>
+        <v>5.632</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8267</v>
+        <v>0.7799</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0933</v>
+        <v>1.9599</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9696</v>
+        <v>5.632</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5173</v>
+        <v>4.1668</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4523</v>
+        <v>1.4652</v>
       </c>
       <c r="H7" t="n">
-        <v>10.0102</v>
+        <v>9.2014</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4054</v>
+        <v>5.1663</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4523</v>
+        <v>1.4652</v>
       </c>
       <c r="K7" t="n">
         <v>237</v>
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>6.8577</v>
+        <v>6.6315</v>
       </c>
       <c r="N7" t="n">
         <v>399</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3142</v>
+        <v>5.2117</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7359</v>
+        <v>0.7217</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7949</v>
+        <v>1.7684</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3142</v>
+        <v>5.2117</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3399</v>
+        <v>3.241</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9743</v>
+        <v>1.9707</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1255</v>
+        <v>5.7253</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3077</v>
+        <v>3.2146</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9743</v>
+        <v>1.9707</v>
       </c>
       <c r="K8" t="n">
         <v>237</v>
@@ -805,7 +805,7 @@
         <v>179</v>
       </c>
       <c r="M8" t="n">
-        <v>5.282</v>
+        <v>5.1853</v>
       </c>
       <c r="N8" t="n">
         <v>416</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9363</v>
+        <v>3.6953</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5451</v>
+        <v>0.5117</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1677</v>
+        <v>1.0776</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9363</v>
+        <v>3.6953</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9731</v>
+        <v>3.7656</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0368</v>
+        <v>-0.0703</v>
       </c>
       <c r="H9" t="n">
-        <v>8.214600000000001</v>
+        <v>7.695</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4358</v>
+        <v>4.3205</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0368</v>
+        <v>-0.0703</v>
       </c>
       <c r="K9" t="n">
         <v>277</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>4.399</v>
+        <v>4.2502</v>
       </c>
       <c r="N9" t="n">
         <v>354</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7453</v>
+        <v>3.6307</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5187</v>
+        <v>0.5028</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0807</v>
+        <v>1.0482</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7453</v>
+        <v>3.6307</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1617</v>
+        <v>3.1082</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5836</v>
+        <v>0.5225</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5373</v>
+        <v>5.2268</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9901</v>
+        <v>2.9347</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5836</v>
+        <v>0.5225</v>
       </c>
       <c r="K10" t="n">
         <v>277</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5737</v>
+        <v>3.4572</v>
       </c>
       <c r="N10" t="n">
         <v>354</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2586</v>
+        <v>3.0238</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4513</v>
+        <v>0.4187</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8592</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2586</v>
+        <v>3.0238</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4783</v>
+        <v>3.2632</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2197</v>
+        <v>-0.2394</v>
       </c>
       <c r="H11" t="n">
-        <v>6.582</v>
+        <v>5.8087</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5542</v>
+        <v>3.2614</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2197</v>
+        <v>-0.2394</v>
       </c>
       <c r="K11" t="n">
         <v>277</v>
@@ -943,7 +943,7 @@
         <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3345</v>
+        <v>3.022</v>
       </c>
       <c r="N11" t="n">
         <v>354</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5359</v>
+        <v>2.4658</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3512</v>
+        <v>0.3415</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5302</v>
+        <v>0.5175</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5359</v>
+        <v>2.4658</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5359</v>
+        <v>2.4658</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8254</v>
+        <v>2.7007</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0495</v>
+        <v>2.923</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0495</v>
+        <v>2.923</v>
       </c>
       <c r="N12" t="n">
         <v>263</v>
@@ -998,277 +998,277 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5342</v>
+        <v>1.3714</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2125</v>
+        <v>0.1899</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0742</v>
+        <v>0.019</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5342</v>
+        <v>1.3714</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5342</v>
+        <v>1.3714</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5342</v>
+        <v>1.3714</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6559</v>
+        <v>1.4843</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6559</v>
+        <v>1.4843</v>
       </c>
       <c r="N13" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4399</v>
+        <v>1.3457</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1994</v>
+        <v>0.1864</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0313</v>
+        <v>0.0072</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4399</v>
+        <v>1.3457</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4399</v>
+        <v>1.3457</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4399</v>
+        <v>1.3457</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5541</v>
+        <v>1.4565</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5541</v>
+        <v>1.4565</v>
       </c>
       <c r="N14" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4089</v>
+        <v>1.2254</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1951</v>
+        <v>0.1697</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0172</v>
+        <v>-0.0476</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4089</v>
+        <v>1.2254</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1396</v>
+        <v>1.2254</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2693</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1396</v>
+        <v>1.2254</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6153999999999999</v>
+        <v>1.3263</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2693</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="L15" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8846999999999999</v>
+        <v>1.3263</v>
       </c>
       <c r="N15" t="n">
-        <v>392</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4036</v>
+        <v>1.0935</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1944</v>
+        <v>0.1514</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0147</v>
+        <v>-0.1076</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4036</v>
+        <v>1.0935</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4036</v>
+        <v>0.8768</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.2167</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4036</v>
+        <v>0.8768</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5149</v>
+        <v>0.4923</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.2167</v>
       </c>
       <c r="K16" t="n">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5149</v>
+        <v>0.7090000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>263</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.334</v>
+        <v>1.0216</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1847</v>
+        <v>0.1415</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0169</v>
+        <v>-0.1404</v>
       </c>
       <c r="E17" t="n">
-        <v>1.334</v>
+        <v>1.0216</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2037</v>
+        <v>1.0216</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1303</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2037</v>
+        <v>1.0216</v>
       </c>
       <c r="I17" t="n">
-        <v>0.65</v>
+        <v>1.1057</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1303</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L17" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7803</v>
+        <v>1.1057</v>
       </c>
       <c r="N17" t="n">
-        <v>335</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2319</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1706</v>
+        <v>0.1112</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0634</v>
+        <v>-0.24</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2319</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2319</v>
+        <v>0.6839</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2319</v>
+        <v>0.6839</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3296</v>
+        <v>0.384</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="K18" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3296</v>
+        <v>0.503</v>
       </c>
       <c r="N18" t="n">
-        <v>263</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1382</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1576</v>
+        <v>0.1064</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1061</v>
+        <v>-0.2557</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1382</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1382</v>
+        <v>1.7686</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1604</v>
+        <v>1.7686</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1666</v>
+        <v>0.993</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1666000000000001</v>
+        <v>-0.007000000000000006</v>
       </c>
       <c r="N19" t="n">
         <v>354</v>
@@ -1320,78 +1320,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5802</v>
+        <v>0.2992</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0803</v>
+        <v>0.0414</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3601</v>
+        <v>-0.4695</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5802</v>
+        <v>0.2992</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0794</v>
+        <v>0.2992</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5008</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0794</v>
+        <v>0.2992</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0429</v>
+        <v>0.3239</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5008</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="L20" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5437000000000001</v>
+        <v>0.3239</v>
       </c>
       <c r="N20" t="n">
-        <v>335</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.488</v>
+        <v>0.2702</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0374</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4021</v>
+        <v>-0.4827</v>
       </c>
       <c r="E21" t="n">
-        <v>0.488</v>
+        <v>0.2702</v>
       </c>
       <c r="F21" t="n">
-        <v>0.488</v>
+        <v>0.2702</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.488</v>
+        <v>0.2702</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.2924</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.2924</v>
       </c>
       <c r="N21" t="n">
         <v>247</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4524</v>
+        <v>0.1418</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0626</v>
+        <v>0.0196</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4183</v>
+        <v>-0.5412</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4524</v>
+        <v>0.1418</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4524</v>
+        <v>0.1418</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4524</v>
+        <v>0.1418</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4883</v>
+        <v>0.1535</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4883</v>
+        <v>0.1535</v>
       </c>
       <c r="N22" t="n">
         <v>247</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3407</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0472</v>
+        <v>0.0128</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4691</v>
+        <v>-0.5637</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3407</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3407</v>
+        <v>-0.3234</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.4157</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3407</v>
+        <v>-0.3234</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3677</v>
+        <v>-0.1816</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.4157</v>
       </c>
       <c r="K23" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3677</v>
+        <v>0.2341</v>
       </c>
       <c r="N23" t="n">
-        <v>247</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1638</v>
+        <v>-0.194</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0227</v>
+        <v>-0.0269</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5496</v>
+        <v>-0.6942</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1638</v>
+        <v>-0.194</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3896</v>
+        <v>0.037</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2258</v>
+        <v>-0.231</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3896</v>
+        <v>0.037</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2104</v>
+        <v>0.0208</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2258</v>
+        <v>-0.231</v>
       </c>
       <c r="K24" t="n">
         <v>256</v>
@@ -1541,7 +1541,7 @@
         <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0154</v>
+        <v>-0.2102</v>
       </c>
       <c r="N24" t="n">
         <v>335</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1831</v>
+        <v>-0.2283</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7076</v>
+        <v>-0.7098</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1831</v>
+        <v>-0.2283</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1831</v>
+        <v>-0.2283</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1831</v>
+        <v>-0.2283</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1976</v>
+        <v>-0.2471</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1976</v>
+        <v>-0.2471</v>
       </c>
       <c r="N25" t="n">
         <v>247</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1946</v>
+        <v>-0.3526</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0269</v>
+        <v>-0.0488</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7128</v>
+        <v>-0.7664</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1946</v>
+        <v>-0.3526</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1932</v>
+        <v>-1.2961</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9986</v>
+        <v>0.9435</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1932</v>
+        <v>-1.2961</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6443</v>
+        <v>-0.7277</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9986</v>
+        <v>0.9435</v>
       </c>
       <c r="K26" t="n">
         <v>232</v>
@@ -1633,7 +1633,7 @@
         <v>143</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3543000000000001</v>
+        <v>0.2158</v>
       </c>
       <c r="N26" t="n">
         <v>375</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3126</v>
+        <v>-0.4633</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0433</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7665</v>
+        <v>-0.8168</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3126</v>
+        <v>-0.4633</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9993</v>
+        <v>-1.095</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6867</v>
+        <v>0.6317</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9993</v>
+        <v>-1.095</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5396</v>
+        <v>-0.6148</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6867</v>
+        <v>0.6317</v>
       </c>
       <c r="K27" t="n">
         <v>256</v>
@@ -1679,7 +1679,7 @@
         <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1471</v>
+        <v>0.01690000000000003</v>
       </c>
       <c r="N27" t="n">
         <v>335</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6433</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0891</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.917</v>
+        <v>-0.9095</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6433</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3567</v>
+        <v>0.3199</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>-0.9867</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3567</v>
+        <v>0.3199</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1926</v>
+        <v>0.1796</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>-0.9867</v>
       </c>
       <c r="K28" t="n">
         <v>277</v>
@@ -1725,7 +1725,7 @@
         <v>77</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8074</v>
+        <v>-0.8071</v>
       </c>
       <c r="N28" t="n">
         <v>354</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1385</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0794</v>
+        <v>-1.0613</v>
       </c>
       <c r="E29" t="n">
         <v>-1</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.8961</v>
+        <v>-1.8613</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2626</v>
+        <v>-0.2578</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.4873</v>
+        <v>-1.4537</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.8961</v>
+        <v>-1.8613</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.6597</v>
+        <v>-2.6219</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.6597</v>
+        <v>-2.6219</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4362</v>
+        <v>-1.4721</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>232</v>
@@ -1817,7 +1817,7 @@
         <v>113</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6726</v>
+        <v>-0.7114999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>345</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.7627</v>
+        <v>-2.8198</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3826</v>
+        <v>-0.3905</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8818</v>
+        <v>-1.8903</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.7627</v>
+        <v>-2.8198</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.8871</v>
+        <v>-1.9591</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8756</v>
+        <v>-0.8607</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8871</v>
+        <v>-1.9591</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.019</v>
+        <v>-1.1</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8756</v>
+        <v>-0.8607</v>
       </c>
       <c r="K31" t="n">
         <v>256</v>
@@ -1863,7 +1863,7 @@
         <v>79</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.8946</v>
+        <v>-1.9607</v>
       </c>
       <c r="N31" t="n">
         <v>335</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.0237</v>
+        <v>-3.9036</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.5572</v>
+        <v>-0.5406</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.4559</v>
+        <v>-2.3841</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.0237</v>
+        <v>-3.9036</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.0237</v>
+        <v>-3.9036</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-4.0237</v>
+        <v>-3.9036</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.3428</v>
+        <v>-4.225</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-4.3428</v>
+        <v>-4.225</v>
       </c>
       <c r="N32" t="n">
         <v>263</v>
@@ -2015,10 +2015,10 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5838</v>
+        <v>0.5525</v>
       </c>
       <c r="J2" t="n">
-        <v>21.0168</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4038</v>
+        <v>0.3707</v>
       </c>
       <c r="J3" t="n">
-        <v>14.5368</v>
+        <v>13.3452</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0607</v>
+        <v>0.0445</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1852</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>0.998</v>
+        <v>0.9906</v>
       </c>
       <c r="J5" t="n">
-        <v>35.928</v>
+        <v>35.6616</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>33.1884</v>
+        <v>32.6808</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5553</v>
+        <v>0.4956</v>
       </c>
       <c r="J7" t="n">
-        <v>19.9908</v>
+        <v>17.8416</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2659</v>
+        <v>-0.2466</v>
       </c>
       <c r="J8" t="n">
-        <v>-9.5724</v>
+        <v>-8.877599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3511</v>
+        <v>-0.3369</v>
       </c>
       <c r="J9" t="n">
-        <v>-12.6396</v>
+        <v>-12.1284</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4748</v>
+        <v>0.4161</v>
       </c>
       <c r="J10" t="n">
-        <v>17.0928</v>
+        <v>14.9796</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.425</v>
+        <v>0.3678</v>
       </c>
       <c r="J11" t="n">
-        <v>15.3</v>
+        <v>13.2408</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.25</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4378</v>
+        <v>0.4445</v>
       </c>
       <c r="J12" t="n">
-        <v>7.4426</v>
+        <v>7.5565</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2837</v>
+        <v>0.2728</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8229</v>
+        <v>4.6376</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.62</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4076</v>
+        <v>-0.397</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.9292</v>
+        <v>-6.749</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3443</v>
+        <v>-0.3287</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.8531</v>
+        <v>-5.5879</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3807</v>
+        <v>-0.3678</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.4719</v>
+        <v>-6.2526</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>0.09</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8478</v>
+        <v>-0.9169</v>
       </c>
       <c r="J17" t="n">
-        <v>-14.4126</v>
+        <v>-15.5873</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9117</v>
+        <v>-0.9983</v>
       </c>
       <c r="J18" t="n">
-        <v>-15.4989</v>
+        <v>-16.9711</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9197</v>
+        <v>-1.0086</v>
       </c>
       <c r="J19" t="n">
-        <v>-15.6349</v>
+        <v>-17.1462</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>2.15</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4264</v>
+        <v>1.4694</v>
       </c>
       <c r="J20" t="n">
-        <v>24.2488</v>
+        <v>24.9798</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>1.87</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1361</v>
+        <v>1.1349</v>
       </c>
       <c r="J21" t="n">
-        <v>19.3137</v>
+        <v>19.2933</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3777</v>
+        <v>1.4145</v>
       </c>
       <c r="J22" t="n">
-        <v>41.331</v>
+        <v>42.435</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.66</v>
       </c>
       <c r="I23" t="n">
-        <v>1.361</v>
+        <v>1.3972</v>
       </c>
       <c r="J23" t="n">
-        <v>40.83</v>
+        <v>41.916</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>1.51</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1047</v>
+        <v>1.1159</v>
       </c>
       <c r="J24" t="n">
-        <v>33.141</v>
+        <v>33.477</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>1.29</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6992</v>
+        <v>0.6802</v>
       </c>
       <c r="J25" t="n">
-        <v>20.976</v>
+        <v>20.406</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>1.16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4179</v>
+        <v>0.3864</v>
       </c>
       <c r="J26" t="n">
-        <v>12.537</v>
+        <v>11.592</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>0.87</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1679</v>
+        <v>-0.1507</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.037</v>
+        <v>-4.521</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>0.62</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4049</v>
+        <v>-0.3939</v>
       </c>
       <c r="J28" t="n">
-        <v>-12.147</v>
+        <v>-11.817</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5357</v>
+        <v>-0.5403</v>
       </c>
       <c r="J29" t="n">
-        <v>-16.071</v>
+        <v>-16.209</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.22</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5175</v>
+        <v>0.4656</v>
       </c>
       <c r="J30" t="n">
-        <v>15.525</v>
+        <v>13.968</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1581</v>
+        <v>0.1238</v>
       </c>
       <c r="J31" t="n">
-        <v>4.743</v>
+        <v>3.714</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6528</v>
+        <v>0.7065</v>
       </c>
       <c r="J32" t="n">
-        <v>18.2784</v>
+        <v>19.782</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>0.89</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1453</v>
+        <v>-0.1291</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.0684</v>
+        <v>-3.6148</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>0.76</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2753</v>
+        <v>-0.2571</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.7084</v>
+        <v>-7.1988</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>0.63</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3951</v>
+        <v>-0.3832</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.0628</v>
+        <v>-10.7296</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5689</v>
+        <v>-0.5786</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.9292</v>
+        <v>-16.2008</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.43</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.477</v>
       </c>
       <c r="J37" t="n">
-        <v>14.5208</v>
+        <v>13.356</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>1.41</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5032</v>
+        <v>0.4575</v>
       </c>
       <c r="J38" t="n">
-        <v>14.0896</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3868</v>
+        <v>0.3272</v>
       </c>
       <c r="J39" t="n">
-        <v>10.8304</v>
+        <v>9.1616</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2077</v>
+        <v>0.1668</v>
       </c>
       <c r="J40" t="n">
-        <v>5.8156</v>
+        <v>4.6704</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0614</v>
+        <v>-0.0493</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7192</v>
+        <v>-1.3804</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0118</v>
+        <v>0.9997</v>
       </c>
       <c r="J42" t="n">
-        <v>23.2714</v>
+        <v>22.9931</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7927</v>
+        <v>0.7785</v>
       </c>
       <c r="J43" t="n">
-        <v>18.2321</v>
+        <v>17.9055</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7359</v>
+        <v>0.7228</v>
       </c>
       <c r="J44" t="n">
-        <v>16.9257</v>
+        <v>16.6244</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2463</v>
+        <v>0.2161</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6649</v>
+        <v>4.9703</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2784</v>
+        <v>-0.2413</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.4032</v>
+        <v>-5.5499</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4765</v>
+        <v>0.4488</v>
       </c>
       <c r="J47" t="n">
-        <v>10.9595</v>
+        <v>10.3224</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>0.83</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1989</v>
+        <v>-0.1832</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.5747</v>
+        <v>-4.2136</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.73</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2947</v>
+        <v>-0.279</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.7781</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.64</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3761</v>
+        <v>-0.3631</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.6503</v>
+        <v>-8.3513</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.36</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6203</v>
+        <v>-0.6374</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.2669</v>
+        <v>-14.6602</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9886</v>
+        <v>0.9766</v>
       </c>
       <c r="J52" t="n">
-        <v>27.6808</v>
+        <v>27.3448</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1821</v>
+        <v>0.1543</v>
       </c>
       <c r="J53" t="n">
-        <v>5.0988</v>
+        <v>4.3204</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.117</v>
+        <v>0.0954</v>
       </c>
       <c r="J54" t="n">
-        <v>3.276</v>
+        <v>2.6712</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0636</v>
       </c>
       <c r="J55" t="n">
-        <v>2.2596</v>
+        <v>1.7808</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>1.02</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0636</v>
       </c>
       <c r="J56" t="n">
-        <v>2.2596</v>
+        <v>1.7808</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4901</v>
+        <v>0.4516</v>
       </c>
       <c r="J57" t="n">
-        <v>13.7228</v>
+        <v>12.6448</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0936</v>
+        <v>-0.079</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.6208</v>
+        <v>-2.212</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1939</v>
+        <v>-0.174</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.4292</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2346</v>
+        <v>-0.2146</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.5688</v>
+        <v>-6.0088</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.293</v>
+        <v>-0.2746</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.204000000000001</v>
+        <v>-7.6888</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4663</v>
+        <v>0.482</v>
       </c>
       <c r="J62" t="n">
-        <v>13.0564</v>
+        <v>13.496</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4364</v>
+        <v>0.4407</v>
       </c>
       <c r="J63" t="n">
-        <v>12.2192</v>
+        <v>12.3396</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0562</v>
+        <v>0.0455</v>
       </c>
       <c r="J64" t="n">
-        <v>1.5736</v>
+        <v>1.274</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2135</v>
+        <v>-0.1929</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.978</v>
+        <v>-5.4012</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4034</v>
+        <v>-0.3938</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.2952</v>
+        <v>-11.0264</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.4</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.461</v>
       </c>
       <c r="J67" t="n">
-        <v>14.1848</v>
+        <v>12.908</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.34</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4577</v>
+        <v>0.3983</v>
       </c>
       <c r="J68" t="n">
-        <v>12.8156</v>
+        <v>11.1524</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3863</v>
+        <v>0.3244</v>
       </c>
       <c r="J69" t="n">
-        <v>10.8164</v>
+        <v>9.0832</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1228</v>
+        <v>-0.1043</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.4384</v>
+        <v>-2.9204</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3124</v>
+        <v>-0.2964</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.747199999999999</v>
+        <v>-8.299200000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.92</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4484</v>
+        <v>1.4621</v>
       </c>
       <c r="J72" t="n">
-        <v>30.4164</v>
+        <v>30.7041</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9244</v>
+        <v>0.9134</v>
       </c>
       <c r="J73" t="n">
-        <v>19.4124</v>
+        <v>19.1814</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>1.3</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6523</v>
+        <v>0.6464</v>
       </c>
       <c r="J74" t="n">
-        <v>13.6983</v>
+        <v>13.5744</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>1.2</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4972</v>
+        <v>0.4882</v>
       </c>
       <c r="J75" t="n">
-        <v>10.4412</v>
+        <v>10.2522</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1966</v>
+        <v>0.1664</v>
       </c>
       <c r="J76" t="n">
-        <v>4.1286</v>
+        <v>3.4944</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1396</v>
+        <v>0.1296</v>
       </c>
       <c r="J77" t="n">
-        <v>2.9316</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>0.73</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2877</v>
+        <v>-0.2745</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.0417</v>
+        <v>-5.7645</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>0.6</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4027</v>
+        <v>-0.3924</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.4567</v>
+        <v>-8.240399999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4292</v>
+        <v>-0.4207</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.013199999999999</v>
+        <v>-8.8347</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5172</v>
+        <v>-0.5174</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.8612</v>
+        <v>-10.8654</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0165</v>
+        <v>1.0048</v>
       </c>
       <c r="J82" t="n">
-        <v>28.462</v>
+        <v>28.1344</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.49</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9234</v>
+        <v>0.91</v>
       </c>
       <c r="J83" t="n">
-        <v>25.8552</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.42</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8282</v>
+        <v>0.8148</v>
       </c>
       <c r="J84" t="n">
-        <v>23.1896</v>
+        <v>22.8144</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3186</v>
+        <v>0.2867</v>
       </c>
       <c r="J85" t="n">
-        <v>8.9208</v>
+        <v>8.0276</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.96</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2235</v>
+        <v>-0.1911</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.258</v>
+        <v>-5.3508</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0137</v>
+        <v>-0.0054</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.3836</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.89</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1354</v>
+        <v>-0.1202</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.7912</v>
+        <v>-3.3656</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.7</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3236</v>
+        <v>-0.308</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.0608</v>
+        <v>-8.624000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.378</v>
+        <v>-0.365</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.584</v>
+        <v>-10.22</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4048</v>
+        <v>-0.3937</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.3344</v>
+        <v>-11.0236</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.05</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2316</v>
+        <v>0.2016</v>
       </c>
       <c r="J92" t="n">
-        <v>4.8636</v>
+        <v>4.2336</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>0.75</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2742</v>
+        <v>-0.2595</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.7582</v>
+        <v>-5.4495</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>0.73</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2926</v>
+        <v>-0.278</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.1446</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3992</v>
+        <v>-0.388</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.3832</v>
+        <v>-8.148</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.45</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5435</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.3358</v>
+        <v>-11.4135</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.91</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5874</v>
+        <v>1.6261</v>
       </c>
       <c r="J97" t="n">
-        <v>33.3354</v>
+        <v>34.1481</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1.39</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8999</v>
+        <v>0.8908</v>
       </c>
       <c r="J98" t="n">
-        <v>18.8979</v>
+        <v>18.7068</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>1.29</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7098</v>
+        <v>0.6892</v>
       </c>
       <c r="J99" t="n">
-        <v>14.9058</v>
+        <v>14.4732</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5203</v>
+        <v>0.4916</v>
       </c>
       <c r="J100" t="n">
-        <v>10.9263</v>
+        <v>10.3236</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>1.12</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3323</v>
+        <v>0.3002</v>
       </c>
       <c r="J101" t="n">
-        <v>6.9783</v>
+        <v>6.3042</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3153</v>
+        <v>1.3364</v>
       </c>
       <c r="J102" t="n">
-        <v>32.8825</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.3153</v>
+        <v>1.3364</v>
       </c>
       <c r="J103" t="n">
-        <v>32.8825</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1017</v>
+        <v>0.0813</v>
       </c>
       <c r="J104" t="n">
-        <v>2.5425</v>
+        <v>2.0325</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2397</v>
+        <v>-0.2034</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.9925</v>
+        <v>-5.085</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>0.77</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6955</v>
+        <v>-0.6667</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.3875</v>
+        <v>-16.6675</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5952</v>
+        <v>0.5434</v>
       </c>
       <c r="J107" t="n">
-        <v>14.88</v>
+        <v>13.585</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>2.4775</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1012</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.53</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2782</v>
+        <v>-0.2596</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.955</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.34</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6464</v>
+        <v>-0.6701</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.16</v>
+        <v>-16.7525</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6483</v>
+        <v>0.5958</v>
       </c>
       <c r="J112" t="n">
-        <v>14.9109</v>
+        <v>13.7034</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>0.95</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0789</v>
+        <v>-0.066</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.8147</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2327</v>
+        <v>-0.2129</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.3521</v>
+        <v>-4.8967</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2814</v>
+        <v>-0.2627</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.4722</v>
+        <v>-6.0421</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3834</v>
+        <v>-0.3708</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.818199999999999</v>
+        <v>-8.5284</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8907</v>
+        <v>0.873</v>
       </c>
       <c r="J117" t="n">
-        <v>20.4861</v>
+        <v>20.079</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6822</v>
       </c>
       <c r="J118" t="n">
-        <v>16.3576</v>
+        <v>15.6906</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>1.26</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6702</v>
+        <v>0.6395</v>
       </c>
       <c r="J119" t="n">
-        <v>15.4146</v>
+        <v>14.7085</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3849</v>
+        <v>0.3509</v>
       </c>
       <c r="J120" t="n">
-        <v>8.8527</v>
+        <v>8.0707</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0945</v>
+        <v>-0.0736</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.1735</v>
+        <v>-1.6928</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8132</v>
+        <v>0.7877</v>
       </c>
       <c r="J122" t="n">
-        <v>24.396</v>
+        <v>23.631</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4898</v>
+        <v>0.4508</v>
       </c>
       <c r="J123" t="n">
-        <v>14.694</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2968</v>
+        <v>0.2617</v>
       </c>
       <c r="J124" t="n">
-        <v>8.904</v>
+        <v>7.851</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2137</v>
+        <v>0.1833</v>
       </c>
       <c r="J125" t="n">
-        <v>6.411</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2524</v>
+        <v>-0.2135</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.572</v>
+        <v>-6.405</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4695</v>
+        <v>0.4111</v>
       </c>
       <c r="J127" t="n">
-        <v>14.085</v>
+        <v>12.333</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1491</v>
+        <v>0.1147</v>
       </c>
       <c r="J128" t="n">
-        <v>4.473</v>
+        <v>3.441</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0441</v>
+        <v>0.0297</v>
       </c>
       <c r="J129" t="n">
-        <v>1.323</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.123</v>
+        <v>-0.1046</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.69</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2907</v>
+        <v>-0.2723</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.721</v>
+        <v>-8.169</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.12</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3733</v>
+        <v>0.3322</v>
       </c>
       <c r="J132" t="n">
-        <v>8.2126</v>
+        <v>7.3084</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>0.95</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.056</v>
+        <v>-0.0432</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.232</v>
+        <v>-0.9504</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>0.58</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4293</v>
+        <v>-0.4203</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.444599999999999</v>
+        <v>-9.246600000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.447</v>
+        <v>-0.4397</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.834</v>
+        <v>-9.673400000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4822</v>
+        <v>-0.4786</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6084</v>
+        <v>-10.5292</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.84</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5141</v>
+        <v>1.5474</v>
       </c>
       <c r="J137" t="n">
-        <v>33.3102</v>
+        <v>34.0428</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.51</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0937</v>
+        <v>1.106</v>
       </c>
       <c r="J138" t="n">
-        <v>24.0614</v>
+        <v>24.332</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>1.18</v>
       </c>
       <c r="I139" t="n">
-        <v>0.483</v>
+        <v>0.4525</v>
       </c>
       <c r="J139" t="n">
-        <v>10.626</v>
+        <v>9.955</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2069</v>
+        <v>0.1775</v>
       </c>
       <c r="J140" t="n">
-        <v>4.5518</v>
+        <v>3.905</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1778</v>
+        <v>0.1497</v>
       </c>
       <c r="J141" t="n">
-        <v>3.9116</v>
+        <v>3.2934</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.85</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5264</v>
+        <v>1.5607</v>
       </c>
       <c r="J142" t="n">
-        <v>35.1072</v>
+        <v>35.8961</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.56</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1597</v>
+        <v>1.1738</v>
       </c>
       <c r="J143" t="n">
-        <v>26.6731</v>
+        <v>26.9974</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5714</v>
+        <v>0.5434</v>
       </c>
       <c r="J144" t="n">
-        <v>13.1422</v>
+        <v>12.4982</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2888</v>
+        <v>0.2573</v>
       </c>
       <c r="J145" t="n">
-        <v>6.6424</v>
+        <v>5.9179</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3189</v>
+        <v>-0.2826</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.3347</v>
+        <v>-6.4998</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.14</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3764</v>
+        <v>0.3264</v>
       </c>
       <c r="J147" t="n">
-        <v>8.6572</v>
+        <v>7.5072</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0771</v>
+        <v>0.0577</v>
       </c>
       <c r="J148" t="n">
-        <v>1.7733</v>
+        <v>1.3271</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0075</v>
+        <v>-0.0031</v>
       </c>
       <c r="J149" t="n">
-        <v>-0.1725</v>
+        <v>-0.0713</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3855</v>
+        <v>-0.3728</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.8665</v>
+        <v>-8.574400000000001</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.37</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6189</v>
+        <v>-0.637</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.2347</v>
+        <v>-14.651</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.76</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8328</v>
+        <v>0.7627</v>
       </c>
       <c r="J152" t="n">
-        <v>15.8232</v>
+        <v>14.4913</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6965</v>
+        <v>0.6272</v>
       </c>
       <c r="J153" t="n">
-        <v>13.2335</v>
+        <v>11.9168</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.42</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5171</v>
+        <v>0.4547</v>
       </c>
       <c r="J154" t="n">
-        <v>9.8249</v>
+        <v>8.6393</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>1.39</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4868</v>
+        <v>0.4258</v>
       </c>
       <c r="J155" t="n">
-        <v>9.2492</v>
+        <v>8.090199999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>1.33</v>
       </c>
       <c r="I156" t="n">
-        <v>0.4239</v>
+        <v>0.3664</v>
       </c>
       <c r="J156" t="n">
-        <v>8.0541</v>
+        <v>6.9616</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>0.73</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.245</v>
+        <v>-0.2268</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.655</v>
+        <v>-4.3092</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>0.53</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.4419</v>
+        <v>-0.4398</v>
       </c>
       <c r="J158" t="n">
-        <v>-8.396100000000001</v>
+        <v>-8.356199999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>0.48</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4831</v>
+        <v>-0.4822</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.178900000000001</v>
+        <v>-9.161799999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.42</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5356</v>
+        <v>-0.5382</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.1764</v>
+        <v>-10.2258</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.38</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5714</v>
+        <v>-0.5779</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.8566</v>
+        <v>-10.9801</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3741</v>
+        <v>0.3123</v>
       </c>
       <c r="J162" t="n">
-        <v>11.223</v>
+        <v>9.369</v>
       </c>
     </row>
     <row r="163">
@@ -8455,10 +8455,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3621</v>
+        <v>0.3012</v>
       </c>
       <c r="J163" t="n">
-        <v>10.863</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="164">
@@ -8495,10 +8495,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0292</v>
+        <v>-0.0207</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.876</v>
+        <v>-0.621</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1037</v>
+        <v>-0.0861</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.111</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1853</v>
+        <v>-0.1647</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.559</v>
+        <v>-4.941</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.47</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8215</v>
+        <v>0.7674</v>
       </c>
       <c r="J167" t="n">
-        <v>24.645</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.29</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5562</v>
+        <v>0.4966</v>
       </c>
       <c r="J168" t="n">
-        <v>16.686</v>
+        <v>14.898</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3456</v>
+        <v>0.2942</v>
       </c>
       <c r="J169" t="n">
-        <v>10.368</v>
+        <v>8.826000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2212</v>
+        <v>-0.2011</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.636</v>
+        <v>-6.033</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2813</v>
+        <v>-0.2632</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.439</v>
+        <v>-7.896</v>
       </c>
     </row>
     <row r="172">
@@ -8815,10 +8815,10 @@
         <v>1.91</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5573</v>
+        <v>1.5932</v>
       </c>
       <c r="J172" t="n">
-        <v>28.0314</v>
+        <v>28.6776</v>
       </c>
     </row>
     <row r="173">
@@ -8855,10 +8855,10 @@
         <v>1.76</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3797</v>
+        <v>1.4052</v>
       </c>
       <c r="J173" t="n">
-        <v>24.8346</v>
+        <v>25.2936</v>
       </c>
     </row>
     <row r="174">
@@ -8895,10 +8895,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.92</v>
+        <v>0.9191</v>
       </c>
       <c r="J174" t="n">
-        <v>16.56</v>
+        <v>16.5438</v>
       </c>
     </row>
     <row r="175">
@@ -8935,10 +8935,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8587</v>
       </c>
       <c r="J175" t="n">
-        <v>15.5592</v>
+        <v>15.4566</v>
       </c>
     </row>
     <row r="176">
@@ -8975,10 +8975,10 @@
         <v>1.21</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5204</v>
+        <v>0.4921</v>
       </c>
       <c r="J176" t="n">
-        <v>9.3672</v>
+        <v>8.857799999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9015,10 +9015,10 @@
         <v>0.9</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.0791</v>
+        <v>-0.0546</v>
       </c>
       <c r="J177" t="n">
-        <v>-1.4238</v>
+        <v>-0.9828</v>
       </c>
     </row>
     <row r="178">
@@ -9055,10 +9055,10 @@
         <v>0.73</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2714</v>
+        <v>-0.2585</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.8852</v>
+        <v>-4.653</v>
       </c>
     </row>
     <row r="179">
@@ -9095,10 +9095,10 @@
         <v>0.62</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3761</v>
+        <v>-0.3681</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.7698</v>
+        <v>-6.6258</v>
       </c>
     </row>
     <row r="180">
@@ -9135,10 +9135,10 @@
         <v>0.38</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5848</v>
+        <v>-0.5937</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.5264</v>
+        <v>-10.6866</v>
       </c>
     </row>
     <row r="181">
@@ -9175,10 +9175,10 @@
         <v>0.33</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.629</v>
+        <v>-0.6452</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.322</v>
+        <v>-11.6136</v>
       </c>
     </row>
     <row r="182">
@@ -9215,10 +9215,10 @@
         <v>1.01</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0985</v>
+        <v>0.0806</v>
       </c>
       <c r="J182" t="n">
-        <v>2.364</v>
+        <v>1.9344</v>
       </c>
     </row>
     <row r="183">
@@ -9255,10 +9255,10 @@
         <v>0.9</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.124</v>
+        <v>-0.1091</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.976</v>
+        <v>-2.6184</v>
       </c>
     </row>
     <row r="184">
@@ -9295,10 +9295,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2217</v>
+        <v>-0.2055</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.3208</v>
+        <v>-4.932</v>
       </c>
     </row>
     <row r="185">
@@ -9335,10 +9335,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4317</v>
+        <v>-0.423</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.3608</v>
+        <v>-10.152</v>
       </c>
     </row>
     <row r="186">
@@ -9375,10 +9375,10 @@
         <v>0.53</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4757</v>
+        <v>-0.4716</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.4168</v>
+        <v>-11.3184</v>
       </c>
     </row>
     <row r="187">
@@ -9415,10 +9415,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1682</v>
+        <v>1.182</v>
       </c>
       <c r="J187" t="n">
-        <v>28.0368</v>
+        <v>28.368</v>
       </c>
     </row>
     <row r="188">
@@ -9455,10 +9455,10 @@
         <v>1.38</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8944</v>
+        <v>0.8799</v>
       </c>
       <c r="J188" t="n">
-        <v>21.4656</v>
+        <v>21.1176</v>
       </c>
     </row>
     <row r="189">
@@ -9495,10 +9495,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5995</v>
+        <v>0.5707</v>
       </c>
       <c r="J189" t="n">
-        <v>14.388</v>
+        <v>13.6968</v>
       </c>
     </row>
     <row r="190">
@@ -9535,10 +9535,10 @@
         <v>1.14</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3969</v>
+        <v>0.3646</v>
       </c>
       <c r="J190" t="n">
-        <v>9.525600000000001</v>
+        <v>8.750400000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9575,10 +9575,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.3224</v>
+        <v>0.2905</v>
       </c>
       <c r="J191" t="n">
-        <v>7.7376</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="192">
@@ -9615,10 +9615,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.751</v>
       </c>
       <c r="J192" t="n">
-        <v>28.6884</v>
+        <v>27.036</v>
       </c>
     </row>
     <row r="193">
@@ -9655,10 +9655,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0371</v>
+        <v>-0.029</v>
       </c>
       <c r="J193" t="n">
-        <v>-1.3356</v>
+        <v>-1.044</v>
       </c>
     </row>
     <row r="194">
@@ -9695,10 +9695,10 @@
         <v>0.82</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.0892</v>
+        <v>-7.3692</v>
       </c>
     </row>
     <row r="195">
@@ -9735,10 +9735,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2545</v>
+        <v>-0.2349</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.162000000000001</v>
+        <v>-8.4564</v>
       </c>
     </row>
     <row r="196">
@@ -9775,10 +9775,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4389</v>
+        <v>-0.4319</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.8004</v>
+        <v>-15.5484</v>
       </c>
     </row>
     <row r="197">
@@ -9815,10 +9815,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3776</v>
+        <v>1.4041</v>
       </c>
       <c r="J197" t="n">
-        <v>49.5936</v>
+        <v>50.5476</v>
       </c>
     </row>
     <row r="198">
@@ -9855,10 +9855,10 @@
         <v>1.25</v>
       </c>
       <c r="I198" t="n">
-        <v>0.654</v>
+        <v>0.6214</v>
       </c>
       <c r="J198" t="n">
-        <v>23.544</v>
+        <v>22.3704</v>
       </c>
     </row>
     <row r="199">
@@ -9895,10 +9895,10 @@
         <v>1.23</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6118</v>
+        <v>0.5778</v>
       </c>
       <c r="J199" t="n">
-        <v>22.0248</v>
+        <v>20.8008</v>
       </c>
     </row>
     <row r="200">
@@ -9935,10 +9935,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3138</v>
+        <v>0.2803</v>
       </c>
       <c r="J200" t="n">
-        <v>11.2968</v>
+        <v>10.0908</v>
       </c>
     </row>
     <row r="201">
@@ -9975,10 +9975,10 @@
         <v>0.61</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.0269</v>
+        <v>-1.0317</v>
       </c>
       <c r="J201" t="n">
-        <v>-36.9684</v>
+        <v>-37.1412</v>
       </c>
     </row>
     <row r="202">
@@ -10015,10 +10015,10 @@
         <v>1.49</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0754</v>
+        <v>1.0851</v>
       </c>
       <c r="J202" t="n">
-        <v>26.885</v>
+        <v>27.1275</v>
       </c>
     </row>
     <row r="203">
@@ -10055,10 +10055,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9851</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>24.6275</v>
+        <v>24.535</v>
       </c>
     </row>
     <row r="204">
@@ -10095,10 +10095,10 @@
         <v>1.36</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8572</v>
+        <v>0.8398</v>
       </c>
       <c r="J204" t="n">
-        <v>21.43</v>
+        <v>20.995</v>
       </c>
     </row>
     <row r="205">
@@ -10135,10 +10135,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6419</v>
+        <v>0.614</v>
       </c>
       <c r="J205" t="n">
-        <v>16.0475</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="206">
@@ -10175,10 +10175,10 @@
         <v>0.86</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4956</v>
+        <v>-0.4581</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.39</v>
+        <v>-11.4525</v>
       </c>
     </row>
     <row r="207">
@@ -10215,10 +10215,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4064</v>
+        <v>0.3514</v>
       </c>
       <c r="J207" t="n">
-        <v>10.16</v>
+        <v>8.785</v>
       </c>
     </row>
     <row r="208">
@@ -10255,10 +10255,10 @@
         <v>1.06</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1887</v>
+        <v>0.1487</v>
       </c>
       <c r="J208" t="n">
-        <v>4.7175</v>
+        <v>3.7175</v>
       </c>
     </row>
     <row r="209">
@@ -10295,10 +10295,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2033</v>
+        <v>-0.1835</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.0825</v>
+        <v>-4.5875</v>
       </c>
     </row>
     <row r="210">
@@ -10335,10 +10335,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2435</v>
+        <v>-0.2238</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.0875</v>
+        <v>-5.595</v>
       </c>
     </row>
     <row r="211">
@@ -10375,10 +10375,10 @@
         <v>0.66</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3754</v>
+        <v>-0.3621</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.385</v>
+        <v>-9.0525</v>
       </c>
     </row>
     <row r="212">
@@ -10415,10 +10415,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6341</v>
+        <v>0.5636</v>
       </c>
       <c r="J212" t="n">
-        <v>14.5843</v>
+        <v>12.9628</v>
       </c>
     </row>
     <row r="213">
@@ -10455,10 +10455,10 @@
         <v>1.44</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5453</v>
+        <v>0.478</v>
       </c>
       <c r="J213" t="n">
-        <v>12.5419</v>
+        <v>10.994</v>
       </c>
     </row>
     <row r="214">
@@ -10495,10 +10495,10 @@
         <v>1.41</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5152</v>
+        <v>0.4495</v>
       </c>
       <c r="J214" t="n">
-        <v>11.8496</v>
+        <v>10.3385</v>
       </c>
     </row>
     <row r="215">
@@ -10535,10 +10535,10 @@
         <v>1.3</v>
       </c>
       <c r="I215" t="n">
-        <v>0.402</v>
+        <v>0.3439</v>
       </c>
       <c r="J215" t="n">
-        <v>9.246</v>
+        <v>7.9097</v>
       </c>
     </row>
     <row r="216">
@@ -10575,10 +10575,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1704</v>
+        <v>0.1345</v>
       </c>
       <c r="J216" t="n">
-        <v>3.9192</v>
+        <v>3.0935</v>
       </c>
     </row>
     <row r="217">
@@ -10615,10 +10615,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2095</v>
+        <v>-0.1944</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.8185</v>
+        <v>-4.4712</v>
       </c>
     </row>
     <row r="218">
@@ -10655,10 +10655,10 @@
         <v>0.72</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2984</v>
+        <v>-0.285</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.8632</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="219">
@@ -10695,10 +10695,10 @@
         <v>0.66</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.351</v>
+        <v>-0.3384</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.073</v>
+        <v>-7.7832</v>
       </c>
     </row>
     <row r="220">
@@ -10735,10 +10735,10 @@
         <v>0.63</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3775</v>
+        <v>-0.3657</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.682499999999999</v>
+        <v>-8.411099999999999</v>
       </c>
     </row>
     <row r="221">
@@ -10775,10 +10775,10 @@
         <v>0.61</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3952</v>
+        <v>-0.3843</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.089600000000001</v>
+        <v>-8.838900000000001</v>
       </c>
     </row>
     <row r="222">
@@ -10815,10 +10815,10 @@
         <v>1.83</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9177</v>
+        <v>0.8494</v>
       </c>
       <c r="J222" t="n">
-        <v>21.1071</v>
+        <v>19.5362</v>
       </c>
     </row>
     <row r="223">
@@ -10855,10 +10855,10 @@
         <v>1.62</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7225</v>
+        <v>0.6505</v>
       </c>
       <c r="J223" t="n">
-        <v>16.6175</v>
+        <v>14.9615</v>
       </c>
     </row>
     <row r="224">
@@ -10895,10 +10895,10 @@
         <v>1.35</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4552</v>
+        <v>0.3929</v>
       </c>
       <c r="J224" t="n">
-        <v>10.4696</v>
+        <v>9.0367</v>
       </c>
     </row>
     <row r="225">
@@ -10935,10 +10935,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.264</v>
+        <v>0.2176</v>
       </c>
       <c r="J225" t="n">
-        <v>6.072</v>
+        <v>5.0048</v>
       </c>
     </row>
     <row r="226">
@@ -10975,10 +10975,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3353</v>
+        <v>-0.3235</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.7119</v>
+        <v>-7.4405</v>
       </c>
     </row>
     <row r="227">
@@ -11015,10 +11015,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.078</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.794</v>
+        <v>-1.4996</v>
       </c>
     </row>
     <row r="228">
@@ -11055,10 +11055,10 @@
         <v>0.9</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1278</v>
+        <v>-0.1128</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.9394</v>
+        <v>-2.5944</v>
       </c>
     </row>
     <row r="229">
@@ -11095,10 +11095,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2042</v>
+        <v>-0.1875</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.6966</v>
+        <v>-4.3125</v>
       </c>
     </row>
     <row r="230">
@@ -11135,10 +11135,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2802</v>
+        <v>-0.263</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.4446</v>
+        <v>-6.049</v>
       </c>
     </row>
     <row r="231">
@@ -11175,10 +11175,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4784</v>
+        <v>-0.4748</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.0032</v>
+        <v>-10.9204</v>
       </c>
     </row>
     <row r="232">
@@ -11215,10 +11215,10 @@
         <v>2.02</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6689</v>
+        <v>1.714</v>
       </c>
       <c r="J232" t="n">
-        <v>31.7091</v>
+        <v>32.566</v>
       </c>
     </row>
     <row r="233">
@@ -11255,10 +11255,10 @@
         <v>1.82</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4391</v>
+        <v>1.4694</v>
       </c>
       <c r="J233" t="n">
-        <v>27.3429</v>
+        <v>27.9186</v>
       </c>
     </row>
     <row r="234">
@@ -11295,10 +11295,10 @@
         <v>1.68</v>
       </c>
       <c r="I234" t="n">
-        <v>1.274</v>
+        <v>1.2984</v>
       </c>
       <c r="J234" t="n">
-        <v>24.206</v>
+        <v>24.6696</v>
       </c>
     </row>
     <row r="235">
@@ -11335,10 +11335,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>0.994</v>
+        <v>1.0053</v>
       </c>
       <c r="J235" t="n">
-        <v>18.886</v>
+        <v>19.1007</v>
       </c>
     </row>
     <row r="236">
@@ -11375,10 +11375,10 @@
         <v>1.15</v>
       </c>
       <c r="I236" t="n">
-        <v>0.3714</v>
+        <v>0.3364</v>
       </c>
       <c r="J236" t="n">
-        <v>7.0566</v>
+        <v>6.3916</v>
       </c>
     </row>
     <row r="237">
@@ -11415,10 +11415,10 @@
         <v>0.7</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2951</v>
+        <v>-0.2835</v>
       </c>
       <c r="J237" t="n">
-        <v>-5.6069</v>
+        <v>-5.3865</v>
       </c>
     </row>
     <row r="238">
@@ -11455,10 +11455,10 @@
         <v>0.63</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3627</v>
+        <v>-0.3551</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.8913</v>
+        <v>-6.7469</v>
       </c>
     </row>
     <row r="239">
@@ -11495,10 +11495,10 @@
         <v>0.61</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.381</v>
+        <v>-0.3742</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.239</v>
+        <v>-7.1098</v>
       </c>
     </row>
     <row r="240">
@@ -11535,10 +11535,10 @@
         <v>0.59</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3987</v>
+        <v>-0.3924</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.5753</v>
+        <v>-7.4556</v>
       </c>
     </row>
     <row r="241">
@@ -11575,10 +11575,10 @@
         <v>0.3</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6522</v>
+        <v>-0.6722</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.3918</v>
+        <v>-12.7718</v>
       </c>
     </row>
     <row r="242">
@@ -11615,10 +11615,10 @@
         <v>0.86</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1161</v>
+        <v>-0.0898</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.0898</v>
+        <v>-1.6164</v>
       </c>
     </row>
     <row r="243">
@@ -11655,10 +11655,10 @@
         <v>0.61</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.3796</v>
+        <v>-0.373</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.8328</v>
+        <v>-6.714</v>
       </c>
     </row>
     <row r="244">
@@ -11695,10 +11695,10 @@
         <v>0.57</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4148</v>
+        <v>-0.4093</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.4664</v>
+        <v>-7.3674</v>
       </c>
     </row>
     <row r="245">
@@ -11735,10 +11735,10 @@
         <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4649</v>
+        <v>-0.4612</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.3682</v>
+        <v>-8.301600000000001</v>
       </c>
     </row>
     <row r="246">
@@ -11775,10 +11775,10 @@
         <v>0.24</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7049</v>
+        <v>-0.7353</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.6882</v>
+        <v>-13.2354</v>
       </c>
     </row>
     <row r="247">
@@ -11815,10 +11815,10 @@
         <v>2.31</v>
       </c>
       <c r="I247" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J247" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="248">
@@ -11855,10 +11855,10 @@
         <v>1.64</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2265</v>
+        <v>1.2499</v>
       </c>
       <c r="J248" t="n">
-        <v>22.077</v>
+        <v>22.4982</v>
       </c>
     </row>
     <row r="249">
@@ -11895,10 +11895,10 @@
         <v>1.51</v>
       </c>
       <c r="I249" t="n">
-        <v>1.066</v>
+        <v>1.0858</v>
       </c>
       <c r="J249" t="n">
-        <v>19.188</v>
+        <v>19.5444</v>
       </c>
     </row>
     <row r="250">
@@ -11935,10 +11935,10 @@
         <v>1.38</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8524</v>
+        <v>0.8474</v>
       </c>
       <c r="J250" t="n">
-        <v>15.3432</v>
+        <v>15.2532</v>
       </c>
     </row>
     <row r="251">
@@ -11975,10 +11975,10 @@
         <v>1.29</v>
       </c>
       <c r="I251" t="n">
-        <v>0.6764</v>
+        <v>0.6573</v>
       </c>
       <c r="J251" t="n">
-        <v>12.1752</v>
+        <v>11.8314</v>
       </c>
     </row>
     <row r="252">
@@ -12015,10 +12015,10 @@
         <v>1.49</v>
       </c>
       <c r="I252" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8142</v>
       </c>
       <c r="J252" t="n">
-        <v>25.932</v>
+        <v>24.426</v>
       </c>
     </row>
     <row r="253">
@@ -12055,10 +12055,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4046</v>
+        <v>0.3485</v>
       </c>
       <c r="J253" t="n">
-        <v>12.138</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="254">
@@ -12095,10 +12095,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3876</v>
+        <v>0.3323</v>
       </c>
       <c r="J254" t="n">
-        <v>11.628</v>
+        <v>9.968999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -12135,10 +12135,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1743</v>
+        <v>-0.1539</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.229</v>
+        <v>-4.617</v>
       </c>
     </row>
     <row r="256">
@@ -12175,10 +12175,10 @@
         <v>0.55</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4847</v>
+        <v>-0.4851</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.541</v>
+        <v>-14.553</v>
       </c>
     </row>
     <row r="257">
@@ -12215,10 +12215,10 @@
         <v>1.4</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5346</v>
+        <v>0.465</v>
       </c>
       <c r="J257" t="n">
-        <v>16.038</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="258">
@@ -12255,10 +12255,10 @@
         <v>1.25</v>
       </c>
       <c r="I258" t="n">
-        <v>0.366</v>
+        <v>0.3054</v>
       </c>
       <c r="J258" t="n">
-        <v>10.98</v>
+        <v>9.162000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12295,10 +12295,10 @@
         <v>1.08</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1483</v>
+        <v>0.1141</v>
       </c>
       <c r="J259" t="n">
-        <v>4.449</v>
+        <v>3.423</v>
       </c>
     </row>
     <row r="260">
@@ -12335,10 +12335,10 @@
         <v>1.02</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0454</v>
+        <v>0.0316</v>
       </c>
       <c r="J260" t="n">
-        <v>1.362</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="261">
@@ -12375,10 +12375,10 @@
         <v>0.82</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2422</v>
+        <v>-0.2226</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.266</v>
+        <v>-6.678</v>
       </c>
     </row>
     <row r="262">
@@ -12415,10 +12415,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6559</v>
+        <v>0.6022</v>
       </c>
       <c r="J262" t="n">
-        <v>16.3975</v>
+        <v>15.055</v>
       </c>
     </row>
     <row r="263">
@@ -12455,10 +12455,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1391</v>
+        <v>0.1056</v>
       </c>
       <c r="J263" t="n">
-        <v>3.4775</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="264">
@@ -12495,10 +12495,10 @@
         <v>0.88</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1623</v>
+        <v>-0.1432</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.0575</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="265">
@@ -12535,10 +12535,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3214</v>
+        <v>-0.3045</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.035</v>
+        <v>-7.6125</v>
       </c>
     </row>
     <row r="266">
@@ -12575,10 +12575,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4035</v>
+        <v>-0.3928</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.0875</v>
+        <v>-9.82</v>
       </c>
     </row>
     <row r="267">
@@ -12615,10 +12615,10 @@
         <v>1.34</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4575</v>
+        <v>0.3917</v>
       </c>
       <c r="J267" t="n">
-        <v>11.4375</v>
+        <v>9.7925</v>
       </c>
     </row>
     <row r="268">
@@ -12655,10 +12655,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2993</v>
+        <v>0.2467</v>
       </c>
       <c r="J268" t="n">
-        <v>7.4825</v>
+        <v>6.1675</v>
       </c>
     </row>
     <row r="269">
@@ -12695,10 +12695,10 @@
         <v>1.19</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2876</v>
+        <v>0.2363</v>
       </c>
       <c r="J269" t="n">
-        <v>7.19</v>
+        <v>5.9075</v>
       </c>
     </row>
     <row r="270">
@@ -12735,10 +12735,10 @@
         <v>1.18</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2756</v>
+        <v>0.2257</v>
       </c>
       <c r="J270" t="n">
-        <v>6.89</v>
+        <v>5.6425</v>
       </c>
     </row>
     <row r="271">
@@ -12775,10 +12775,10 @@
         <v>1.07</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1258</v>
+        <v>0.0963</v>
       </c>
       <c r="J271" t="n">
-        <v>3.145</v>
+        <v>2.4075</v>
       </c>
     </row>
     <row r="272">
@@ -12815,10 +12815,10 @@
         <v>1.28</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5724</v>
+        <v>0.5139</v>
       </c>
       <c r="J272" t="n">
-        <v>20.6064</v>
+        <v>18.5004</v>
       </c>
     </row>
     <row r="273">
@@ -12855,10 +12855,10 @@
         <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2766</v>
+        <v>0.2277</v>
       </c>
       <c r="J273" t="n">
-        <v>9.957599999999999</v>
+        <v>8.1972</v>
       </c>
     </row>
     <row r="274">
@@ -12895,10 +12895,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2097</v>
+        <v>-0.1892</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.5492</v>
+        <v>-6.8112</v>
       </c>
     </row>
     <row r="275">
@@ -12935,10 +12935,10 @@
         <v>0.83</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.22</v>
+        <v>-0.1995</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.92</v>
+        <v>-7.182</v>
       </c>
     </row>
     <row r="276">
@@ -12975,10 +12975,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2302</v>
+        <v>-0.2098</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.2872</v>
+        <v>-7.5528</v>
       </c>
     </row>
     <row r="277">
@@ -13015,10 +13015,10 @@
         <v>1.32</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4512</v>
+        <v>0.3849</v>
       </c>
       <c r="J277" t="n">
-        <v>16.2432</v>
+        <v>13.8564</v>
       </c>
     </row>
     <row r="278">
@@ -13055,10 +13055,10 @@
         <v>1.32</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4512</v>
+        <v>0.3849</v>
       </c>
       <c r="J278" t="n">
-        <v>16.2432</v>
+        <v>13.8564</v>
       </c>
     </row>
     <row r="279">
@@ -13095,10 +13095,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.322</v>
+        <v>0.2647</v>
       </c>
       <c r="J279" t="n">
-        <v>11.592</v>
+        <v>9.529199999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13135,10 +13135,10 @@
         <v>0.87</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1875</v>
+        <v>-0.1669</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.75</v>
+        <v>-6.0084</v>
       </c>
     </row>
     <row r="281">
@@ -13175,10 +13175,10 @@
         <v>0.7</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3547</v>
+        <v>-0.3412</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.7692</v>
+        <v>-12.2832</v>
       </c>
     </row>
     <row r="282">
@@ -13215,10 +13215,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3552</v>
+        <v>0.3026</v>
       </c>
       <c r="J282" t="n">
-        <v>12.0768</v>
+        <v>10.2884</v>
       </c>
     </row>
     <row r="283">
@@ -13255,10 +13255,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="J283" t="n">
-        <v>-2.1998</v>
+        <v>-1.8122</v>
       </c>
     </row>
     <row r="284">
@@ -13295,10 +13295,10 @@
         <v>0.84</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2021</v>
+        <v>-0.1825</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.8714</v>
+        <v>-6.205</v>
       </c>
     </row>
     <row r="285">
@@ -13335,10 +13335,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2714</v>
+        <v>-0.2524</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.227600000000001</v>
+        <v>-8.5816</v>
       </c>
     </row>
     <row r="286">
@@ -13375,10 +13375,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2906</v>
+        <v>-0.2721</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.8804</v>
+        <v>-9.2514</v>
       </c>
     </row>
     <row r="287">
@@ -13415,10 +13415,10 @@
         <v>1.38</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4983</v>
+        <v>0.4306</v>
       </c>
       <c r="J287" t="n">
-        <v>16.9422</v>
+        <v>14.6404</v>
       </c>
     </row>
     <row r="288">
@@ -13455,10 +13455,10 @@
         <v>1.3</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4117</v>
+        <v>0.3492</v>
       </c>
       <c r="J288" t="n">
-        <v>13.9978</v>
+        <v>11.8728</v>
       </c>
     </row>
     <row r="289">
@@ -13495,10 +13495,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2744</v>
+        <v>0.2251</v>
       </c>
       <c r="J289" t="n">
-        <v>9.329599999999999</v>
+        <v>7.6534</v>
       </c>
     </row>
     <row r="290">
@@ -13535,10 +13535,10 @@
         <v>1.16</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2495</v>
+        <v>0.2031</v>
       </c>
       <c r="J290" t="n">
-        <v>8.483000000000001</v>
+        <v>6.9054</v>
       </c>
     </row>
     <row r="291">
@@ -13575,10 +13575,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0917</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>3.1178</v>
+        <v>2.3154</v>
       </c>
     </row>
     <row r="292">
@@ -13615,10 +13615,10 @@
         <v>0.88</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1428</v>
+        <v>-0.1274</v>
       </c>
       <c r="J292" t="n">
-        <v>-2.7132</v>
+        <v>-2.4206</v>
       </c>
     </row>
     <row r="293">
@@ -13655,10 +13655,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2184</v>
+        <v>-0.2028</v>
       </c>
       <c r="J293" t="n">
-        <v>-4.1496</v>
+        <v>-3.8532</v>
       </c>
     </row>
     <row r="294">
@@ -13695,10 +13695,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2285</v>
+        <v>-0.2129</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.3415</v>
+        <v>-4.0451</v>
       </c>
     </row>
     <row r="295">
@@ -13735,10 +13735,10 @@
         <v>0.66</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3571</v>
+        <v>-0.3433</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.7849</v>
+        <v>-6.5227</v>
       </c>
     </row>
     <row r="296">
@@ -13775,10 +13775,10 @@
         <v>0.55</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4551</v>
+        <v>-0.4486</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.6469</v>
+        <v>-8.523400000000001</v>
       </c>
     </row>
     <row r="297">
@@ -13815,10 +13815,10 @@
         <v>1.65</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6748</v>
       </c>
       <c r="J297" t="n">
-        <v>14.1835</v>
+        <v>12.8212</v>
       </c>
     </row>
     <row r="298">
@@ -13855,10 +13855,10 @@
         <v>1.6</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6992</v>
+        <v>0.6278</v>
       </c>
       <c r="J298" t="n">
-        <v>13.2848</v>
+        <v>11.9282</v>
       </c>
     </row>
     <row r="299">
@@ -13895,10 +13895,10 @@
         <v>1.41</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5139</v>
+        <v>0.4487</v>
       </c>
       <c r="J299" t="n">
-        <v>9.764099999999999</v>
+        <v>8.5253</v>
       </c>
     </row>
     <row r="300">
@@ -13935,10 +13935,10 @@
         <v>1.2</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2858</v>
+        <v>0.2375</v>
       </c>
       <c r="J300" t="n">
-        <v>5.4302</v>
+        <v>4.5125</v>
       </c>
     </row>
     <row r="301">
@@ -13975,10 +13975,10 @@
         <v>1.03</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0411</v>
+        <v>0.0255</v>
       </c>
       <c r="J301" t="n">
-        <v>0.7809</v>
+        <v>0.4845</v>
       </c>
     </row>
     <row r="302">
@@ -14015,10 +14015,10 @@
         <v>1.26</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5458</v>
+        <v>0.4877</v>
       </c>
       <c r="J302" t="n">
-        <v>14.7366</v>
+        <v>13.1679</v>
       </c>
     </row>
     <row r="303">
@@ -14055,10 +14055,10 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.0049</v>
+        <v>0.0027</v>
       </c>
       <c r="J303" t="n">
-        <v>0.1323</v>
+        <v>0.07290000000000001</v>
       </c>
     </row>
     <row r="304">
@@ -14095,10 +14095,10 @@
         <v>0.92</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1201</v>
+        <v>-0.1025</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.2427</v>
+        <v>-2.7675</v>
       </c>
     </row>
     <row r="305">
@@ -14135,10 +14135,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2384</v>
+        <v>-0.2182</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.4368</v>
+        <v>-5.8914</v>
       </c>
     </row>
     <row r="306">
@@ -14175,10 +14175,10 @@
         <v>0.79</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2582</v>
+        <v>-0.2385</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.9714</v>
+        <v>-6.4395</v>
       </c>
     </row>
     <row r="307">
@@ -14215,10 +14215,10 @@
         <v>1.6</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7379</v>
+        <v>0.6674</v>
       </c>
       <c r="J307" t="n">
-        <v>19.9233</v>
+        <v>18.0198</v>
       </c>
     </row>
     <row r="308">
@@ -14255,10 +14255,10 @@
         <v>1.27</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3863</v>
+        <v>0.3244</v>
       </c>
       <c r="J308" t="n">
-        <v>10.4301</v>
+        <v>8.758800000000001</v>
       </c>
     </row>
     <row r="309">
@@ -14295,10 +14295,10 @@
         <v>1.02</v>
       </c>
       <c r="I309" t="n">
-        <v>0.0431</v>
+        <v>0.0298</v>
       </c>
       <c r="J309" t="n">
-        <v>1.1637</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="310">
@@ -14335,10 +14335,10 @@
         <v>0.91</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1469</v>
+        <v>-0.1274</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.9663</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="311">
@@ -14375,10 +14375,10 @@
         <v>0.89</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1699</v>
+        <v>-0.1498</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.5873</v>
+        <v>-4.0446</v>
       </c>
     </row>
     <row r="312">
@@ -14415,10 +14415,10 @@
         <v>1.5</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1096</v>
+        <v>1.1214</v>
       </c>
       <c r="J312" t="n">
-        <v>29.9592</v>
+        <v>30.2778</v>
       </c>
     </row>
     <row r="313">
@@ -14455,10 +14455,10 @@
         <v>1.2</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5476</v>
+        <v>0.5123</v>
       </c>
       <c r="J313" t="n">
-        <v>14.7852</v>
+        <v>13.8321</v>
       </c>
     </row>
     <row r="314">
@@ -14495,10 +14495,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5041</v>
+        <v>0.4683</v>
       </c>
       <c r="J314" t="n">
-        <v>13.6107</v>
+        <v>12.6441</v>
       </c>
     </row>
     <row r="315">
@@ -14535,10 +14535,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4598</v>
+        <v>0.4239</v>
       </c>
       <c r="J315" t="n">
-        <v>12.4146</v>
+        <v>11.4453</v>
       </c>
     </row>
     <row r="316">
@@ -14575,10 +14575,10 @@
         <v>0.84</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5273</v>
+        <v>-0.4881</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.2371</v>
+        <v>-13.1787</v>
       </c>
     </row>
     <row r="317">
@@ -14615,10 +14615,10 @@
         <v>1.38</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7204</v>
+        <v>0.6649</v>
       </c>
       <c r="J317" t="n">
-        <v>19.4508</v>
+        <v>17.9523</v>
       </c>
     </row>
     <row r="318">
@@ -14655,10 +14655,10 @@
         <v>1.1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2521</v>
+        <v>0.2057</v>
       </c>
       <c r="J318" t="n">
-        <v>6.8067</v>
+        <v>5.5539</v>
       </c>
     </row>
     <row r="319">
@@ -14695,10 +14695,10 @@
         <v>0.98</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0428</v>
+        <v>-0.0325</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.1556</v>
+        <v>-0.8774999999999999</v>
       </c>
     </row>
     <row r="320">
@@ -14735,10 +14735,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1584</v>
+        <v>-0.1384</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.2768</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="321">
@@ -14775,10 +14775,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3842</v>
+        <v>-0.3725</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.3734</v>
+        <v>-10.0575</v>
       </c>
     </row>
     <row r="322">
@@ -14815,10 +14815,10 @@
         <v>1.2</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4591</v>
+        <v>0.4031</v>
       </c>
       <c r="J322" t="n">
-        <v>13.773</v>
+        <v>12.093</v>
       </c>
     </row>
     <row r="323">
@@ -14855,10 +14855,10 @@
         <v>1.15</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3692</v>
+        <v>0.3154</v>
       </c>
       <c r="J323" t="n">
-        <v>11.076</v>
+        <v>9.462</v>
       </c>
     </row>
     <row r="324">
@@ -14895,10 +14895,10 @@
         <v>0.87</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1722</v>
+        <v>-0.153</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.166</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="325">
@@ -14935,10 +14935,10 @@
         <v>0.79</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2536</v>
+        <v>-0.234</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.608</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="326">
@@ -14975,10 +14975,10 @@
         <v>0.53</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4901</v>
+        <v>-0.4892</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.703</v>
+        <v>-14.676</v>
       </c>
     </row>
     <row r="327">
@@ -15015,10 +15015,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8944</v>
+        <v>0.8766</v>
       </c>
       <c r="J327" t="n">
-        <v>26.832</v>
+        <v>26.298</v>
       </c>
     </row>
     <row r="328">
@@ -15055,10 +15055,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8129</v>
       </c>
       <c r="J328" t="n">
-        <v>25.056</v>
+        <v>24.387</v>
       </c>
     </row>
     <row r="329">
@@ -15095,10 +15095,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.6935</v>
+        <v>0.663</v>
       </c>
       <c r="J329" t="n">
-        <v>20.805</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="330">
@@ -15135,10 +15135,10 @@
         <v>1.23</v>
       </c>
       <c r="I330" t="n">
-        <v>0.61</v>
+        <v>0.5765</v>
       </c>
       <c r="J330" t="n">
-        <v>18.3</v>
+        <v>17.295</v>
       </c>
     </row>
     <row r="331">
@@ -15175,10 +15175,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.7332</v>
       </c>
       <c r="J331" t="n">
-        <v>-22.728</v>
+        <v>-21.996</v>
       </c>
     </row>
     <row r="332">
@@ -15215,10 +15215,10 @@
         <v>0.95</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0433</v>
+        <v>-0.028</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.9093</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="333">
@@ -15255,10 +15255,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2414</v>
+        <v>-0.2269</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.0694</v>
+        <v>-4.7649</v>
       </c>
     </row>
     <row r="334">
@@ -15295,10 +15295,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3255</v>
+        <v>-0.3122</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.8355</v>
+        <v>-6.5562</v>
       </c>
     </row>
     <row r="335">
@@ -15335,10 +15335,10 @@
         <v>0.62</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.387</v>
+        <v>-0.3756</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.127000000000001</v>
+        <v>-7.8876</v>
       </c>
     </row>
     <row r="336">
@@ -15375,10 +15375,10 @@
         <v>0.42</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5628</v>
+        <v>-0.5695</v>
       </c>
       <c r="J336" t="n">
-        <v>-11.8188</v>
+        <v>-11.9595</v>
       </c>
     </row>
     <row r="337">
@@ -15415,10 +15415,10 @@
         <v>1.7</v>
       </c>
       <c r="I337" t="n">
-        <v>0.7885</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J337" t="n">
-        <v>16.5585</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="338">
@@ -15455,10 +15455,10 @@
         <v>1.58</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6763</v>
+        <v>0.6058</v>
       </c>
       <c r="J338" t="n">
-        <v>14.2023</v>
+        <v>12.7218</v>
       </c>
     </row>
     <row r="339">
@@ -15495,10 +15495,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4721</v>
+        <v>0.4104</v>
       </c>
       <c r="J339" t="n">
-        <v>9.914099999999999</v>
+        <v>8.618399999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15535,10 +15535,10 @@
         <v>1.25</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3419</v>
+        <v>0.2892</v>
       </c>
       <c r="J340" t="n">
-        <v>7.1799</v>
+        <v>6.0732</v>
       </c>
     </row>
     <row r="341">
@@ -15575,10 +15575,10 @@
         <v>1.17</v>
       </c>
       <c r="I341" t="n">
-        <v>0.2456</v>
+        <v>0.2012</v>
       </c>
       <c r="J341" t="n">
-        <v>5.1576</v>
+        <v>4.2252</v>
       </c>
     </row>
     <row r="342">
@@ -15615,10 +15615,10 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3734</v>
+        <v>0.3184</v>
       </c>
       <c r="J342" t="n">
-        <v>9.335000000000001</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="343">
@@ -15655,10 +15655,10 @@
         <v>1.05</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1544</v>
+        <v>0.1188</v>
       </c>
       <c r="J343" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="344">
@@ -15695,10 +15695,10 @@
         <v>0.98</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0406</v>
+        <v>-0.0315</v>
       </c>
       <c r="J344" t="n">
-        <v>-1.015</v>
+        <v>-0.7875</v>
       </c>
     </row>
     <row r="345">
@@ -15735,10 +15735,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0833</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.0825</v>
+        <v>-1.715</v>
       </c>
     </row>
     <row r="346">
@@ -15775,10 +15775,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3805</v>
+        <v>-0.3681</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.512499999999999</v>
+        <v>-9.202500000000001</v>
       </c>
     </row>
     <row r="347">
@@ -15815,10 +15815,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5848</v>
+        <v>0.514</v>
       </c>
       <c r="J347" t="n">
-        <v>14.62</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="348">
@@ -15855,10 +15855,10 @@
         <v>1.24</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3521</v>
+        <v>0.2928</v>
       </c>
       <c r="J348" t="n">
-        <v>8.8025</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="349">
@@ -15895,10 +15895,10 @@
         <v>1.21</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3163</v>
+        <v>0.2604</v>
       </c>
       <c r="J349" t="n">
-        <v>7.9075</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="350">
@@ -15935,10 +15935,10 @@
         <v>1.06</v>
       </c>
       <c r="I350" t="n">
-        <v>0.1158</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J350" t="n">
-        <v>2.895</v>
+        <v>2.1875</v>
       </c>
     </row>
     <row r="351">
@@ -15975,10 +15975,10 @@
         <v>0.7</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3583</v>
+        <v>-0.3457</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.9575</v>
+        <v>-8.6425</v>
       </c>
     </row>
     <row r="352">
@@ -16015,10 +16015,10 @@
         <v>1.15</v>
       </c>
       <c r="I352" t="n">
-        <v>0.2457</v>
+        <v>0.1967</v>
       </c>
       <c r="J352" t="n">
-        <v>6.6339</v>
+        <v>5.3109</v>
       </c>
     </row>
     <row r="353">
@@ -16055,10 +16055,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1922</v>
+        <v>0.1505</v>
       </c>
       <c r="J353" t="n">
-        <v>5.1894</v>
+        <v>4.0635</v>
       </c>
     </row>
     <row r="354">
@@ -16095,10 +16095,10 @@
         <v>1.1</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1784</v>
+        <v>0.1388</v>
       </c>
       <c r="J354" t="n">
-        <v>4.8168</v>
+        <v>3.7476</v>
       </c>
     </row>
     <row r="355">
@@ -16135,10 +16135,10 @@
         <v>1.05</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1031</v>
+        <v>0.0765</v>
       </c>
       <c r="J355" t="n">
-        <v>2.7837</v>
+        <v>2.0655</v>
       </c>
     </row>
     <row r="356">
@@ -16175,10 +16175,10 @@
         <v>1.04</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0859</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J356" t="n">
-        <v>2.3193</v>
+        <v>1.6956</v>
       </c>
     </row>
     <row r="357">
@@ -16215,10 +16215,10 @@
         <v>1.4</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7305</v>
+        <v>0.6733</v>
       </c>
       <c r="J357" t="n">
-        <v>19.7235</v>
+        <v>18.1791</v>
       </c>
     </row>
     <row r="358">
@@ -16255,10 +16255,10 @@
         <v>1.14</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3158</v>
+        <v>0.2654</v>
       </c>
       <c r="J358" t="n">
-        <v>8.5266</v>
+        <v>7.1658</v>
       </c>
     </row>
     <row r="359">
@@ -16295,10 +16295,10 @@
         <v>1.06</v>
       </c>
       <c r="I359" t="n">
-        <v>0.1626</v>
+        <v>0.1287</v>
       </c>
       <c r="J359" t="n">
-        <v>4.3902</v>
+        <v>3.4749</v>
       </c>
     </row>
     <row r="360">
@@ -16335,10 +16335,10 @@
         <v>1.04</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1178</v>
+        <v>0.0907</v>
       </c>
       <c r="J360" t="n">
-        <v>3.1806</v>
+        <v>2.4489</v>
       </c>
     </row>
     <row r="361">
@@ -16375,10 +16375,10 @@
         <v>0.71</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3444</v>
+        <v>-0.33</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.2988</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="362">
@@ -16415,10 +16415,10 @@
         <v>1.49</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6087</v>
+        <v>0.5374</v>
       </c>
       <c r="J362" t="n">
-        <v>13.3914</v>
+        <v>11.8228</v>
       </c>
     </row>
     <row r="363">
@@ -16455,10 +16455,10 @@
         <v>1.34</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4524</v>
+        <v>0.3878</v>
       </c>
       <c r="J363" t="n">
-        <v>9.9528</v>
+        <v>8.531599999999999</v>
       </c>
     </row>
     <row r="364">
@@ -16495,10 +16495,10 @@
         <v>1.24</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3429</v>
+        <v>0.287</v>
       </c>
       <c r="J364" t="n">
-        <v>7.5438</v>
+        <v>6.314</v>
       </c>
     </row>
     <row r="365">
@@ -16535,10 +16535,10 @@
         <v>1.23</v>
       </c>
       <c r="I365" t="n">
-        <v>0.3316</v>
+        <v>0.2769</v>
       </c>
       <c r="J365" t="n">
-        <v>7.2952</v>
+        <v>6.0918</v>
       </c>
     </row>
     <row r="366">
@@ -16575,10 +16575,10 @@
         <v>0.91</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.1549</v>
+        <v>-0.136</v>
       </c>
       <c r="J366" t="n">
-        <v>-3.4078</v>
+        <v>-2.992</v>
       </c>
     </row>
     <row r="367">
@@ -16615,10 +16615,10 @@
         <v>1.1</v>
       </c>
       <c r="I367" t="n">
-        <v>0.2975</v>
+        <v>0.2511</v>
       </c>
       <c r="J367" t="n">
-        <v>6.545</v>
+        <v>5.5242</v>
       </c>
     </row>
     <row r="368">
@@ -16655,10 +16655,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0565</v>
+        <v>-0.0458</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.243</v>
+        <v>-1.0076</v>
       </c>
     </row>
     <row r="369">
@@ -16695,10 +16695,10 @@
         <v>0.71</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3214</v>
+        <v>-0.3047</v>
       </c>
       <c r="J369" t="n">
-        <v>-7.0708</v>
+        <v>-6.7034</v>
       </c>
     </row>
     <row r="370">
@@ -16735,10 +16735,10 @@
         <v>0.7</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3306</v>
+        <v>-0.3144</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.2732</v>
+        <v>-6.9168</v>
       </c>
     </row>
     <row r="371">
@@ -16775,10 +16775,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3581</v>
+        <v>-0.3435</v>
       </c>
       <c r="J371" t="n">
-        <v>-7.8782</v>
+        <v>-7.557</v>
       </c>
     </row>
     <row r="372">
@@ -16815,10 +16815,10 @@
         <v>1.38</v>
       </c>
       <c r="I372" t="n">
-        <v>0.7009</v>
+        <v>0.6428</v>
       </c>
       <c r="J372" t="n">
-        <v>21.027</v>
+        <v>19.284</v>
       </c>
     </row>
     <row r="373">
@@ -16855,10 +16855,10 @@
         <v>1.22</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4523</v>
+        <v>0.3945</v>
       </c>
       <c r="J373" t="n">
-        <v>13.569</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="374">
@@ -16895,10 +16895,10 @@
         <v>0.98</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0478</v>
+        <v>-0.0362</v>
       </c>
       <c r="J374" t="n">
-        <v>-1.434</v>
+        <v>-1.086</v>
       </c>
     </row>
     <row r="375">
@@ -16935,10 +16935,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1047</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J375" t="n">
-        <v>-3.141</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="376">
@@ -16975,10 +16975,10 @@
         <v>0.83</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2284</v>
+        <v>-0.2081</v>
       </c>
       <c r="J376" t="n">
-        <v>-6.852</v>
+        <v>-6.243</v>
       </c>
     </row>
     <row r="377">
@@ -17015,10 +17015,10 @@
         <v>1.33</v>
       </c>
       <c r="I377" t="n">
-        <v>0.8488</v>
+        <v>0.8263</v>
       </c>
       <c r="J377" t="n">
-        <v>25.464</v>
+        <v>24.789</v>
       </c>
     </row>
     <row r="378">
@@ -17055,10 +17055,10 @@
         <v>1.3</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7863</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J378" t="n">
-        <v>23.589</v>
+        <v>22.758</v>
       </c>
     </row>
     <row r="379">
@@ -17095,10 +17095,10 @@
         <v>1.08</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2757</v>
+        <v>0.2392</v>
       </c>
       <c r="J379" t="n">
-        <v>8.271000000000001</v>
+        <v>7.176</v>
       </c>
     </row>
     <row r="380">
@@ -17135,10 +17135,10 @@
         <v>0.95</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2125</v>
+        <v>-0.176</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.375</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="381">
@@ -17175,10 +17175,10 @@
         <v>0.67</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.8854</v>
+        <v>-0.87</v>
       </c>
       <c r="J381" t="n">
-        <v>-26.562</v>
+        <v>-26.1</v>
       </c>
     </row>
     <row r="382">
@@ -17215,10 +17215,10 @@
         <v>1.53</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1494</v>
+        <v>1.1627</v>
       </c>
       <c r="J382" t="n">
-        <v>27.5856</v>
+        <v>27.9048</v>
       </c>
     </row>
     <row r="383">
@@ -17255,10 +17255,10 @@
         <v>1.29</v>
       </c>
       <c r="I383" t="n">
-        <v>0.7361</v>
+        <v>0.7074</v>
       </c>
       <c r="J383" t="n">
-        <v>17.6664</v>
+        <v>16.9776</v>
       </c>
     </row>
     <row r="384">
@@ -17295,10 +17295,10 @@
         <v>1.24</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6323</v>
+        <v>0.5991</v>
       </c>
       <c r="J384" t="n">
-        <v>15.1752</v>
+        <v>14.3784</v>
       </c>
     </row>
     <row r="385">
@@ -17335,10 +17335,10 @@
         <v>1.03</v>
       </c>
       <c r="I385" t="n">
-        <v>0.1073</v>
+        <v>0.0867</v>
       </c>
       <c r="J385" t="n">
-        <v>2.5752</v>
+        <v>2.0808</v>
       </c>
     </row>
     <row r="386">
@@ -17375,10 +17375,10 @@
         <v>0.82</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5759</v>
+        <v>-0.5389</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.8216</v>
+        <v>-12.9336</v>
       </c>
     </row>
     <row r="387">
@@ -17415,10 +17415,10 @@
         <v>1.1</v>
       </c>
       <c r="I387" t="n">
-        <v>0.2708</v>
+        <v>0.2227</v>
       </c>
       <c r="J387" t="n">
-        <v>6.4992</v>
+        <v>5.3448</v>
       </c>
     </row>
     <row r="388">
@@ -17455,10 +17455,10 @@
         <v>1.06</v>
       </c>
       <c r="I388" t="n">
-        <v>0.1863</v>
+        <v>0.1465</v>
       </c>
       <c r="J388" t="n">
-        <v>4.4712</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="389">
@@ -17495,10 +17495,10 @@
         <v>0.95</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="J389" t="n">
-        <v>-1.9368</v>
+        <v>-1.6152</v>
       </c>
     </row>
     <row r="390">
@@ -17535,10 +17535,10 @@
         <v>0.86</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1834</v>
+        <v>-0.1638</v>
       </c>
       <c r="J390" t="n">
-        <v>-4.4016</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="391">
@@ -17575,10 +17575,10 @@
         <v>0.61</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.421</v>
+        <v>-0.4121</v>
       </c>
       <c r="J391" t="n">
-        <v>-10.104</v>
+        <v>-9.8904</v>
       </c>
     </row>
   </sheetData>
